--- a/ETF_Allocation_Model.xlsx
+++ b/ETF_Allocation_Model.xlsx
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>73.09999999999999</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -609,7 +609,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>71.2</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>75.8</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>63.8</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -732,7 +732,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>81.2</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>

--- a/ETF_Allocation_Model.xlsx
+++ b/ETF_Allocation_Model.xlsx
@@ -609,7 +609,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>71.40000000000001</v>
+        <v>71.3</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>75.90000000000001</v>
+        <v>75.8</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -732,7 +732,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>81.40000000000001</v>
+        <v>81.2</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -773,7 +773,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>36.4</v>
+        <v>36.3</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>

--- a/ETF_Allocation_Model.xlsx
+++ b/ETF_Allocation_Model.xlsx
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>73.59999999999999</v>
+        <v>74.2</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>73</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -609,7 +609,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>71.3</v>
+        <v>71.2</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -631,12 +631,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>XAIX.MI</t>
+          <t>DFNS.MI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Xtrackers Artificial Intelligence &amp; Big Data UCITS ETF</t>
+          <t>VanEck Defense UCITS ETF</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -646,15 +646,15 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Artificial Intelligence</t>
+          <t>Defense</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>75.8</v>
+        <v>80.2</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Accumulate Carefully</t>
+          <t>Buy Watchlist</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -665,19 +665,19 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Tema strutturale forte, ma rischio euforia/concentrazione elevato.</t>
+          <t>Tema sostenuto da contesto geopolitico, ma da usare come satellite.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>RBOT.MI</t>
+          <t>XAIX.MI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>iShares Automation &amp; Robotics UCITS ETF</t>
+          <t>Xtrackers Artificial Intelligence &amp; Big Data UCITS ETF</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -687,15 +687,15 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Robotics</t>
+          <t>Artificial Intelligence</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>64.09999999999999</v>
+        <v>76.3</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hold / Monitor</t>
+          <t>Accumulate Carefully</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -706,7 +706,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Drawdown storico importante.</t>
+          <t>Tema strutturale forte, ma rischio euforia/concentrazione elevato.</t>
         </is>
       </c>
     </row>
@@ -732,11 +732,11 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>81.2</v>
+        <v>79.7</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Buy Watchlist</t>
+          <t>Accumulate Carefully</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -773,7 +773,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>36.3</v>
+        <v>36.1</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>

--- a/ETF_Allocation_Model.xlsx
+++ b/ETF_Allocation_Model.xlsx
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>73.09999999999999</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -568,7 +568,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>82</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -609,7 +609,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>71.2</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -631,12 +631,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DFNS.MI</t>
+          <t>XAIX.MI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>VanEck Defense UCITS ETF</t>
+          <t>Xtrackers Artificial Intelligence &amp; Big Data UCITS ETF</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -646,15 +646,15 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Defense</t>
+          <t>Artificial Intelligence</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>80.2</v>
+        <v>76</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Buy Watchlist</t>
+          <t>Accumulate Carefully</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -665,19 +665,19 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Tema sostenuto da contesto geopolitico, ma da usare come satellite.</t>
+          <t>Tema strutturale forte, ma rischio euforia/concentrazione elevato.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>XAIX.MI</t>
+          <t>DFNS.MI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Xtrackers Artificial Intelligence &amp; Big Data UCITS ETF</t>
+          <t>VanEck Defense UCITS ETF</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -687,15 +687,15 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Artificial Intelligence</t>
+          <t>Defense</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>76.3</v>
+        <v>63.2</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Accumulate Carefully</t>
+          <t>Hold / Monitor</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -706,7 +706,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Tema strutturale forte, ma rischio euforia/concentrazione elevato.</t>
+          <t>Tema sostenuto da contesto geopolitico, ma da usare come satellite.</t>
         </is>
       </c>
     </row>
@@ -732,7 +732,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>79.7</v>
+        <v>79</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -773,7 +773,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>36.1</v>
+        <v>36.3</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>

--- a/ETF_Allocation_Model.xlsx
+++ b/ETF_Allocation_Model.xlsx
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>74.2</v>
+        <v>74.8</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>72.59999999999999</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -568,7 +568,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>81.90000000000001</v>
+        <v>82.2</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -631,12 +631,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>XAIX.MI</t>
+          <t>DFNS.MI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Xtrackers Artificial Intelligence &amp; Big Data UCITS ETF</t>
+          <t>VanEck Defense UCITS ETF</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -646,15 +646,15 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Artificial Intelligence</t>
+          <t>Defense</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Accumulate Carefully</t>
+          <t>Buy Watchlist</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -665,19 +665,19 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Tema strutturale forte, ma rischio euforia/concentrazione elevato.</t>
+          <t>Tema sostenuto da contesto geopolitico, ma da usare come satellite.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DFNS.MI</t>
+          <t>XAIX.MI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>VanEck Defense UCITS ETF</t>
+          <t>Xtrackers Artificial Intelligence &amp; Big Data UCITS ETF</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -687,15 +687,15 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Defense</t>
+          <t>Artificial Intelligence</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>63.2</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hold / Monitor</t>
+          <t>Accumulate Carefully</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -706,7 +706,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Tema sostenuto da contesto geopolitico, ma da usare come satellite.</t>
+          <t>Tema strutturale forte, ma rischio euforia/concentrazione elevato.</t>
         </is>
       </c>
     </row>
@@ -732,7 +732,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>79</v>
+        <v>79.7</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -773,7 +773,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>36.3</v>
+        <v>36.4</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>

--- a/ETF_Allocation_Model.xlsx
+++ b/ETF_Allocation_Model.xlsx
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>74.8</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>72.90000000000001</v>
+        <v>72.7</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -609,7 +609,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>70.59999999999999</v>
+        <v>70.2</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>82</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>76.40000000000001</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -732,11 +732,11 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>79.7</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Accumulate Carefully</t>
+          <t>Buy Watchlist</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -773,11 +773,11 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>36.4</v>
+        <v>52.5</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Avoid for Now</t>
+          <t>Hold / Monitor</t>
         </is>
       </c>
       <c r="G9" t="n">

--- a/ETF_Allocation_Model.xlsx
+++ b/ETF_Allocation_Model.xlsx
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>74.40000000000001</v>
+        <v>76</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>72.7</v>
+        <v>73</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>81.40000000000001</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>76.59999999999999</v>
+        <v>70.8</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -732,11 +732,11 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>80.90000000000001</v>
+        <v>79.3</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Buy Watchlist</t>
+          <t>Accumulate Carefully</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -773,11 +773,11 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>52.5</v>
+        <v>36</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Hold / Monitor</t>
+          <t>Avoid for Now</t>
         </is>
       </c>
       <c r="G9" t="n">

--- a/ETF_Allocation_Model.xlsx
+++ b/ETF_Allocation_Model.xlsx
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>76</v>
+        <v>76.2</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>73</v>
+        <v>73.2</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -590,12 +590,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>IWQU.MI</t>
+          <t>IWMO.MI</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>iShares MSCI World Quality Factor UCITS ETF</t>
+          <t>iShares MSCI World Momentum Factor UCITS ETF</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -605,11 +605,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Quality</t>
+          <t>Momentum</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>70.2</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -631,12 +631,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DFNS.MI</t>
+          <t>XAIX.MI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>VanEck Defense UCITS ETF</t>
+          <t>Xtrackers Artificial Intelligence &amp; Big Data UCITS ETF</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -646,15 +646,15 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Defense</t>
+          <t>Artificial Intelligence</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>80.59999999999999</v>
+        <v>70.8</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Buy Watchlist</t>
+          <t>Accumulate Carefully</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -665,19 +665,19 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Tema sostenuto da contesto geopolitico, ma da usare come satellite.</t>
+          <t>Tema strutturale forte, ma rischio euforia/concentrazione elevato.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>XAIX.MI</t>
+          <t>ISPY.MI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Xtrackers Artificial Intelligence &amp; Big Data UCITS ETF</t>
+          <t>L&amp;G Cyber Security UCITS ETF</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -687,11 +687,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Artificial Intelligence</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>70.8</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -706,7 +706,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Tema strutturale forte, ma rischio euforia/concentrazione elevato.</t>
+          <t>Monitorare secondo score e trend.</t>
         </is>
       </c>
     </row>
@@ -732,11 +732,11 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>79.3</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Accumulate Carefully</t>
+          <t>Buy Watchlist</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -773,7 +773,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>36</v>
+        <v>36.2</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>

--- a/ETF_Allocation_Model.xlsx
+++ b/ETF_Allocation_Model.xlsx
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>76.2</v>
+        <v>75.8</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>73.2</v>
+        <v>73</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -609,7 +609,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>70.09999999999999</v>
+        <v>71</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>70.8</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>67.40000000000001</v>
+        <v>67.3</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -732,11 +732,11 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>80.09999999999999</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Buy Watchlist</t>
+          <t>Accumulate Carefully</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -773,7 +773,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>36.2</v>
+        <v>36</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>

--- a/ETF_Allocation_Model.xlsx
+++ b/ETF_Allocation_Model.xlsx
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>75.8</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>73</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -568,7 +568,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>82.2</v>
+        <v>81.8</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -590,12 +590,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>IWMO.MI</t>
+          <t>IWQU.MI</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>iShares MSCI World Momentum Factor UCITS ETF</t>
+          <t>iShares MSCI World Quality Factor UCITS ETF</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -605,11 +605,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Momentum</t>
+          <t>Quality</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>76.59999999999999</v>
+        <v>75.8</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -691,11 +691,11 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>67.3</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Accumulate Carefully</t>
+          <t>Hold / Monitor</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -732,7 +732,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>78.59999999999999</v>
+        <v>77.2</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -773,7 +773,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>36</v>
+        <v>35.9</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>

--- a/ETF_Allocation_Model.xlsx
+++ b/ETF_Allocation_Model.xlsx
@@ -568,7 +568,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>81.8</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>64.40000000000001</v>
+        <v>64.3</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>

--- a/ETF_Allocation_Model.xlsx
+++ b/ETF_Allocation_Model.xlsx
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>71.90000000000001</v>
+        <v>72.7</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -501,7 +501,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Monitorare secondo score e trend.</t>
+          <t>Monitorare secondo score, trend e rischio.</t>
         </is>
       </c>
     </row>
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>71.90000000000001</v>
+        <v>71.5</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -568,7 +568,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>81.90000000000001</v>
+        <v>82</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -583,7 +583,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Monitorare secondo score e trend.</t>
+          <t>Monitorare secondo score, trend e rischio.</t>
         </is>
       </c>
     </row>
@@ -609,7 +609,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>70</v>
+        <v>69.5</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -624,7 +624,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Monitorare secondo score e trend.</t>
+          <t>Monitorare secondo score, trend e rischio.</t>
         </is>
       </c>
     </row>
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>75.8</v>
+        <v>76</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -665,7 +665,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Tema strutturale forte, ma rischio euforia/concentrazione elevato.</t>
+          <t>Tema strutturale forte, ma con rischio euforia e concentrazione.</t>
         </is>
       </c>
     </row>
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>64.3</v>
+        <v>62.2</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -706,7 +706,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Monitorare secondo score e trend.</t>
+          <t>Monitorare secondo score, trend e rischio.</t>
         </is>
       </c>
     </row>
@@ -732,11 +732,11 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>77.2</v>
+        <v>61.3</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Accumulate Carefully</t>
+          <t>Hold / Monitor</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -747,7 +747,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Utile come protezione macro/geopolitica.</t>
+          <t>Utile come protezione macro/geopolitica. Prezzo sotto media 200: trend non ancora convincente.</t>
         </is>
       </c>
     </row>
@@ -773,7 +773,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>35.9</v>
+        <v>38.9</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Componente difensiva, utile per bilanciare rischio equity.</t>
+          <t>Componente difensiva utile per bilanciare il rischio equity. Prezzo sotto media 200: trend non ancora convincente.</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -845,10 +845,22 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>Ultimo aggiornamento</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>09/06/2026 09:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
           <t>Nota</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Allocazione indicativa, non consulenza finanziaria personalizzata</t>
         </is>

--- a/ETF_Allocation_Model.xlsx
+++ b/ETF_Allocation_Model.xlsx
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>72.7</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -609,7 +609,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>69.5</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -732,7 +732,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>61.3</v>
+        <v>61.2</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -850,7 +850,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>09/06/2026 09:44</t>
+          <t>09/06/2026 11:21</t>
         </is>
       </c>
     </row>

--- a/ETF_Allocation_Model.xlsx
+++ b/ETF_Allocation_Model.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -440,25 +440,35 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>Peso Target %</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Importo su 1000 EUR</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>Score Finale</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Stato</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Peso Target %</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Importo su 1000 EUR</t>
-        </is>
-      </c>
       <c r="I1" t="inlineStr">
+        <is>
+          <t>Volatilità %</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Max Drawdown %</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
         <is>
           <t>Note AI</t>
         </is>
@@ -472,7 +482,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>iShares Core MSCI Emerging Markets IMI UCITS ETF</t>
+          <t>iShares Core MSCI EM IMI UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -482,38 +492,44 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Emerging Markets</t>
+          <t>Mercati emergenti</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>72.90000000000001</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Accumulate Carefully</t>
-        </is>
+        <v>18.33</v>
+      </c>
+      <c r="F2" t="n">
+        <v>183.3</v>
       </c>
       <c r="G2" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="H2" t="n">
-        <v>325</v>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Monitorare secondo score, trend e rischio.</t>
+        <v>79.3</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Buy Watchlist</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>16.01</v>
+      </c>
+      <c r="J2" t="n">
+        <v>-19.17</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>ETF forte e in trend favorevole; valutare solo con coerenza di portafoglio.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>VWCE.MI</t>
+          <t>VWCE.DE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Vanguard FTSE All-World UCITS ETF</t>
+          <t>Vanguard FTSE All-World UCITS ETF USD Accumulation</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -523,272 +539,451 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Global Equity</t>
+          <t>Azionario globale</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>71.5</v>
-      </c>
-      <c r="F3" t="inlineStr">
+        <v>18.33</v>
+      </c>
+      <c r="F3" t="n">
+        <v>183.3</v>
+      </c>
+      <c r="G3" t="n">
+        <v>76.40000000000001</v>
+      </c>
+      <c r="H3" t="inlineStr">
         <is>
           <t>Accumulate Carefully</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="H3" t="n">
-        <v>325</v>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Buona base core di lungo periodo.</t>
+      <c r="I3" t="n">
+        <v>12.86</v>
+      </c>
+      <c r="J3" t="n">
+        <v>-21.07</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>XDEV.MI</t>
+          <t>SWDA.MI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Xtrackers MSCI World Value UCITS ETF</t>
+          <t>iShares Core MSCI World UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Factor</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Value</t>
+          <t>Azionario globale sviluppato</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>82</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Buy Watchlist</t>
-        </is>
+        <v>18.33</v>
+      </c>
+      <c r="F4" t="n">
+        <v>183.3</v>
       </c>
       <c r="G4" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="H4" t="n">
-        <v>75</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Monitorare secondo score, trend e rischio.</t>
+        <v>75.5</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Accumulate Carefully</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>13.13</v>
+      </c>
+      <c r="J4" t="n">
+        <v>-21.63</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>IWQU.MI</t>
+          <t>MVOL.MI</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>iShares MSCI World Quality Factor UCITS ETF</t>
+          <t>iShares Edge MSCI World Minimum Volatility UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Factor</t>
+          <t>Defensive</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Quality</t>
+          <t>Min volatility</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>69.59999999999999</v>
-      </c>
-      <c r="F5" t="inlineStr">
+        <v>6.67</v>
+      </c>
+      <c r="F5" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="G5" t="n">
+        <v>68.3</v>
+      </c>
+      <c r="H5" t="inlineStr">
         <is>
           <t>Accumulate Carefully</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="H5" t="n">
-        <v>75</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Monitorare secondo score, trend e rischio.</t>
+      <c r="I5" t="n">
+        <v>9.550000000000001</v>
+      </c>
+      <c r="J5" t="n">
+        <v>-12.85</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Strumento utile per bilanciare volatilità e rischio macro.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>XAIX.MI</t>
+          <t>SGLD.MI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Xtrackers Artificial Intelligence &amp; Big Data UCITS ETF</t>
+          <t>Invesco Physical Gold ETC</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Thematic</t>
+          <t>Defensive</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Artificial Intelligence</t>
+          <t>Oro</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>76</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Accumulate Carefully</t>
-        </is>
+        <v>6.67</v>
+      </c>
+      <c r="F6" t="n">
+        <v>66.7</v>
       </c>
       <c r="G6" t="n">
-        <v>5</v>
-      </c>
-      <c r="H6" t="n">
-        <v>50</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Tema strutturale forte, ma con rischio euforia e concentrazione.</t>
+        <v>55.5</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Hold / Monitor</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>17.78</v>
+      </c>
+      <c r="J6" t="n">
+        <v>-17.4</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Strumento utile per bilanciare volatilità e rischio macro.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ISPY.MI</t>
+          <t>EUNA.MI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>L&amp;G Cyber Security UCITS ETF</t>
+          <t>iShares Core Global Aggregate Bond</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Thematic</t>
+          <t>Defensive</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Cybersecurity</t>
+          <t>Obbligazionario globale</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>62.2</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Hold / Monitor</t>
-        </is>
+        <v>6.67</v>
+      </c>
+      <c r="F7" t="n">
+        <v>66.7</v>
       </c>
       <c r="G7" t="n">
-        <v>5</v>
-      </c>
-      <c r="H7" t="n">
-        <v>50</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Monitorare secondo score, trend e rischio.</t>
+        <v>28.6</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Avoid for Now</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Strumento utile per bilanciare volatilità e rischio macro.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SGLD.MI</t>
+          <t>XDEV.MI</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Invesco Physical Gold ETC</t>
+          <t>Xtrackers MSCI World Value UCITS ETF 1C</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Defensive</t>
+          <t>Factor</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Value globale</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>61.2</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Hold / Monitor</t>
-        </is>
+        <v>7.5</v>
+      </c>
+      <c r="F8" t="n">
+        <v>75</v>
       </c>
       <c r="G8" t="n">
-        <v>5</v>
-      </c>
-      <c r="H8" t="n">
-        <v>50</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Utile come protezione macro/geopolitica. Prezzo sotto media 200: trend non ancora convincente.</t>
+        <v>79.2</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Accumulate Carefully</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>13.61</v>
+      </c>
+      <c r="J8" t="n">
+        <v>-17.8</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>ETF interessante ma ingresso non ideale: meglio attendere pullback o conferma.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AGGH.MI</t>
+          <t>IWQU.MI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>iShares Core Global Aggregate Bond UCITS ETF</t>
+          <t>iShares Edge MSCI World Quality Factor UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Defensive</t>
+          <t>Factor</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Global Bonds</t>
+          <t>Quality globale</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>38.9</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Avoid for Now</t>
-        </is>
+        <v>7.5</v>
+      </c>
+      <c r="F9" t="n">
+        <v>75</v>
       </c>
       <c r="G9" t="n">
-        <v>5</v>
-      </c>
-      <c r="H9" t="n">
-        <v>50</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Componente difensiva utile per bilanciare il rischio equity. Prezzo sotto media 200: trend non ancora convincente.</t>
+        <v>72.8</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Accumulate Carefully</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>12.86</v>
+      </c>
+      <c r="J9" t="n">
+        <v>-20.6</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>RBOT.MI</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>iShares Automation &amp; Robotics UCITS ETF USD (Acc)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Thematic</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Robotica e automazione</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="F10" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="G10" t="n">
+        <v>68.90000000000001</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Accumulate Carefully</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>21.32</v>
+      </c>
+      <c r="J10" t="n">
+        <v>-29.37</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>INRG.MI</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>iShares Global Clean Energy Transition UCITS ETF USD (Dist)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Thematic</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Energia pulita</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="F11" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="G11" t="n">
+        <v>64.3</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Hold / Monitor</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>23.17</v>
+      </c>
+      <c r="J11" t="n">
+        <v>-44.26</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Rischio elevato: usare solo come quota satellite e con size ridotta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>SMH</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>VanEck Semiconductor ETF</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Thematic</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Semiconduttori</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="F12" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="G12" t="n">
+        <v>61.9</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Hold / Monitor</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>34.92</v>
+      </c>
+      <c r="J12" t="n">
+        <v>-35.74</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Rischio elevato: usare solo come quota satellite e con size ridotta.</t>
         </is>
       </c>
     </row>
@@ -803,7 +998,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -833,36 +1028,42 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Importo simulato</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>1000 EUR</t>
-        </is>
+          <t>ETF analizzati</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Ultimo aggiornamento</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>09/06/2026 11:21</t>
-        </is>
+          <t>ETF in allocazione</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>Score medio</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>65.92</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>Nota</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Allocazione indicativa, non consulenza finanziaria personalizzata</t>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Allocazione informativa su 1000 EUR, non consulenza personalizzata.</t>
         </is>
       </c>
     </row>

--- a/ETF_Allocation_Model.xlsx
+++ b/ETF_Allocation_Model.xlsx
@@ -510,7 +510,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>16.01</v>
+        <v>16</v>
       </c>
       <c r="J2" t="n">
         <v>-19.17</v>
@@ -596,7 +596,7 @@
         <v>183.3</v>
       </c>
       <c r="G4" t="n">
-        <v>75.5</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -643,7 +643,7 @@
         <v>66.7</v>
       </c>
       <c r="G5" t="n">
-        <v>68.3</v>
+        <v>68.2</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>9.550000000000001</v>
+        <v>9.56</v>
       </c>
       <c r="J5" t="n">
         <v>-12.85</v>
@@ -690,7 +690,7 @@
         <v>66.7</v>
       </c>
       <c r="G6" t="n">
-        <v>55.5</v>
+        <v>55.4</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -701,7 +701,7 @@
         <v>17.78</v>
       </c>
       <c r="J6" t="n">
-        <v>-17.4</v>
+        <v>-17.45</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -827,7 +827,7 @@
         <v>75</v>
       </c>
       <c r="G9" t="n">
-        <v>72.8</v>
+        <v>72.7</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -874,7 +874,7 @@
         <v>33.3</v>
       </c>
       <c r="G10" t="n">
-        <v>68.90000000000001</v>
+        <v>69</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>65.92</v>
+        <v>65.90000000000001</v>
       </c>
     </row>
     <row r="6">

--- a/ETF_Allocation_Model.xlsx
+++ b/ETF_Allocation_Model.xlsx
@@ -690,7 +690,7 @@
         <v>66.7</v>
       </c>
       <c r="G6" t="n">
-        <v>55.4</v>
+        <v>55.5</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -701,7 +701,7 @@
         <v>17.78</v>
       </c>
       <c r="J6" t="n">
-        <v>-17.45</v>
+        <v>-17.39</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>65.90000000000001</v>
+        <v>65.91</v>
       </c>
     </row>
     <row r="6">

--- a/ETF_Allocation_Model.xlsx
+++ b/ETF_Allocation_Model.xlsx
@@ -510,7 +510,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>16</v>
+        <v>16.01</v>
       </c>
       <c r="J2" t="n">
         <v>-19.17</v>
@@ -596,7 +596,7 @@
         <v>183.3</v>
       </c>
       <c r="G4" t="n">
-        <v>75.40000000000001</v>
+        <v>75.5</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -701,7 +701,7 @@
         <v>17.78</v>
       </c>
       <c r="J6" t="n">
-        <v>-17.39</v>
+        <v>-17.4</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>

--- a/ETF_Allocation_Model.xlsx
+++ b/ETF_Allocation_Model.xlsx
@@ -502,7 +502,7 @@
         <v>183.3</v>
       </c>
       <c r="G2" t="n">
-        <v>79.3</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>65.91</v>
+        <v>65.92</v>
       </c>
     </row>
     <row r="6">

--- a/ETF_Allocation_Model.xlsx
+++ b/ETF_Allocation_Model.xlsx
@@ -502,7 +502,7 @@
         <v>183.3</v>
       </c>
       <c r="G2" t="n">
-        <v>79.40000000000001</v>
+        <v>79.3</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -596,7 +596,7 @@
         <v>183.3</v>
       </c>
       <c r="G4" t="n">
-        <v>75.5</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -690,7 +690,7 @@
         <v>66.7</v>
       </c>
       <c r="G6" t="n">
-        <v>55.5</v>
+        <v>55.6</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -701,7 +701,7 @@
         <v>17.78</v>
       </c>
       <c r="J6" t="n">
-        <v>-17.4</v>
+        <v>-17.31</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -874,7 +874,7 @@
         <v>33.3</v>
       </c>
       <c r="G10" t="n">
-        <v>69</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>65.92</v>
+        <v>65.54000000000001</v>
       </c>
     </row>
     <row r="6">

--- a/ETF_Allocation_Model.xlsx
+++ b/ETF_Allocation_Model.xlsx
@@ -596,7 +596,7 @@
         <v>183.3</v>
       </c>
       <c r="G4" t="n">
-        <v>75.40000000000001</v>
+        <v>75.3</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -701,7 +701,7 @@
         <v>17.78</v>
       </c>
       <c r="J6" t="n">
-        <v>-17.31</v>
+        <v>-17.28</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>75</v>
       </c>
       <c r="G8" t="n">
-        <v>79.2</v>
+        <v>79.3</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -874,7 +874,7 @@
         <v>33.3</v>
       </c>
       <c r="G10" t="n">
-        <v>68.90000000000001</v>
+        <v>69</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>

--- a/ETF_Allocation_Model.xlsx
+++ b/ETF_Allocation_Model.xlsx
@@ -510,7 +510,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>16.01</v>
+        <v>16</v>
       </c>
       <c r="J2" t="n">
         <v>-19.17</v>
@@ -701,7 +701,7 @@
         <v>17.78</v>
       </c>
       <c r="J6" t="n">
-        <v>-17.28</v>
+        <v>-17.36</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>

--- a/ETF_Allocation_Model.xlsx
+++ b/ETF_Allocation_Model.xlsx
@@ -502,7 +502,7 @@
         <v>183.3</v>
       </c>
       <c r="G2" t="n">
-        <v>79.3</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -510,7 +510,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>16</v>
+        <v>16.01</v>
       </c>
       <c r="J2" t="n">
         <v>-19.17</v>
@@ -596,7 +596,7 @@
         <v>183.3</v>
       </c>
       <c r="G4" t="n">
-        <v>75.3</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -701,7 +701,7 @@
         <v>17.78</v>
       </c>
       <c r="J6" t="n">
-        <v>-17.36</v>
+        <v>-17.33</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>75</v>
       </c>
       <c r="G8" t="n">
-        <v>79.3</v>
+        <v>79.2</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -827,7 +827,7 @@
         <v>75</v>
       </c>
       <c r="G9" t="n">
-        <v>72.7</v>
+        <v>72.8</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -874,7 +874,7 @@
         <v>33.3</v>
       </c>
       <c r="G10" t="n">
-        <v>69</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>65.54000000000001</v>
+        <v>65.55</v>
       </c>
     </row>
     <row r="6">

--- a/ETF_Allocation_Model.xlsx
+++ b/ETF_Allocation_Model.xlsx
@@ -701,7 +701,7 @@
         <v>17.78</v>
       </c>
       <c r="J6" t="n">
-        <v>-17.33</v>
+        <v>-17.31</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -874,7 +874,7 @@
         <v>33.3</v>
       </c>
       <c r="G10" t="n">
-        <v>68.90000000000001</v>
+        <v>68.8</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>65.55</v>
+        <v>65.54000000000001</v>
       </c>
     </row>
     <row r="6">

--- a/ETF_Allocation_Model.xlsx
+++ b/ETF_Allocation_Model.xlsx
@@ -502,7 +502,7 @@
         <v>183.3</v>
       </c>
       <c r="G2" t="n">
-        <v>79.40000000000001</v>
+        <v>79</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -510,7 +510,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>16.01</v>
+        <v>15.98</v>
       </c>
       <c r="J2" t="n">
         <v>-19.17</v>
@@ -549,7 +549,7 @@
         <v>183.3</v>
       </c>
       <c r="G3" t="n">
-        <v>76.40000000000001</v>
+        <v>75.8</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>12.86</v>
+        <v>12.87</v>
       </c>
       <c r="J3" t="n">
         <v>-21.07</v>
@@ -596,7 +596,7 @@
         <v>183.3</v>
       </c>
       <c r="G4" t="n">
-        <v>75.40000000000001</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>13.13</v>
+        <v>13.14</v>
       </c>
       <c r="J4" t="n">
         <v>-21.63</v>
@@ -643,7 +643,7 @@
         <v>66.7</v>
       </c>
       <c r="G5" t="n">
-        <v>68.2</v>
+        <v>68.3</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>9.56</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="J5" t="n">
         <v>-12.85</v>
@@ -690,18 +690,18 @@
         <v>66.7</v>
       </c>
       <c r="G6" t="n">
-        <v>55.6</v>
+        <v>54.5</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Hold / Monitor</t>
+          <t>Avoid for Now</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>17.78</v>
+        <v>17.79</v>
       </c>
       <c r="J6" t="n">
-        <v>-17.31</v>
+        <v>-18.11</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -780,22 +780,22 @@
         <v>75</v>
       </c>
       <c r="G8" t="n">
-        <v>79.2</v>
+        <v>80</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Accumulate Carefully</t>
+          <t>Buy Watchlist</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>13.61</v>
+        <v>13.62</v>
       </c>
       <c r="J8" t="n">
         <v>-17.8</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>ETF interessante ma ingresso non ideale: meglio attendere pullback o conferma.</t>
+          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
         <v>75</v>
       </c>
       <c r="G9" t="n">
-        <v>72.8</v>
+        <v>72.5</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>12.86</v>
+        <v>12.87</v>
       </c>
       <c r="J9" t="n">
         <v>-20.6</v>
@@ -874,7 +874,7 @@
         <v>33.3</v>
       </c>
       <c r="G10" t="n">
-        <v>68.8</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>21.32</v>
+        <v>21.33</v>
       </c>
       <c r="J10" t="n">
         <v>-29.37</v>
@@ -921,7 +921,7 @@
         <v>33.3</v>
       </c>
       <c r="G11" t="n">
-        <v>64.3</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>23.17</v>
+        <v>23.22</v>
       </c>
       <c r="J11" t="n">
         <v>-44.26</v>
@@ -968,7 +968,7 @@
         <v>33.3</v>
       </c>
       <c r="G12" t="n">
-        <v>61.9</v>
+        <v>63.3</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -976,7 +976,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>34.92</v>
+        <v>34.91</v>
       </c>
       <c r="J12" t="n">
         <v>-35.74</v>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>65.54000000000001</v>
+        <v>65.53</v>
       </c>
     </row>
     <row r="6">

--- a/ETF_Allocation_Model.xlsx
+++ b/ETF_Allocation_Model.xlsx
@@ -549,7 +549,7 @@
         <v>183.3</v>
       </c>
       <c r="G3" t="n">
-        <v>75.8</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -701,7 +701,7 @@
         <v>17.79</v>
       </c>
       <c r="J6" t="n">
-        <v>-18.11</v>
+        <v>-18.16</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>75</v>
       </c>
       <c r="G8" t="n">
-        <v>80</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -827,7 +827,7 @@
         <v>75</v>
       </c>
       <c r="G9" t="n">
-        <v>72.5</v>
+        <v>72.7</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -874,7 +874,7 @@
         <v>33.3</v>
       </c>
       <c r="G10" t="n">
-        <v>69.59999999999999</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -896,12 +896,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>INRG.MI</t>
+          <t>SMH</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>iShares Global Clean Energy Transition UCITS ETF USD (Dist)</t>
+          <t>VanEck Semiconductor ETF</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -911,7 +911,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Energia pulita</t>
+          <t>Semiconduttori</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -921,7 +921,7 @@
         <v>33.3</v>
       </c>
       <c r="G11" t="n">
-        <v>64.09999999999999</v>
+        <v>64.5</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>23.22</v>
+        <v>34.96</v>
       </c>
       <c r="J11" t="n">
-        <v>-44.26</v>
+        <v>-35.74</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -943,12 +943,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SMH</t>
+          <t>INRG.MI</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>VanEck Semiconductor ETF</t>
+          <t>iShares Global Clean Energy Transition UCITS ETF USD (Dist)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -958,7 +958,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Semiconduttori</t>
+          <t>Energia pulita</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -968,7 +968,7 @@
         <v>33.3</v>
       </c>
       <c r="G12" t="n">
-        <v>63.3</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>34.91</v>
+        <v>23.21</v>
       </c>
       <c r="J12" t="n">
-        <v>-35.74</v>
+        <v>-44.26</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>65.53</v>
+        <v>65.59999999999999</v>
       </c>
     </row>
     <row r="6">

--- a/ETF_Allocation_Model.xlsx
+++ b/ETF_Allocation_Model.xlsx
@@ -502,7 +502,7 @@
         <v>183.3</v>
       </c>
       <c r="G2" t="n">
-        <v>79</v>
+        <v>78.7</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -510,7 +510,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>15.98</v>
+        <v>15.99</v>
       </c>
       <c r="J2" t="n">
         <v>-19.17</v>
@@ -549,7 +549,7 @@
         <v>183.3</v>
       </c>
       <c r="G3" t="n">
-        <v>75.90000000000001</v>
+        <v>75.8</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -596,7 +596,7 @@
         <v>183.3</v>
       </c>
       <c r="G4" t="n">
-        <v>74.90000000000001</v>
+        <v>74.8</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>9.550000000000001</v>
+        <v>9.56</v>
       </c>
       <c r="J5" t="n">
         <v>-12.85</v>
@@ -690,18 +690,18 @@
         <v>66.7</v>
       </c>
       <c r="G6" t="n">
-        <v>54.5</v>
+        <v>55.7</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Avoid for Now</t>
+          <t>Hold / Monitor</t>
         </is>
       </c>
       <c r="I6" t="n">
         <v>17.79</v>
       </c>
       <c r="J6" t="n">
-        <v>-18.16</v>
+        <v>-17.19</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -780,11 +780,11 @@
         <v>75</v>
       </c>
       <c r="G8" t="n">
-        <v>79.90000000000001</v>
+        <v>79.2</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Buy Watchlist</t>
+          <t>Accumulate Carefully</t>
         </is>
       </c>
       <c r="I8" t="n">
@@ -795,7 +795,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
+          <t>ETF interessante ma ingresso non ideale: meglio attendere pullback o conferma.</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
         <v>75</v>
       </c>
       <c r="G9" t="n">
-        <v>72.7</v>
+        <v>72.3</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -874,7 +874,7 @@
         <v>33.3</v>
       </c>
       <c r="G10" t="n">
-        <v>69.40000000000001</v>
+        <v>68.8</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>21.33</v>
+        <v>21.34</v>
       </c>
       <c r="J10" t="n">
         <v>-29.37</v>
@@ -896,12 +896,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SMH</t>
+          <t>INRG.MI</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>VanEck Semiconductor ETF</t>
+          <t>iShares Global Clean Energy Transition UCITS ETF USD (Dist)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -911,7 +911,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Semiconduttori</t>
+          <t>Energia pulita</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -921,7 +921,7 @@
         <v>33.3</v>
       </c>
       <c r="G11" t="n">
-        <v>64.5</v>
+        <v>64.2</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>34.96</v>
+        <v>23.18</v>
       </c>
       <c r="J11" t="n">
-        <v>-35.74</v>
+        <v>-44.26</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -943,12 +943,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>INRG.MI</t>
+          <t>SMH</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>iShares Global Clean Energy Transition UCITS ETF USD (Dist)</t>
+          <t>VanEck Semiconductor ETF</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -958,7 +958,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Energia pulita</t>
+          <t>Semiconduttori</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -968,7 +968,7 @@
         <v>33.3</v>
       </c>
       <c r="G12" t="n">
-        <v>64.09999999999999</v>
+        <v>63.1</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>23.21</v>
+        <v>34.89</v>
       </c>
       <c r="J12" t="n">
-        <v>-44.26</v>
+        <v>-35.74</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>65.59999999999999</v>
+        <v>65.73999999999999</v>
       </c>
     </row>
     <row r="6">

--- a/ETF_Allocation_Model.xlsx
+++ b/ETF_Allocation_Model.xlsx
@@ -502,7 +502,7 @@
         <v>183.3</v>
       </c>
       <c r="G2" t="n">
-        <v>78.7</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -510,7 +510,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>15.99</v>
+        <v>16</v>
       </c>
       <c r="J2" t="n">
         <v>-19.17</v>
@@ -549,7 +549,7 @@
         <v>183.3</v>
       </c>
       <c r="G3" t="n">
-        <v>75.8</v>
+        <v>75.3</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>12.87</v>
+        <v>12.89</v>
       </c>
       <c r="J3" t="n">
         <v>-21.07</v>
@@ -596,7 +596,7 @@
         <v>183.3</v>
       </c>
       <c r="G4" t="n">
-        <v>74.8</v>
+        <v>74.3</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>13.14</v>
+        <v>13.17</v>
       </c>
       <c r="J4" t="n">
         <v>-21.63</v>
@@ -643,7 +643,7 @@
         <v>66.7</v>
       </c>
       <c r="G5" t="n">
-        <v>68.3</v>
+        <v>68.2</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -690,18 +690,18 @@
         <v>66.7</v>
       </c>
       <c r="G6" t="n">
-        <v>55.7</v>
+        <v>54.1</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Hold / Monitor</t>
+          <t>Avoid for Now</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>17.79</v>
+        <v>17.81</v>
       </c>
       <c r="J6" t="n">
-        <v>-17.19</v>
+        <v>-18.47</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -780,22 +780,22 @@
         <v>75</v>
       </c>
       <c r="G8" t="n">
-        <v>79.2</v>
+        <v>80.5</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Accumulate Carefully</t>
+          <t>Buy Watchlist</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>13.62</v>
+        <v>13.67</v>
       </c>
       <c r="J8" t="n">
         <v>-17.8</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>ETF interessante ma ingresso non ideale: meglio attendere pullback o conferma.</t>
+          <t>ETF forte e in trend favorevole; valutare solo con coerenza di portafoglio.</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
         <v>75</v>
       </c>
       <c r="G9" t="n">
-        <v>72.3</v>
+        <v>72.2</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>12.87</v>
+        <v>12.88</v>
       </c>
       <c r="J9" t="n">
         <v>-20.6</v>
@@ -874,7 +874,7 @@
         <v>33.3</v>
       </c>
       <c r="G10" t="n">
-        <v>68.8</v>
+        <v>70.3</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>21.34</v>
+        <v>21.37</v>
       </c>
       <c r="J10" t="n">
         <v>-29.37</v>
@@ -896,12 +896,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>INRG.MI</t>
+          <t>SMH</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>iShares Global Clean Energy Transition UCITS ETF USD (Dist)</t>
+          <t>VanEck Semiconductor ETF</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -911,7 +911,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Energia pulita</t>
+          <t>Semiconduttori</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -921,7 +921,7 @@
         <v>33.3</v>
       </c>
       <c r="G11" t="n">
-        <v>64.2</v>
+        <v>65.7</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>23.18</v>
+        <v>34.93</v>
       </c>
       <c r="J11" t="n">
-        <v>-44.26</v>
+        <v>-35.74</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -943,12 +943,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SMH</t>
+          <t>INRG.MI</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>VanEck Semiconductor ETF</t>
+          <t>iShares Global Clean Energy Transition UCITS ETF USD (Dist)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -958,7 +958,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Semiconduttori</t>
+          <t>Energia pulita</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -968,7 +968,7 @@
         <v>33.3</v>
       </c>
       <c r="G12" t="n">
-        <v>63.1</v>
+        <v>64</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>34.89</v>
+        <v>23.28</v>
       </c>
       <c r="J12" t="n">
-        <v>-35.74</v>
+        <v>-44.26</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>65.73999999999999</v>
+        <v>65.48999999999999</v>
       </c>
     </row>
     <row r="6">

--- a/ETF_Allocation_Model.xlsx
+++ b/ETF_Allocation_Model.xlsx
@@ -502,22 +502,22 @@
         <v>183.3</v>
       </c>
       <c r="G2" t="n">
-        <v>78.09999999999999</v>
+        <v>77</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Buy Watchlist</t>
+          <t>Accumulate Carefully</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>16</v>
+        <v>15.99</v>
       </c>
       <c r="J2" t="n">
         <v>-19.17</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>ETF forte e in trend favorevole; valutare solo con coerenza di portafoglio.</t>
+          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
         </is>
       </c>
     </row>
@@ -549,7 +549,7 @@
         <v>183.3</v>
       </c>
       <c r="G3" t="n">
-        <v>75.3</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -596,7 +596,7 @@
         <v>183.3</v>
       </c>
       <c r="G4" t="n">
-        <v>74.3</v>
+        <v>73.7</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>13.17</v>
+        <v>13.16</v>
       </c>
       <c r="J4" t="n">
         <v>-21.63</v>
@@ -643,7 +643,7 @@
         <v>66.7</v>
       </c>
       <c r="G5" t="n">
-        <v>68.2</v>
+        <v>68.8</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -690,7 +690,7 @@
         <v>66.7</v>
       </c>
       <c r="G6" t="n">
-        <v>54.1</v>
+        <v>49.8</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -698,10 +698,10 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>17.81</v>
+        <v>17.91</v>
       </c>
       <c r="J6" t="n">
-        <v>-18.47</v>
+        <v>-21.24</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>75</v>
       </c>
       <c r="G8" t="n">
-        <v>80.5</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>13.67</v>
+        <v>13.66</v>
       </c>
       <c r="J8" t="n">
         <v>-17.8</v>
@@ -827,7 +827,7 @@
         <v>75</v>
       </c>
       <c r="G9" t="n">
-        <v>72.2</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -874,7 +874,7 @@
         <v>33.3</v>
       </c>
       <c r="G10" t="n">
-        <v>70.3</v>
+        <v>71</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>21.37</v>
+        <v>21.36</v>
       </c>
       <c r="J10" t="n">
         <v>-29.37</v>
@@ -921,7 +921,7 @@
         <v>33.3</v>
       </c>
       <c r="G11" t="n">
-        <v>65.7</v>
+        <v>62.2</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>34.93</v>
+        <v>35.11</v>
       </c>
       <c r="J11" t="n">
         <v>-35.74</v>
@@ -968,7 +968,7 @@
         <v>33.3</v>
       </c>
       <c r="G12" t="n">
-        <v>64</v>
+        <v>57.3</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -976,7 +976,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>23.28</v>
+        <v>23.32</v>
       </c>
       <c r="J12" t="n">
         <v>-44.26</v>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>65.48999999999999</v>
+        <v>64.33</v>
       </c>
     </row>
     <row r="6">

--- a/ETF_Allocation_Model.xlsx
+++ b/ETF_Allocation_Model.xlsx
@@ -502,7 +502,7 @@
         <v>183.3</v>
       </c>
       <c r="G2" t="n">
-        <v>77</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -549,7 +549,7 @@
         <v>183.3</v>
       </c>
       <c r="G3" t="n">
-        <v>74.59999999999999</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>12.89</v>
+        <v>12.88</v>
       </c>
       <c r="J3" t="n">
         <v>-21.07</v>
@@ -596,7 +596,7 @@
         <v>183.3</v>
       </c>
       <c r="G4" t="n">
-        <v>73.7</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>13.16</v>
+        <v>13.15</v>
       </c>
       <c r="J4" t="n">
         <v>-21.63</v>
@@ -643,7 +643,7 @@
         <v>66.7</v>
       </c>
       <c r="G5" t="n">
-        <v>68.8</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -690,7 +690,7 @@
         <v>66.7</v>
       </c>
       <c r="G6" t="n">
-        <v>49.8</v>
+        <v>49.2</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -701,7 +701,7 @@
         <v>17.91</v>
       </c>
       <c r="J6" t="n">
-        <v>-21.24</v>
+        <v>-21.9</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -827,7 +827,7 @@
         <v>75</v>
       </c>
       <c r="G9" t="n">
-        <v>71.90000000000001</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>12.88</v>
+        <v>12.87</v>
       </c>
       <c r="J9" t="n">
         <v>-20.6</v>
@@ -874,7 +874,7 @@
         <v>33.3</v>
       </c>
       <c r="G10" t="n">
-        <v>71</v>
+        <v>70.8</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>21.36</v>
+        <v>21.35</v>
       </c>
       <c r="J10" t="n">
         <v>-29.37</v>
@@ -921,7 +921,7 @@
         <v>33.3</v>
       </c>
       <c r="G11" t="n">
-        <v>62.2</v>
+        <v>61.6</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>35.11</v>
+        <v>35.12</v>
       </c>
       <c r="J11" t="n">
         <v>-35.74</v>
@@ -968,7 +968,7 @@
         <v>33.3</v>
       </c>
       <c r="G12" t="n">
-        <v>57.3</v>
+        <v>58</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>64.33</v>
+        <v>64.54000000000001</v>
       </c>
     </row>
     <row r="6">

--- a/ETF_Allocation_Model.xlsx
+++ b/ETF_Allocation_Model.xlsx
@@ -502,22 +502,22 @@
         <v>183.3</v>
       </c>
       <c r="G2" t="n">
-        <v>77.90000000000001</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Accumulate Carefully</t>
+          <t>Buy Watchlist</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>15.99</v>
+        <v>16.1</v>
       </c>
       <c r="J2" t="n">
         <v>-19.17</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
+          <t>ETF forte e in trend favorevole; valutare solo con coerenza di portafoglio.</t>
         </is>
       </c>
     </row>
@@ -549,7 +549,7 @@
         <v>183.3</v>
       </c>
       <c r="G3" t="n">
-        <v>74.90000000000001</v>
+        <v>76.3</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>12.88</v>
+        <v>12.92</v>
       </c>
       <c r="J3" t="n">
         <v>-21.07</v>
@@ -596,7 +596,7 @@
         <v>183.3</v>
       </c>
       <c r="G4" t="n">
-        <v>73.90000000000001</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>13.15</v>
+        <v>13.19</v>
       </c>
       <c r="J4" t="n">
         <v>-21.63</v>
@@ -643,7 +643,7 @@
         <v>66.7</v>
       </c>
       <c r="G5" t="n">
-        <v>69.09999999999999</v>
+        <v>69</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>9.56</v>
+        <v>9.57</v>
       </c>
       <c r="J5" t="n">
         <v>-12.85</v>
@@ -690,7 +690,7 @@
         <v>66.7</v>
       </c>
       <c r="G6" t="n">
-        <v>49.2</v>
+        <v>51.7</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -698,7 +698,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>17.91</v>
+        <v>17.99</v>
       </c>
       <c r="J6" t="n">
         <v>-21.9</v>
@@ -780,7 +780,7 @@
         <v>75</v>
       </c>
       <c r="G8" t="n">
-        <v>80.90000000000001</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -788,14 +788,14 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>13.66</v>
+        <v>13.75</v>
       </c>
       <c r="J8" t="n">
         <v>-17.8</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>ETF forte e in trend favorevole; valutare solo con coerenza di portafoglio.</t>
+          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
         <v>75</v>
       </c>
       <c r="G9" t="n">
-        <v>72.40000000000001</v>
+        <v>73.2</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>12.87</v>
+        <v>12.89</v>
       </c>
       <c r="J9" t="n">
         <v>-20.6</v>
@@ -874,7 +874,7 @@
         <v>33.3</v>
       </c>
       <c r="G10" t="n">
-        <v>70.8</v>
+        <v>68.8</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>21.35</v>
+        <v>21.47</v>
       </c>
       <c r="J10" t="n">
         <v>-29.37</v>
@@ -896,12 +896,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SMH</t>
+          <t>INRG.MI</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>VanEck Semiconductor ETF</t>
+          <t>iShares Global Clean Energy Transition UCITS ETF USD (Dist)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -911,7 +911,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Semiconduttori</t>
+          <t>Energia pulita</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -921,7 +921,7 @@
         <v>33.3</v>
       </c>
       <c r="G11" t="n">
-        <v>61.6</v>
+        <v>63.7</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>35.12</v>
+        <v>23.42</v>
       </c>
       <c r="J11" t="n">
-        <v>-35.74</v>
+        <v>-43.61</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -943,12 +943,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>INRG.MI</t>
+          <t>SMH</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>iShares Global Clean Energy Transition UCITS ETF USD (Dist)</t>
+          <t>VanEck Semiconductor ETF</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -958,7 +958,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Energia pulita</t>
+          <t>Semiconduttori</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -968,7 +968,7 @@
         <v>33.3</v>
       </c>
       <c r="G12" t="n">
-        <v>58</v>
+        <v>59.4</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>23.32</v>
+        <v>35.23</v>
       </c>
       <c r="J12" t="n">
-        <v>-44.26</v>
+        <v>-35.74</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>64.54000000000001</v>
+        <v>65.25</v>
       </c>
     </row>
     <row r="6">

--- a/ETF_Allocation_Model.xlsx
+++ b/ETF_Allocation_Model.xlsx
@@ -502,7 +502,7 @@
         <v>183.3</v>
       </c>
       <c r="G2" t="n">
-        <v>79.59999999999999</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -510,7 +510,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>16.1</v>
+        <v>16.17</v>
       </c>
       <c r="J2" t="n">
         <v>-19.17</v>
@@ -549,7 +549,7 @@
         <v>183.3</v>
       </c>
       <c r="G3" t="n">
-        <v>76.3</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>12.92</v>
+        <v>12.94</v>
       </c>
       <c r="J3" t="n">
         <v>-21.07</v>
@@ -596,7 +596,7 @@
         <v>183.3</v>
       </c>
       <c r="G4" t="n">
-        <v>75.09999999999999</v>
+        <v>75.8</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>13.19</v>
+        <v>13.2</v>
       </c>
       <c r="J4" t="n">
         <v>-21.63</v>
@@ -643,7 +643,7 @@
         <v>66.7</v>
       </c>
       <c r="G5" t="n">
-        <v>69</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>9.57</v>
+        <v>9.56</v>
       </c>
       <c r="J5" t="n">
         <v>-12.85</v>
@@ -690,7 +690,7 @@
         <v>66.7</v>
       </c>
       <c r="G6" t="n">
-        <v>51.7</v>
+        <v>54.5</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -698,7 +698,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>17.99</v>
+        <v>18.06</v>
       </c>
       <c r="J6" t="n">
         <v>-21.9</v>
@@ -780,22 +780,22 @@
         <v>75</v>
       </c>
       <c r="G8" t="n">
-        <v>79.59999999999999</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Buy Watchlist</t>
+          <t>Accumulate Carefully</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>13.75</v>
+        <v>13.77</v>
       </c>
       <c r="J8" t="n">
         <v>-17.8</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
+          <t>ETF interessante ma ingresso non ideale: meglio attendere pullback o conferma.</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
         <v>75</v>
       </c>
       <c r="G9" t="n">
-        <v>73.2</v>
+        <v>73.5</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -874,15 +874,15 @@
         <v>33.3</v>
       </c>
       <c r="G10" t="n">
-        <v>68.8</v>
+        <v>67.3</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Accumulate Carefully</t>
+          <t>Hold / Monitor</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>21.47</v>
+        <v>21.54</v>
       </c>
       <c r="J10" t="n">
         <v>-29.37</v>
@@ -921,7 +921,7 @@
         <v>33.3</v>
       </c>
       <c r="G11" t="n">
-        <v>63.7</v>
+        <v>64</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -932,7 +932,7 @@
         <v>23.42</v>
       </c>
       <c r="J11" t="n">
-        <v>-43.61</v>
+        <v>-43.51</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -968,7 +968,7 @@
         <v>33.3</v>
       </c>
       <c r="G12" t="n">
-        <v>59.4</v>
+        <v>63.2</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -976,7 +976,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>35.23</v>
+        <v>35.35</v>
       </c>
       <c r="J12" t="n">
         <v>-35.74</v>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>65.25</v>
+        <v>65.7</v>
       </c>
     </row>
     <row r="6">

--- a/ETF_Allocation_Model.xlsx
+++ b/ETF_Allocation_Model.xlsx
@@ -502,7 +502,7 @@
         <v>183.3</v>
       </c>
       <c r="G2" t="n">
-        <v>78.40000000000001</v>
+        <v>79.3</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -510,7 +510,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>16.17</v>
+        <v>16.18</v>
       </c>
       <c r="J2" t="n">
         <v>-19.17</v>
@@ -549,7 +549,7 @@
         <v>183.3</v>
       </c>
       <c r="G3" t="n">
-        <v>76.90000000000001</v>
+        <v>77</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -596,7 +596,7 @@
         <v>183.3</v>
       </c>
       <c r="G4" t="n">
-        <v>75.8</v>
+        <v>76</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>13.2</v>
+        <v>13.19</v>
       </c>
       <c r="J4" t="n">
         <v>-21.63</v>
@@ -690,7 +690,7 @@
         <v>66.7</v>
       </c>
       <c r="G6" t="n">
-        <v>54.5</v>
+        <v>54.4</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -698,7 +698,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>18.06</v>
+        <v>18.07</v>
       </c>
       <c r="J6" t="n">
         <v>-21.9</v>
@@ -780,22 +780,22 @@
         <v>75</v>
       </c>
       <c r="G8" t="n">
-        <v>79.09999999999999</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Accumulate Carefully</t>
+          <t>Buy Watchlist</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>13.77</v>
+        <v>13.78</v>
       </c>
       <c r="J8" t="n">
         <v>-17.8</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>ETF interessante ma ingresso non ideale: meglio attendere pullback o conferma.</t>
+          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
         <v>75</v>
       </c>
       <c r="G9" t="n">
-        <v>73.5</v>
+        <v>73.8</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>12.89</v>
+        <v>12.88</v>
       </c>
       <c r="J9" t="n">
         <v>-20.6</v>
@@ -874,15 +874,15 @@
         <v>33.3</v>
       </c>
       <c r="G10" t="n">
-        <v>67.3</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Hold / Monitor</t>
+          <t>Accumulate Carefully</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>21.54</v>
+        <v>21.56</v>
       </c>
       <c r="J10" t="n">
         <v>-29.37</v>
@@ -921,7 +921,7 @@
         <v>33.3</v>
       </c>
       <c r="G11" t="n">
-        <v>64</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -932,7 +932,7 @@
         <v>23.42</v>
       </c>
       <c r="J11" t="n">
-        <v>-43.51</v>
+        <v>-43.46</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -968,7 +968,7 @@
         <v>33.3</v>
       </c>
       <c r="G12" t="n">
-        <v>63.2</v>
+        <v>62.9</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -976,7 +976,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>35.35</v>
+        <v>35.33</v>
       </c>
       <c r="J12" t="n">
         <v>-35.74</v>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>65.7</v>
+        <v>65.98999999999999</v>
       </c>
     </row>
     <row r="6">

--- a/ETF_Allocation_Model.xlsx
+++ b/ETF_Allocation_Model.xlsx
@@ -502,7 +502,7 @@
         <v>183.3</v>
       </c>
       <c r="G2" t="n">
-        <v>79.3</v>
+        <v>78.8</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -549,7 +549,7 @@
         <v>183.3</v>
       </c>
       <c r="G3" t="n">
-        <v>77</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>12.94</v>
+        <v>12.93</v>
       </c>
       <c r="J3" t="n">
         <v>-21.07</v>
@@ -643,7 +643,7 @@
         <v>66.7</v>
       </c>
       <c r="G5" t="n">
-        <v>68.59999999999999</v>
+        <v>68.5</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>9.56</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="J5" t="n">
         <v>-12.85</v>
@@ -690,15 +690,15 @@
         <v>66.7</v>
       </c>
       <c r="G6" t="n">
-        <v>54.4</v>
+        <v>55.2</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Avoid for Now</t>
+          <t>Hold / Monitor</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>18.07</v>
+        <v>18.06</v>
       </c>
       <c r="J6" t="n">
         <v>-21.9</v>
@@ -780,7 +780,7 @@
         <v>75</v>
       </c>
       <c r="G8" t="n">
-        <v>79.90000000000001</v>
+        <v>80.2</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>13.78</v>
+        <v>13.77</v>
       </c>
       <c r="J8" t="n">
         <v>-17.8</v>
@@ -827,7 +827,7 @@
         <v>75</v>
       </c>
       <c r="G9" t="n">
-        <v>73.8</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -874,7 +874,7 @@
         <v>33.3</v>
       </c>
       <c r="G10" t="n">
-        <v>68.59999999999999</v>
+        <v>68.5</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>21.56</v>
+        <v>21.55</v>
       </c>
       <c r="J10" t="n">
         <v>-29.37</v>
@@ -921,7 +921,7 @@
         <v>33.3</v>
       </c>
       <c r="G11" t="n">
-        <v>64.40000000000001</v>
+        <v>63.6</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -968,7 +968,7 @@
         <v>33.3</v>
       </c>
       <c r="G12" t="n">
-        <v>62.9</v>
+        <v>59.9</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -976,7 +976,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>35.33</v>
+        <v>35.45</v>
       </c>
       <c r="J12" t="n">
         <v>-35.74</v>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>65.98999999999999</v>
+        <v>65.75</v>
       </c>
     </row>
     <row r="6">

--- a/ETF_Allocation_Model.xlsx
+++ b/ETF_Allocation_Model.xlsx
@@ -502,7 +502,7 @@
         <v>183.3</v>
       </c>
       <c r="G2" t="n">
-        <v>78.8</v>
+        <v>78</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -510,7 +510,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>16.18</v>
+        <v>16.21</v>
       </c>
       <c r="J2" t="n">
         <v>-19.17</v>
@@ -549,7 +549,7 @@
         <v>183.3</v>
       </c>
       <c r="G3" t="n">
-        <v>77.09999999999999</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>12.93</v>
+        <v>12.92</v>
       </c>
       <c r="J3" t="n">
         <v>-21.07</v>
@@ -596,7 +596,7 @@
         <v>183.3</v>
       </c>
       <c r="G4" t="n">
-        <v>76</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>13.19</v>
+        <v>13.18</v>
       </c>
       <c r="J4" t="n">
         <v>-21.63</v>
@@ -643,7 +643,7 @@
         <v>66.7</v>
       </c>
       <c r="G5" t="n">
-        <v>68.5</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -690,15 +690,15 @@
         <v>66.7</v>
       </c>
       <c r="G6" t="n">
-        <v>55.2</v>
+        <v>54.2</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Hold / Monitor</t>
+          <t>Avoid for Now</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>18.06</v>
+        <v>18.09</v>
       </c>
       <c r="J6" t="n">
         <v>-21.9</v>
@@ -780,7 +780,7 @@
         <v>75</v>
       </c>
       <c r="G8" t="n">
-        <v>80.2</v>
+        <v>80</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -827,7 +827,7 @@
         <v>75</v>
       </c>
       <c r="G9" t="n">
-        <v>73.90000000000001</v>
+        <v>74.3</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>12.88</v>
+        <v>12.87</v>
       </c>
       <c r="J9" t="n">
         <v>-20.6</v>
@@ -874,15 +874,15 @@
         <v>33.3</v>
       </c>
       <c r="G10" t="n">
-        <v>68.5</v>
+        <v>67.8</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Accumulate Carefully</t>
+          <t>Hold / Monitor</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>21.55</v>
+        <v>21.56</v>
       </c>
       <c r="J10" t="n">
         <v>-29.37</v>
@@ -921,7 +921,7 @@
         <v>33.3</v>
       </c>
       <c r="G11" t="n">
-        <v>63.6</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>65.75</v>
+        <v>65.7</v>
       </c>
     </row>
     <row r="6">

--- a/ETF_Allocation_Model.xlsx
+++ b/ETF_Allocation_Model.xlsx
@@ -502,7 +502,7 @@
         <v>183.3</v>
       </c>
       <c r="G2" t="n">
-        <v>78</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -549,22 +549,22 @@
         <v>183.3</v>
       </c>
       <c r="G3" t="n">
-        <v>77.59999999999999</v>
+        <v>78.8</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Accumulate Carefully</t>
+          <t>Buy Watchlist</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>12.92</v>
+        <v>12.93</v>
       </c>
       <c r="J3" t="n">
         <v>-21.07</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
+          <t>ETF forte e in trend favorevole; valutare solo con coerenza di portafoglio.</t>
         </is>
       </c>
     </row>
@@ -596,7 +596,7 @@
         <v>183.3</v>
       </c>
       <c r="G4" t="n">
-        <v>76.59999999999999</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>13.18</v>
+        <v>13.19</v>
       </c>
       <c r="J4" t="n">
         <v>-21.63</v>
@@ -643,7 +643,7 @@
         <v>66.7</v>
       </c>
       <c r="G5" t="n">
-        <v>68.40000000000001</v>
+        <v>69</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>9.550000000000001</v>
+        <v>9.56</v>
       </c>
       <c r="J5" t="n">
         <v>-12.85</v>
@@ -690,7 +690,7 @@
         <v>66.7</v>
       </c>
       <c r="G6" t="n">
-        <v>54.2</v>
+        <v>54.8</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -698,7 +698,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>18.09</v>
+        <v>18.12</v>
       </c>
       <c r="J6" t="n">
         <v>-21.9</v>
@@ -780,7 +780,7 @@
         <v>75</v>
       </c>
       <c r="G8" t="n">
-        <v>80</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>13.77</v>
+        <v>13.76</v>
       </c>
       <c r="J8" t="n">
         <v>-17.8</v>
@@ -827,7 +827,7 @@
         <v>75</v>
       </c>
       <c r="G9" t="n">
-        <v>74.3</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>12.87</v>
+        <v>12.88</v>
       </c>
       <c r="J9" t="n">
         <v>-20.6</v>
@@ -874,7 +874,7 @@
         <v>33.3</v>
       </c>
       <c r="G10" t="n">
-        <v>67.8</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>21.56</v>
+        <v>21.57</v>
       </c>
       <c r="J10" t="n">
         <v>-29.37</v>
@@ -921,7 +921,7 @@
         <v>33.3</v>
       </c>
       <c r="G11" t="n">
-        <v>64.40000000000001</v>
+        <v>64.8</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>23.42</v>
+        <v>23.44</v>
       </c>
       <c r="J11" t="n">
-        <v>-43.46</v>
+        <v>-43.36</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -976,7 +976,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>35.45</v>
+        <v>35.46</v>
       </c>
       <c r="J12" t="n">
         <v>-35.74</v>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>65.7</v>
+        <v>66.37</v>
       </c>
     </row>
     <row r="6">

--- a/ETF_Allocation_Model.xlsx
+++ b/ETF_Allocation_Model.xlsx
@@ -477,12 +477,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>EIMI.MI</t>
+          <t>VWCE.DE</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>iShares Core MSCI EM IMI UCITS ETF USD (Acc)</t>
+          <t>Vanguard FTSE All-World UCITS ETF USD Accumulation</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -492,7 +492,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Mercati emergenti</t>
+          <t>Azionario globale</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -502,7 +502,7 @@
         <v>183.3</v>
       </c>
       <c r="G2" t="n">
-        <v>78.90000000000001</v>
+        <v>79.5</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -510,10 +510,10 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>16.21</v>
+        <v>12.93</v>
       </c>
       <c r="J2" t="n">
-        <v>-19.17</v>
+        <v>-21.07</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -524,12 +524,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>VWCE.DE</t>
+          <t>EIMI.MI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Vanguard FTSE All-World UCITS ETF USD Accumulation</t>
+          <t>iShares Core MSCI EM IMI UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -539,7 +539,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Azionario globale</t>
+          <t>Mercati emergenti</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -549,7 +549,7 @@
         <v>183.3</v>
       </c>
       <c r="G3" t="n">
-        <v>78.8</v>
+        <v>78.3</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -557,10 +557,10 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>12.93</v>
+        <v>16.23</v>
       </c>
       <c r="J3" t="n">
-        <v>-21.07</v>
+        <v>-19.17</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -596,11 +596,11 @@
         <v>183.3</v>
       </c>
       <c r="G4" t="n">
-        <v>77.59999999999999</v>
+        <v>78.2</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Accumulate Carefully</t>
+          <t>Buy Watchlist</t>
         </is>
       </c>
       <c r="I4" t="n">
@@ -611,7 +611,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
+          <t>ETF forte e in trend favorevole; valutare solo con coerenza di portafoglio.</t>
         </is>
       </c>
     </row>
@@ -643,7 +643,7 @@
         <v>66.7</v>
       </c>
       <c r="G5" t="n">
-        <v>69</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -690,11 +690,11 @@
         <v>66.7</v>
       </c>
       <c r="G6" t="n">
-        <v>54.8</v>
+        <v>55.8</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Avoid for Now</t>
+          <t>Hold / Monitor</t>
         </is>
       </c>
       <c r="I6" t="n">
@@ -780,22 +780,22 @@
         <v>75</v>
       </c>
       <c r="G8" t="n">
-        <v>80.40000000000001</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Buy Watchlist</t>
+          <t>Accumulate Carefully</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>13.76</v>
+        <v>13.78</v>
       </c>
       <c r="J8" t="n">
         <v>-17.8</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
+          <t>ETF interessante ma ingresso non ideale: meglio attendere pullback o conferma.</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
         <v>75</v>
       </c>
       <c r="G9" t="n">
-        <v>75.09999999999999</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -874,7 +874,7 @@
         <v>33.3</v>
       </c>
       <c r="G10" t="n">
-        <v>67.90000000000001</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -896,12 +896,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>INRG.MI</t>
+          <t>SMH</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>iShares Global Clean Energy Transition UCITS ETF USD (Dist)</t>
+          <t>VanEck Semiconductor ETF</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -911,7 +911,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Energia pulita</t>
+          <t>Semiconduttori</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>23.44</v>
+        <v>35.7</v>
       </c>
       <c r="J11" t="n">
-        <v>-43.36</v>
+        <v>-35.74</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -943,12 +943,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SMH</t>
+          <t>INRG.MI</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>VanEck Semiconductor ETF</t>
+          <t>iShares Global Clean Energy Transition UCITS ETF USD (Dist)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -958,7 +958,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Semiconduttori</t>
+          <t>Energia pulita</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -968,7 +968,7 @@
         <v>33.3</v>
       </c>
       <c r="G12" t="n">
-        <v>59.9</v>
+        <v>64.8</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>35.46</v>
+        <v>23.45</v>
       </c>
       <c r="J12" t="n">
-        <v>-35.74</v>
+        <v>-43.36</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>66.37</v>
+        <v>66.68000000000001</v>
       </c>
     </row>
     <row r="6">

--- a/ETF_Allocation_Model.xlsx
+++ b/ETF_Allocation_Model.xlsx
@@ -477,12 +477,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>VWCE.DE</t>
+          <t>EIMI.MI</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Vanguard FTSE All-World UCITS ETF USD Accumulation</t>
+          <t>iShares Core MSCI EM IMI UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -492,7 +492,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Azionario globale</t>
+          <t>Mercati emergenti</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -502,7 +502,7 @@
         <v>183.3</v>
       </c>
       <c r="G2" t="n">
-        <v>79.5</v>
+        <v>80.7</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -510,10 +510,10 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>12.93</v>
+        <v>16.44</v>
       </c>
       <c r="J2" t="n">
-        <v>-21.07</v>
+        <v>-19.17</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -524,12 +524,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>EIMI.MI</t>
+          <t>VWCE.DE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>iShares Core MSCI EM IMI UCITS ETF USD (Acc)</t>
+          <t>Vanguard FTSE All-World UCITS ETF USD Accumulation</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -539,7 +539,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Mercati emergenti</t>
+          <t>Azionario globale</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -549,7 +549,7 @@
         <v>183.3</v>
       </c>
       <c r="G3" t="n">
-        <v>78.3</v>
+        <v>78.8</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -557,10 +557,10 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>16.23</v>
+        <v>12.95</v>
       </c>
       <c r="J3" t="n">
-        <v>-19.17</v>
+        <v>-21.07</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -596,22 +596,22 @@
         <v>183.3</v>
       </c>
       <c r="G4" t="n">
-        <v>78.2</v>
+        <v>77.5</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Buy Watchlist</t>
+          <t>Accumulate Carefully</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>13.19</v>
+        <v>13.2</v>
       </c>
       <c r="J4" t="n">
         <v>-21.63</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>ETF forte e in trend favorevole; valutare solo con coerenza di portafoglio.</t>
+          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
         </is>
       </c>
     </row>
@@ -643,7 +643,7 @@
         <v>66.7</v>
       </c>
       <c r="G5" t="n">
-        <v>69.40000000000001</v>
+        <v>70.2</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -690,7 +690,7 @@
         <v>66.7</v>
       </c>
       <c r="G6" t="n">
-        <v>55.8</v>
+        <v>56.7</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -698,7 +698,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>18.12</v>
+        <v>18.13</v>
       </c>
       <c r="J6" t="n">
         <v>-21.9</v>
@@ -780,22 +780,22 @@
         <v>75</v>
       </c>
       <c r="G8" t="n">
-        <v>80.09999999999999</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Accumulate Carefully</t>
+          <t>Buy Watchlist</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>13.78</v>
+        <v>13.83</v>
       </c>
       <c r="J8" t="n">
         <v>-17.8</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>ETF interessante ma ingresso non ideale: meglio attendere pullback o conferma.</t>
+          <t>ETF forte e in trend favorevole; valutare solo con coerenza di portafoglio.</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
         <v>75</v>
       </c>
       <c r="G9" t="n">
-        <v>75.59999999999999</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -874,15 +874,15 @@
         <v>33.3</v>
       </c>
       <c r="G10" t="n">
-        <v>67.59999999999999</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Hold / Monitor</t>
+          <t>Accumulate Carefully</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>21.57</v>
+        <v>21.69</v>
       </c>
       <c r="J10" t="n">
         <v>-29.37</v>
@@ -921,7 +921,7 @@
         <v>33.3</v>
       </c>
       <c r="G11" t="n">
-        <v>64.8</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>35.7</v>
+        <v>35.68</v>
       </c>
       <c r="J11" t="n">
         <v>-35.74</v>
@@ -976,7 +976,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>23.45</v>
+        <v>23.52</v>
       </c>
       <c r="J12" t="n">
         <v>-43.36</v>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>66.68000000000001</v>
+        <v>67.39</v>
       </c>
     </row>
     <row r="6">

--- a/ETF_Allocation_Model.xlsx
+++ b/ETF_Allocation_Model.xlsx
@@ -510,7 +510,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>16.44</v>
+        <v>16.42</v>
       </c>
       <c r="J2" t="n">
         <v>-19.17</v>
@@ -549,7 +549,7 @@
         <v>183.3</v>
       </c>
       <c r="G3" t="n">
-        <v>78.8</v>
+        <v>78.3</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>12.95</v>
+        <v>12.94</v>
       </c>
       <c r="J3" t="n">
         <v>-21.07</v>
@@ -596,7 +596,7 @@
         <v>183.3</v>
       </c>
       <c r="G4" t="n">
-        <v>77.5</v>
+        <v>77.2</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>13.2</v>
+        <v>13.19</v>
       </c>
       <c r="J4" t="n">
         <v>-21.63</v>
@@ -643,7 +643,7 @@
         <v>66.7</v>
       </c>
       <c r="G5" t="n">
-        <v>70.2</v>
+        <v>70.5</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>9.56</v>
+        <v>9.57</v>
       </c>
       <c r="J5" t="n">
         <v>-12.85</v>
@@ -690,18 +690,18 @@
         <v>66.7</v>
       </c>
       <c r="G6" t="n">
-        <v>56.7</v>
+        <v>52.8</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Hold / Monitor</t>
+          <t>Avoid for Now</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>18.13</v>
+        <v>18.18</v>
       </c>
       <c r="J6" t="n">
-        <v>-21.9</v>
+        <v>-22.17</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>75</v>
       </c>
       <c r="G8" t="n">
-        <v>81.40000000000001</v>
+        <v>81</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>13.83</v>
+        <v>13.87</v>
       </c>
       <c r="J8" t="n">
         <v>-17.8</v>
@@ -874,7 +874,7 @@
         <v>33.3</v>
       </c>
       <c r="G10" t="n">
-        <v>70.09999999999999</v>
+        <v>70.2</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>21.69</v>
+        <v>21.66</v>
       </c>
       <c r="J10" t="n">
         <v>-29.37</v>
@@ -921,7 +921,7 @@
         <v>33.3</v>
       </c>
       <c r="G11" t="n">
-        <v>65.59999999999999</v>
+        <v>64.3</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>35.68</v>
+        <v>35.69</v>
       </c>
       <c r="J11" t="n">
         <v>-35.74</v>
@@ -968,7 +968,7 @@
         <v>33.3</v>
       </c>
       <c r="G12" t="n">
-        <v>64.8</v>
+        <v>59.2</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -976,7 +976,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>23.52</v>
+        <v>23.56</v>
       </c>
       <c r="J12" t="n">
         <v>-43.36</v>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>67.39</v>
+        <v>66.56999999999999</v>
       </c>
     </row>
     <row r="6">

--- a/ETF_Allocation_Model.xlsx
+++ b/ETF_Allocation_Model.xlsx
@@ -510,7 +510,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>16.42</v>
+        <v>16.43</v>
       </c>
       <c r="J2" t="n">
         <v>-19.17</v>
@@ -549,7 +549,7 @@
         <v>183.3</v>
       </c>
       <c r="G3" t="n">
-        <v>78.3</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>12.94</v>
+        <v>12.93</v>
       </c>
       <c r="J3" t="n">
         <v>-21.07</v>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>13.19</v>
+        <v>13.18</v>
       </c>
       <c r="J4" t="n">
         <v>-21.63</v>
@@ -643,7 +643,7 @@
         <v>66.7</v>
       </c>
       <c r="G5" t="n">
-        <v>70.5</v>
+        <v>70.8</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>9.57</v>
+        <v>9.56</v>
       </c>
       <c r="J5" t="n">
         <v>-12.85</v>
@@ -690,11 +690,11 @@
         <v>66.7</v>
       </c>
       <c r="G6" t="n">
-        <v>52.8</v>
+        <v>55.2</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Avoid for Now</t>
+          <t>Hold / Monitor</t>
         </is>
       </c>
       <c r="I6" t="n">
@@ -780,7 +780,7 @@
         <v>75</v>
       </c>
       <c r="G8" t="n">
-        <v>81</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -827,7 +827,7 @@
         <v>75</v>
       </c>
       <c r="G9" t="n">
-        <v>74.90000000000001</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>12.88</v>
+        <v>12.87</v>
       </c>
       <c r="J9" t="n">
         <v>-20.6</v>
@@ -874,7 +874,7 @@
         <v>33.3</v>
       </c>
       <c r="G10" t="n">
-        <v>70.2</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>21.66</v>
+        <v>21.67</v>
       </c>
       <c r="J10" t="n">
         <v>-29.37</v>
@@ -921,7 +921,7 @@
         <v>33.3</v>
       </c>
       <c r="G11" t="n">
-        <v>64.3</v>
+        <v>66.8</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>35.69</v>
+        <v>35.73</v>
       </c>
       <c r="J11" t="n">
         <v>-35.74</v>
@@ -968,7 +968,7 @@
         <v>33.3</v>
       </c>
       <c r="G12" t="n">
-        <v>59.2</v>
+        <v>57.9</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -976,7 +976,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>23.56</v>
+        <v>23.58</v>
       </c>
       <c r="J12" t="n">
         <v>-43.36</v>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>66.56999999999999</v>
+        <v>67.06</v>
       </c>
     </row>
     <row r="6">

--- a/ETF_Allocation_Model.xlsx
+++ b/ETF_Allocation_Model.xlsx
@@ -502,7 +502,7 @@
         <v>183.3</v>
       </c>
       <c r="G2" t="n">
-        <v>80.7</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -510,7 +510,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>16.43</v>
+        <v>16.46</v>
       </c>
       <c r="J2" t="n">
         <v>-19.17</v>
@@ -549,7 +549,7 @@
         <v>183.3</v>
       </c>
       <c r="G3" t="n">
-        <v>78.40000000000001</v>
+        <v>78.7</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>12.93</v>
+        <v>12.94</v>
       </c>
       <c r="J3" t="n">
         <v>-21.07</v>
@@ -596,7 +596,7 @@
         <v>183.3</v>
       </c>
       <c r="G4" t="n">
-        <v>77.2</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>13.18</v>
+        <v>13.19</v>
       </c>
       <c r="J4" t="n">
         <v>-21.63</v>
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>9.56</v>
+        <v>9.57</v>
       </c>
       <c r="J5" t="n">
         <v>-12.85</v>
@@ -690,18 +690,18 @@
         <v>66.7</v>
       </c>
       <c r="G6" t="n">
-        <v>55.2</v>
+        <v>52.6</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Hold / Monitor</t>
+          <t>Avoid for Now</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>18.18</v>
+        <v>18.22</v>
       </c>
       <c r="J6" t="n">
-        <v>-22.17</v>
+        <v>-22.39</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>75</v>
       </c>
       <c r="G8" t="n">
-        <v>81.59999999999999</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>13.87</v>
+        <v>13.93</v>
       </c>
       <c r="J8" t="n">
         <v>-17.8</v>
@@ -827,7 +827,7 @@
         <v>75</v>
       </c>
       <c r="G9" t="n">
-        <v>75.09999999999999</v>
+        <v>76</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>12.87</v>
+        <v>12.88</v>
       </c>
       <c r="J9" t="n">
         <v>-20.6</v>
@@ -874,7 +874,7 @@
         <v>33.3</v>
       </c>
       <c r="G10" t="n">
-        <v>71.40000000000001</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>21.67</v>
+        <v>21.68</v>
       </c>
       <c r="J10" t="n">
         <v>-29.37</v>
@@ -921,7 +921,7 @@
         <v>33.3</v>
       </c>
       <c r="G11" t="n">
-        <v>66.8</v>
+        <v>65.2</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>35.73</v>
+        <v>35.81</v>
       </c>
       <c r="J11" t="n">
         <v>-35.74</v>
@@ -968,7 +968,7 @@
         <v>33.3</v>
       </c>
       <c r="G12" t="n">
-        <v>57.9</v>
+        <v>57.1</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -976,7 +976,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>23.58</v>
+        <v>23.59</v>
       </c>
       <c r="J12" t="n">
         <v>-43.36</v>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>67.06</v>
+        <v>67.44</v>
       </c>
     </row>
     <row r="6">

--- a/ETF_Allocation_Model.xlsx
+++ b/ETF_Allocation_Model.xlsx
@@ -502,7 +502,7 @@
         <v>183.3</v>
       </c>
       <c r="G2" t="n">
-        <v>80.59999999999999</v>
+        <v>80.8</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -510,7 +510,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>16.46</v>
+        <v>16.5</v>
       </c>
       <c r="J2" t="n">
         <v>-19.17</v>
@@ -549,7 +549,7 @@
         <v>183.3</v>
       </c>
       <c r="G3" t="n">
-        <v>78.7</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>12.94</v>
+        <v>12.95</v>
       </c>
       <c r="J3" t="n">
         <v>-21.07</v>
@@ -596,7 +596,7 @@
         <v>183.3</v>
       </c>
       <c r="G4" t="n">
-        <v>77.59999999999999</v>
+        <v>78</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -643,7 +643,7 @@
         <v>66.7</v>
       </c>
       <c r="G5" t="n">
-        <v>70.8</v>
+        <v>70.3</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -690,7 +690,7 @@
         <v>66.7</v>
       </c>
       <c r="G6" t="n">
-        <v>52.6</v>
+        <v>52.5</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>75</v>
       </c>
       <c r="G8" t="n">
-        <v>82.59999999999999</v>
+        <v>82.2</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>13.93</v>
+        <v>13.94</v>
       </c>
       <c r="J8" t="n">
         <v>-17.8</v>
@@ -827,7 +827,7 @@
         <v>75</v>
       </c>
       <c r="G9" t="n">
-        <v>76</v>
+        <v>76.3</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -874,7 +874,7 @@
         <v>33.3</v>
       </c>
       <c r="G10" t="n">
-        <v>70.90000000000001</v>
+        <v>69</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>21.68</v>
+        <v>21.78</v>
       </c>
       <c r="J10" t="n">
         <v>-29.37</v>
@@ -921,7 +921,7 @@
         <v>33.3</v>
       </c>
       <c r="G11" t="n">
-        <v>65.2</v>
+        <v>63.3</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>35.81</v>
+        <v>35.87</v>
       </c>
       <c r="J11" t="n">
         <v>-35.74</v>
@@ -968,7 +968,7 @@
         <v>33.3</v>
       </c>
       <c r="G12" t="n">
-        <v>57.1</v>
+        <v>60.4</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -976,7 +976,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>23.59</v>
+        <v>23.7</v>
       </c>
       <c r="J12" t="n">
         <v>-43.36</v>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>67.44</v>
+        <v>67.43000000000001</v>
       </c>
     </row>
     <row r="6">

--- a/ETF_Allocation_Model.xlsx
+++ b/ETF_Allocation_Model.xlsx
@@ -502,7 +502,7 @@
         <v>183.3</v>
       </c>
       <c r="G2" t="n">
-        <v>80.8</v>
+        <v>80.5</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -549,7 +549,7 @@
         <v>183.3</v>
       </c>
       <c r="G3" t="n">
-        <v>79.09999999999999</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -596,11 +596,11 @@
         <v>183.3</v>
       </c>
       <c r="G4" t="n">
-        <v>78</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Accumulate Carefully</t>
+          <t>Buy Watchlist</t>
         </is>
       </c>
       <c r="I4" t="n">
@@ -611,7 +611,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
+          <t>ETF forte e in trend favorevole; valutare solo con coerenza di portafoglio.</t>
         </is>
       </c>
     </row>
@@ -643,7 +643,7 @@
         <v>66.7</v>
       </c>
       <c r="G5" t="n">
-        <v>70.3</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>9.57</v>
+        <v>9.58</v>
       </c>
       <c r="J5" t="n">
         <v>-12.85</v>
@@ -690,7 +690,7 @@
         <v>66.7</v>
       </c>
       <c r="G6" t="n">
-        <v>52.5</v>
+        <v>54</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -698,7 +698,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>18.22</v>
+        <v>18.24</v>
       </c>
       <c r="J6" t="n">
         <v>-22.39</v>
@@ -780,7 +780,7 @@
         <v>75</v>
       </c>
       <c r="G8" t="n">
-        <v>82.2</v>
+        <v>82.7</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -827,7 +827,7 @@
         <v>75</v>
       </c>
       <c r="G9" t="n">
-        <v>76.3</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>12.88</v>
+        <v>12.89</v>
       </c>
       <c r="J9" t="n">
         <v>-20.6</v>
@@ -874,7 +874,7 @@
         <v>33.3</v>
       </c>
       <c r="G10" t="n">
-        <v>69</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -921,7 +921,7 @@
         <v>33.3</v>
       </c>
       <c r="G11" t="n">
-        <v>63.3</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>35.87</v>
+        <v>35.99</v>
       </c>
       <c r="J11" t="n">
         <v>-35.74</v>
@@ -968,7 +968,7 @@
         <v>33.3</v>
       </c>
       <c r="G12" t="n">
-        <v>60.4</v>
+        <v>60.8</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -976,7 +976,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>23.7</v>
+        <v>23.71</v>
       </c>
       <c r="J12" t="n">
         <v>-43.36</v>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>67.43000000000001</v>
+        <v>67.98999999999999</v>
       </c>
     </row>
     <row r="6">

--- a/ETF_Allocation_Model.xlsx
+++ b/ETF_Allocation_Model.xlsx
@@ -502,7 +502,7 @@
         <v>183.3</v>
       </c>
       <c r="G2" t="n">
-        <v>80.5</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -510,7 +510,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>16.5</v>
+        <v>16.54</v>
       </c>
       <c r="J2" t="n">
         <v>-19.17</v>
@@ -549,7 +549,7 @@
         <v>183.3</v>
       </c>
       <c r="G3" t="n">
-        <v>79.40000000000001</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -596,11 +596,11 @@
         <v>183.3</v>
       </c>
       <c r="G4" t="n">
-        <v>78.40000000000001</v>
+        <v>77.2</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Buy Watchlist</t>
+          <t>Accumulate Carefully</t>
         </is>
       </c>
       <c r="I4" t="n">
@@ -611,7 +611,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>ETF forte e in trend favorevole; valutare solo con coerenza di portafoglio.</t>
+          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
         </is>
       </c>
     </row>
@@ -643,7 +643,7 @@
         <v>66.7</v>
       </c>
       <c r="G5" t="n">
-        <v>70.90000000000001</v>
+        <v>71.3</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -690,7 +690,7 @@
         <v>66.7</v>
       </c>
       <c r="G6" t="n">
-        <v>54</v>
+        <v>53.7</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -698,7 +698,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>18.24</v>
+        <v>18.23</v>
       </c>
       <c r="J6" t="n">
         <v>-22.39</v>
@@ -780,7 +780,7 @@
         <v>75</v>
       </c>
       <c r="G8" t="n">
-        <v>82.7</v>
+        <v>83.3</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>13.94</v>
+        <v>13.95</v>
       </c>
       <c r="J8" t="n">
         <v>-17.8</v>
@@ -827,7 +827,7 @@
         <v>75</v>
       </c>
       <c r="G9" t="n">
-        <v>76.40000000000001</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>12.89</v>
+        <v>12.88</v>
       </c>
       <c r="J9" t="n">
         <v>-20.6</v>
@@ -874,7 +874,7 @@
         <v>33.3</v>
       </c>
       <c r="G10" t="n">
-        <v>69.40000000000001</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>21.78</v>
+        <v>21.85</v>
       </c>
       <c r="J10" t="n">
         <v>-29.37</v>
@@ -921,15 +921,15 @@
         <v>33.3</v>
       </c>
       <c r="G11" t="n">
-        <v>66.90000000000001</v>
+        <v>68.7</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Hold / Monitor</t>
+          <t>Accumulate Carefully</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>35.99</v>
+        <v>36.08</v>
       </c>
       <c r="J11" t="n">
         <v>-35.74</v>
@@ -968,7 +968,7 @@
         <v>33.3</v>
       </c>
       <c r="G12" t="n">
-        <v>60.8</v>
+        <v>57.6</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -976,7 +976,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>23.71</v>
+        <v>23.82</v>
       </c>
       <c r="J12" t="n">
         <v>-43.36</v>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>67.98999999999999</v>
+        <v>67.63</v>
       </c>
     </row>
     <row r="6">

--- a/ETF_Allocation_Model.xlsx
+++ b/ETF_Allocation_Model.xlsx
@@ -502,7 +502,7 @@
         <v>183.3</v>
       </c>
       <c r="G2" t="n">
-        <v>79.59999999999999</v>
+        <v>80.5</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -510,7 +510,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>16.54</v>
+        <v>16.57</v>
       </c>
       <c r="J2" t="n">
         <v>-19.17</v>
@@ -549,7 +549,7 @@
         <v>183.3</v>
       </c>
       <c r="G3" t="n">
-        <v>78.09999999999999</v>
+        <v>78.5</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>12.95</v>
+        <v>12.94</v>
       </c>
       <c r="J3" t="n">
         <v>-21.07</v>
@@ -596,7 +596,7 @@
         <v>183.3</v>
       </c>
       <c r="G4" t="n">
-        <v>77.2</v>
+        <v>77.5</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>13.19</v>
+        <v>13.18</v>
       </c>
       <c r="J4" t="n">
         <v>-21.63</v>
@@ -643,7 +643,7 @@
         <v>66.7</v>
       </c>
       <c r="G5" t="n">
-        <v>71.3</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>9.58</v>
+        <v>9.57</v>
       </c>
       <c r="J5" t="n">
         <v>-12.85</v>
@@ -690,11 +690,11 @@
         <v>66.7</v>
       </c>
       <c r="G6" t="n">
-        <v>53.7</v>
+        <v>55.1</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Avoid for Now</t>
+          <t>Hold / Monitor</t>
         </is>
       </c>
       <c r="I6" t="n">
@@ -780,7 +780,7 @@
         <v>75</v>
       </c>
       <c r="G8" t="n">
-        <v>83.3</v>
+        <v>83.2</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -827,7 +827,7 @@
         <v>75</v>
       </c>
       <c r="G9" t="n">
-        <v>75.59999999999999</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -874,7 +874,7 @@
         <v>33.3</v>
       </c>
       <c r="G10" t="n">
-        <v>71.40000000000001</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>21.85</v>
+        <v>21.84</v>
       </c>
       <c r="J10" t="n">
         <v>-29.37</v>
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>36.08</v>
+        <v>36.07</v>
       </c>
       <c r="J11" t="n">
         <v>-35.74</v>
@@ -968,7 +968,7 @@
         <v>33.3</v>
       </c>
       <c r="G12" t="n">
-        <v>57.6</v>
+        <v>57.7</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -976,7 +976,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>23.82</v>
+        <v>23.8</v>
       </c>
       <c r="J12" t="n">
         <v>-43.36</v>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>67.63</v>
+        <v>67.89</v>
       </c>
     </row>
     <row r="6">

--- a/ETF_Allocation_Model.xlsx
+++ b/ETF_Allocation_Model.xlsx
@@ -502,7 +502,7 @@
         <v>183.3</v>
       </c>
       <c r="G2" t="n">
-        <v>80.5</v>
+        <v>80.8</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -510,7 +510,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>16.57</v>
+        <v>16.53</v>
       </c>
       <c r="J2" t="n">
         <v>-19.17</v>
@@ -549,7 +549,7 @@
         <v>183.3</v>
       </c>
       <c r="G3" t="n">
-        <v>78.5</v>
+        <v>79</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>12.94</v>
+        <v>12.92</v>
       </c>
       <c r="J3" t="n">
         <v>-21.07</v>
@@ -596,22 +596,22 @@
         <v>183.3</v>
       </c>
       <c r="G4" t="n">
-        <v>77.5</v>
+        <v>78.2</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Accumulate Carefully</t>
+          <t>Buy Watchlist</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>13.18</v>
+        <v>13.17</v>
       </c>
       <c r="J4" t="n">
         <v>-21.63</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
+          <t>ETF forte e in trend favorevole; valutare solo con coerenza di portafoglio.</t>
         </is>
       </c>
     </row>
@@ -643,7 +643,7 @@
         <v>66.7</v>
       </c>
       <c r="G5" t="n">
-        <v>71.09999999999999</v>
+        <v>71.5</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -690,15 +690,15 @@
         <v>66.7</v>
       </c>
       <c r="G6" t="n">
-        <v>55.1</v>
+        <v>54.8</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Hold / Monitor</t>
+          <t>Avoid for Now</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>18.23</v>
+        <v>18.25</v>
       </c>
       <c r="J6" t="n">
         <v>-22.39</v>
@@ -780,7 +780,7 @@
         <v>75</v>
       </c>
       <c r="G8" t="n">
-        <v>83.2</v>
+        <v>83.8</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>13.95</v>
+        <v>13.91</v>
       </c>
       <c r="J8" t="n">
         <v>-17.8</v>
@@ -827,7 +827,7 @@
         <v>75</v>
       </c>
       <c r="G9" t="n">
-        <v>75.90000000000001</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>12.88</v>
+        <v>12.86</v>
       </c>
       <c r="J9" t="n">
         <v>-20.6</v>
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>21.84</v>
+        <v>21.83</v>
       </c>
       <c r="J10" t="n">
         <v>-29.37</v>
@@ -921,7 +921,7 @@
         <v>33.3</v>
       </c>
       <c r="G11" t="n">
-        <v>68.7</v>
+        <v>69</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>36.07</v>
+        <v>36.11</v>
       </c>
       <c r="J11" t="n">
         <v>-35.74</v>
@@ -968,7 +968,7 @@
         <v>33.3</v>
       </c>
       <c r="G12" t="n">
-        <v>57.7</v>
+        <v>60.4</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -976,7 +976,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>23.8</v>
+        <v>23.79</v>
       </c>
       <c r="J12" t="n">
         <v>-43.36</v>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>67.89</v>
+        <v>68.42</v>
       </c>
     </row>
     <row r="6">

--- a/ETF_Allocation_Model.xlsx
+++ b/ETF_Allocation_Model.xlsx
@@ -477,12 +477,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>EIMI.MI</t>
+          <t>SWDA.MI</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>iShares Core MSCI EM IMI UCITS ETF USD (Acc)</t>
+          <t>iShares Core MSCI World UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -492,7 +492,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Mercati emergenti</t>
+          <t>Azionario globale sviluppato</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -502,34 +502,34 @@
         <v>183.3</v>
       </c>
       <c r="G2" t="n">
-        <v>80.8</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Buy Watchlist</t>
+          <t>Accumulate Carefully</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>16.53</v>
+        <v>13.17</v>
       </c>
       <c r="J2" t="n">
-        <v>-19.17</v>
+        <v>-21.63</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>ETF forte e in trend favorevole; valutare solo con coerenza di portafoglio.</t>
+          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>VWCE.DE</t>
+          <t>SXR8.DE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Vanguard FTSE All-World UCITS ETF USD Accumulation</t>
+          <t>iShares Core S&amp;P 500 UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -539,7 +539,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Azionario globale</t>
+          <t>USA large cap</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -549,34 +549,34 @@
         <v>183.3</v>
       </c>
       <c r="G3" t="n">
-        <v>79</v>
+        <v>76.2</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Buy Watchlist</t>
+          <t>Accumulate Carefully</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>12.92</v>
+        <v>14.17</v>
       </c>
       <c r="J3" t="n">
-        <v>-21.07</v>
+        <v>-23.32</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>ETF forte e in trend favorevole; valutare solo con coerenza di portafoglio.</t>
+          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SWDA.MI</t>
+          <t>EXSA.DE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>iShares Core MSCI World UCITS ETF USD (Acc)</t>
+          <t>iShares STOXX Europe 600 UCITS ETF (DE) EUR (Dist)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -586,7 +586,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Azionario globale sviluppato</t>
+          <t>Europa</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -596,22 +596,22 @@
         <v>183.3</v>
       </c>
       <c r="G4" t="n">
-        <v>78.2</v>
+        <v>75.5</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Buy Watchlist</t>
+          <t>Accumulate Carefully</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>13.17</v>
+        <v>12.83</v>
       </c>
       <c r="J4" t="n">
-        <v>-21.63</v>
+        <v>-16.33</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>ETF forte e in trend favorevole; valutare solo con coerenza di portafoglio.</t>
+          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
         </is>
       </c>
     </row>
@@ -643,7 +643,7 @@
         <v>66.7</v>
       </c>
       <c r="G5" t="n">
-        <v>71.5</v>
+        <v>72.3</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -690,7 +690,7 @@
         <v>66.7</v>
       </c>
       <c r="G6" t="n">
-        <v>54.8</v>
+        <v>54.1</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>75</v>
       </c>
       <c r="G8" t="n">
-        <v>83.8</v>
+        <v>83.5</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>13.91</v>
+        <v>13.95</v>
       </c>
       <c r="J8" t="n">
         <v>-17.8</v>
@@ -827,7 +827,7 @@
         <v>75</v>
       </c>
       <c r="G9" t="n">
-        <v>76.09999999999999</v>
+        <v>74.5</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>12.86</v>
+        <v>12.87</v>
       </c>
       <c r="J9" t="n">
         <v>-20.6</v>
@@ -874,7 +874,7 @@
         <v>33.3</v>
       </c>
       <c r="G10" t="n">
-        <v>71.09999999999999</v>
+        <v>72</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>21.83</v>
+        <v>22.02</v>
       </c>
       <c r="J10" t="n">
         <v>-29.37</v>
@@ -921,15 +921,15 @@
         <v>33.3</v>
       </c>
       <c r="G11" t="n">
-        <v>69</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Accumulate Carefully</t>
+          <t>Hold / Monitor</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>36.11</v>
+        <v>36.18</v>
       </c>
       <c r="J11" t="n">
         <v>-35.74</v>
@@ -968,15 +968,15 @@
         <v>33.3</v>
       </c>
       <c r="G12" t="n">
-        <v>60.4</v>
+        <v>53.4</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Hold / Monitor</t>
+          <t>High Risk</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>23.79</v>
+        <v>23.99</v>
       </c>
       <c r="J12" t="n">
         <v>-43.36</v>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>68.42</v>
+        <v>63.14</v>
       </c>
     </row>
     <row r="6">

--- a/ETF_Allocation_Model.xlsx
+++ b/ETF_Allocation_Model.xlsx
@@ -477,12 +477,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SWDA.MI</t>
+          <t>VWCE.DE</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>iShares Core MSCI World UCITS ETF USD (Acc)</t>
+          <t>Vanguard FTSE All-World UCITS ETF USD Accumulation</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -492,7 +492,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Azionario globale sviluppato</t>
+          <t>Azionario globale</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -502,7 +502,7 @@
         <v>183.3</v>
       </c>
       <c r="G2" t="n">
-        <v>76.40000000000001</v>
+        <v>76.5</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -510,10 +510,10 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>13.17</v>
+        <v>12.94</v>
       </c>
       <c r="J2" t="n">
-        <v>-21.63</v>
+        <v>-21.07</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -524,12 +524,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SXR8.DE</t>
+          <t>SWDA.MI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>iShares Core S&amp;P 500 UCITS ETF USD (Acc)</t>
+          <t>iShares Core MSCI World UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -539,7 +539,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>USA large cap</t>
+          <t>Azionario globale sviluppato</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -549,7 +549,7 @@
         <v>183.3</v>
       </c>
       <c r="G3" t="n">
-        <v>76.2</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -557,10 +557,10 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>14.17</v>
+        <v>13.18</v>
       </c>
       <c r="J3" t="n">
-        <v>-23.32</v>
+        <v>-21.63</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -571,12 +571,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>SXR8.DE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>iShares STOXX Europe 600 UCITS ETF (DE) EUR (Dist)</t>
+          <t>iShares Core S&amp;P 500 UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -586,7 +586,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Europa</t>
+          <t>USA large cap</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -596,7 +596,7 @@
         <v>183.3</v>
       </c>
       <c r="G4" t="n">
-        <v>75.5</v>
+        <v>75.7</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -604,10 +604,10 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>12.83</v>
+        <v>14.17</v>
       </c>
       <c r="J4" t="n">
-        <v>-16.33</v>
+        <v>-23.32</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -643,7 +643,7 @@
         <v>66.7</v>
       </c>
       <c r="G5" t="n">
-        <v>72.3</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -690,7 +690,7 @@
         <v>66.7</v>
       </c>
       <c r="G6" t="n">
-        <v>54.1</v>
+        <v>51.8</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -698,7 +698,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>18.25</v>
+        <v>18.31</v>
       </c>
       <c r="J6" t="n">
         <v>-22.39</v>
@@ -780,7 +780,7 @@
         <v>75</v>
       </c>
       <c r="G8" t="n">
-        <v>83.5</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -827,7 +827,7 @@
         <v>75</v>
       </c>
       <c r="G9" t="n">
-        <v>74.5</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -849,12 +849,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>RBOT.MI</t>
+          <t>SMH</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>iShares Automation &amp; Robotics UCITS ETF USD (Acc)</t>
+          <t>VanEck Semiconductor ETF</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -864,7 +864,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Robotica e automazione</t>
+          <t>Semiconduttori</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -874,7 +874,7 @@
         <v>33.3</v>
       </c>
       <c r="G10" t="n">
-        <v>72</v>
+        <v>68.8</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -882,26 +882,26 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>22.02</v>
+        <v>36.17</v>
       </c>
       <c r="J10" t="n">
-        <v>-29.37</v>
+        <v>-35.74</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
+          <t>Rischio elevato: usare solo come quota satellite e con size ridotta.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SMH</t>
+          <t>RBOT.MI</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>VanEck Semiconductor ETF</t>
+          <t>iShares Automation &amp; Robotics UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -911,7 +911,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Semiconduttori</t>
+          <t>Robotica e automazione</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -921,34 +921,34 @@
         <v>33.3</v>
       </c>
       <c r="G11" t="n">
-        <v>65.09999999999999</v>
+        <v>68.2</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Hold / Monitor</t>
+          <t>Accumulate Carefully</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>36.18</v>
+        <v>22.04</v>
       </c>
       <c r="J11" t="n">
-        <v>-35.74</v>
+        <v>-29.37</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Rischio elevato: usare solo come quota satellite e con size ridotta.</t>
+          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>INRG.MI</t>
+          <t>WCLD.MI</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>iShares Global Clean Energy Transition UCITS ETF USD (Dist)</t>
+          <t>WisdomTree Cloud Computing UCITS ETF - USD Acc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -958,7 +958,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Energia pulita</t>
+          <t>Cloud</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -968,7 +968,7 @@
         <v>33.3</v>
       </c>
       <c r="G12" t="n">
-        <v>53.4</v>
+        <v>53.9</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>23.99</v>
+        <v>34.45</v>
       </c>
       <c r="J12" t="n">
-        <v>-43.36</v>
+        <v>-48.6</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>63.14</v>
+        <v>66.23999999999999</v>
       </c>
     </row>
     <row r="6">

--- a/ETF_Allocation_Model.xlsx
+++ b/ETF_Allocation_Model.xlsx
@@ -477,12 +477,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>VWCE.DE</t>
+          <t>EIMI.MI</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Vanguard FTSE All-World UCITS ETF USD Accumulation</t>
+          <t>iShares Core MSCI EM IMI UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -492,7 +492,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Azionario globale</t>
+          <t>Mercati emergenti</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -502,7 +502,7 @@
         <v>183.3</v>
       </c>
       <c r="G2" t="n">
-        <v>76.5</v>
+        <v>78</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -510,10 +510,10 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>12.94</v>
+        <v>16.69</v>
       </c>
       <c r="J2" t="n">
-        <v>-21.07</v>
+        <v>-19.17</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -524,12 +524,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SWDA.MI</t>
+          <t>VWCE.DE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>iShares Core MSCI World UCITS ETF USD (Acc)</t>
+          <t>Vanguard FTSE All-World UCITS ETF USD Accumulation</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -539,7 +539,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Azionario globale sviluppato</t>
+          <t>Azionario globale</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -549,7 +549,7 @@
         <v>183.3</v>
       </c>
       <c r="G3" t="n">
-        <v>75.90000000000001</v>
+        <v>77.3</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -557,10 +557,10 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>13.18</v>
+        <v>12.95</v>
       </c>
       <c r="J3" t="n">
-        <v>-21.63</v>
+        <v>-21.07</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -571,12 +571,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SXR8.DE</t>
+          <t>SWDA.MI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>iShares Core S&amp;P 500 UCITS ETF USD (Acc)</t>
+          <t>iShares Core MSCI World UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -586,7 +586,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>USA large cap</t>
+          <t>Azionario globale sviluppato</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -596,7 +596,7 @@
         <v>183.3</v>
       </c>
       <c r="G4" t="n">
-        <v>75.7</v>
+        <v>76.5</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -604,10 +604,10 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>14.17</v>
+        <v>13.18</v>
       </c>
       <c r="J4" t="n">
-        <v>-23.32</v>
+        <v>-21.63</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -690,7 +690,7 @@
         <v>66.7</v>
       </c>
       <c r="G6" t="n">
-        <v>51.8</v>
+        <v>53.8</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -698,7 +698,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>18.31</v>
+        <v>18.34</v>
       </c>
       <c r="J6" t="n">
         <v>-22.39</v>
@@ -780,7 +780,7 @@
         <v>75</v>
       </c>
       <c r="G8" t="n">
-        <v>83.40000000000001</v>
+        <v>83.7</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>13.95</v>
+        <v>14.01</v>
       </c>
       <c r="J8" t="n">
         <v>-17.8</v>
@@ -827,7 +827,7 @@
         <v>75</v>
       </c>
       <c r="G9" t="n">
-        <v>74.09999999999999</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -849,12 +849,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SMH</t>
+          <t>RBOT.MI</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>VanEck Semiconductor ETF</t>
+          <t>iShares Automation &amp; Robotics UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -864,7 +864,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Semiconduttori</t>
+          <t>Robotica e automazione</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -874,7 +874,7 @@
         <v>33.3</v>
       </c>
       <c r="G10" t="n">
-        <v>68.8</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -882,26 +882,26 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>36.17</v>
+        <v>22.14</v>
       </c>
       <c r="J10" t="n">
-        <v>-35.74</v>
+        <v>-29.37</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Rischio elevato: usare solo come quota satellite e con size ridotta.</t>
+          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>RBOT.MI</t>
+          <t>SMH</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>iShares Automation &amp; Robotics UCITS ETF USD (Acc)</t>
+          <t>VanEck Semiconductor ETF</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -911,7 +911,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Robotica e automazione</t>
+          <t>Semiconduttori</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -921,7 +921,7 @@
         <v>33.3</v>
       </c>
       <c r="G11" t="n">
-        <v>68.2</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -929,14 +929,14 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>22.04</v>
+        <v>36.17</v>
       </c>
       <c r="J11" t="n">
-        <v>-29.37</v>
+        <v>-35.74</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
+          <t>Rischio elevato: usare solo come quota satellite e con size ridotta.</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
         <v>33.3</v>
       </c>
       <c r="G12" t="n">
-        <v>53.9</v>
+        <v>54.1</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -976,7 +976,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>34.45</v>
+        <v>34.44</v>
       </c>
       <c r="J12" t="n">
         <v>-48.6</v>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>66.23999999999999</v>
+        <v>67.41</v>
       </c>
     </row>
     <row r="6">

--- a/ETF_Allocation_Model.xlsx
+++ b/ETF_Allocation_Model.xlsx
@@ -502,22 +502,22 @@
         <v>183.3</v>
       </c>
       <c r="G2" t="n">
-        <v>78</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Accumulate Carefully</t>
+          <t>Buy Watchlist</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>16.69</v>
+        <v>16.68</v>
       </c>
       <c r="J2" t="n">
         <v>-19.17</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
+          <t>ETF forte e in trend favorevole; valutare solo con coerenza di portafoglio.</t>
         </is>
       </c>
     </row>
@@ -549,7 +549,7 @@
         <v>183.3</v>
       </c>
       <c r="G3" t="n">
-        <v>77.3</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>12.95</v>
+        <v>12.94</v>
       </c>
       <c r="J3" t="n">
         <v>-21.07</v>
@@ -596,7 +596,7 @@
         <v>183.3</v>
       </c>
       <c r="G4" t="n">
-        <v>76.5</v>
+        <v>76.7</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>13.18</v>
+        <v>13.17</v>
       </c>
       <c r="J4" t="n">
         <v>-21.63</v>
@@ -643,7 +643,7 @@
         <v>66.7</v>
       </c>
       <c r="G5" t="n">
-        <v>71.90000000000001</v>
+        <v>72</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>9.57</v>
+        <v>9.56</v>
       </c>
       <c r="J5" t="n">
         <v>-12.85</v>
@@ -690,7 +690,7 @@
         <v>66.7</v>
       </c>
       <c r="G6" t="n">
-        <v>53.8</v>
+        <v>53.5</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -698,7 +698,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>18.34</v>
+        <v>18.33</v>
       </c>
       <c r="J6" t="n">
         <v>-22.39</v>
@@ -780,7 +780,7 @@
         <v>75</v>
       </c>
       <c r="G8" t="n">
-        <v>83.7</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>14.01</v>
+        <v>14</v>
       </c>
       <c r="J8" t="n">
         <v>-17.8</v>
@@ -827,7 +827,7 @@
         <v>75</v>
       </c>
       <c r="G9" t="n">
-        <v>74.59999999999999</v>
+        <v>74.8</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>12.87</v>
+        <v>12.86</v>
       </c>
       <c r="J9" t="n">
         <v>-20.6</v>
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>22.14</v>
+        <v>22.13</v>
       </c>
       <c r="J10" t="n">
         <v>-29.37</v>
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>36.17</v>
+        <v>36.14</v>
       </c>
       <c r="J11" t="n">
         <v>-35.74</v>
@@ -968,7 +968,7 @@
         <v>33.3</v>
       </c>
       <c r="G12" t="n">
-        <v>54.1</v>
+        <v>54.9</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -976,7 +976,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>34.44</v>
+        <v>34.42</v>
       </c>
       <c r="J12" t="n">
         <v>-48.6</v>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>67.41</v>
+        <v>65.45999999999999</v>
       </c>
     </row>
     <row r="6">

--- a/ETF_Allocation_Model.xlsx
+++ b/ETF_Allocation_Model.xlsx
@@ -477,12 +477,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>EIMI.MI</t>
+          <t>VWCE.DE</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>iShares Core MSCI EM IMI UCITS ETF USD (Acc)</t>
+          <t>Vanguard FTSE All-World UCITS ETF USD Accumulation</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -492,7 +492,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Mercati emergenti</t>
+          <t>Azionario globale</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -502,34 +502,34 @@
         <v>183.3</v>
       </c>
       <c r="G2" t="n">
-        <v>78.09999999999999</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Buy Watchlist</t>
+          <t>Accumulate Carefully</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>16.68</v>
+        <v>12.95</v>
       </c>
       <c r="J2" t="n">
-        <v>-19.17</v>
+        <v>-21.07</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>ETF forte e in trend favorevole; valutare solo con coerenza di portafoglio.</t>
+          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>VWCE.DE</t>
+          <t>SWDA.MI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Vanguard FTSE All-World UCITS ETF USD Accumulation</t>
+          <t>iShares Core MSCI World UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -539,7 +539,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Azionario globale</t>
+          <t>Azionario globale sviluppato</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -549,7 +549,7 @@
         <v>183.3</v>
       </c>
       <c r="G3" t="n">
-        <v>77.40000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -557,10 +557,10 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>12.94</v>
+        <v>13.19</v>
       </c>
       <c r="J3" t="n">
-        <v>-21.07</v>
+        <v>-21.63</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -571,12 +571,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SWDA.MI</t>
+          <t>SXR8.DE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>iShares Core MSCI World UCITS ETF USD (Acc)</t>
+          <t>iShares Core S&amp;P 500 UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -586,7 +586,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Azionario globale sviluppato</t>
+          <t>USA large cap</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -596,7 +596,7 @@
         <v>183.3</v>
       </c>
       <c r="G4" t="n">
-        <v>76.7</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -604,10 +604,10 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>13.17</v>
+        <v>14.18</v>
       </c>
       <c r="J4" t="n">
-        <v>-21.63</v>
+        <v>-23.32</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -643,7 +643,7 @@
         <v>66.7</v>
       </c>
       <c r="G5" t="n">
-        <v>72</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>9.56</v>
+        <v>9.58</v>
       </c>
       <c r="J5" t="n">
         <v>-12.85</v>
@@ -690,7 +690,7 @@
         <v>66.7</v>
       </c>
       <c r="G6" t="n">
-        <v>53.5</v>
+        <v>51.4</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -698,7 +698,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>18.33</v>
+        <v>18.38</v>
       </c>
       <c r="J6" t="n">
         <v>-22.39</v>
@@ -780,7 +780,7 @@
         <v>75</v>
       </c>
       <c r="G8" t="n">
-        <v>83.59999999999999</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>14</v>
+        <v>14.02</v>
       </c>
       <c r="J8" t="n">
         <v>-17.8</v>
@@ -827,7 +827,7 @@
         <v>75</v>
       </c>
       <c r="G9" t="n">
-        <v>74.8</v>
+        <v>74.5</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>12.86</v>
+        <v>12.87</v>
       </c>
       <c r="J9" t="n">
         <v>-20.6</v>
@@ -874,7 +874,7 @@
         <v>33.3</v>
       </c>
       <c r="G10" t="n">
-        <v>72.09999999999999</v>
+        <v>71.8</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>22.13</v>
+        <v>22.15</v>
       </c>
       <c r="J10" t="n">
         <v>-29.37</v>
@@ -921,15 +921,15 @@
         <v>33.3</v>
       </c>
       <c r="G11" t="n">
-        <v>68.90000000000001</v>
+        <v>64.7</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Accumulate Carefully</t>
+          <t>Hold / Monitor</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>36.14</v>
+        <v>36.23</v>
       </c>
       <c r="J11" t="n">
         <v>-35.74</v>
@@ -968,7 +968,7 @@
         <v>33.3</v>
       </c>
       <c r="G12" t="n">
-        <v>54.9</v>
+        <v>53.1</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -976,7 +976,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>34.42</v>
+        <v>34.48</v>
       </c>
       <c r="J12" t="n">
         <v>-48.6</v>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>65.45999999999999</v>
+        <v>66.04000000000001</v>
       </c>
     </row>
     <row r="6">

--- a/ETF_Allocation_Model.xlsx
+++ b/ETF_Allocation_Model.xlsx
@@ -502,7 +502,7 @@
         <v>183.3</v>
       </c>
       <c r="G2" t="n">
-        <v>76.59999999999999</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -549,7 +549,7 @@
         <v>183.3</v>
       </c>
       <c r="G3" t="n">
-        <v>76.2</v>
+        <v>75.8</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -596,7 +596,7 @@
         <v>183.3</v>
       </c>
       <c r="G4" t="n">
-        <v>76.09999999999999</v>
+        <v>75.5</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -643,7 +643,7 @@
         <v>66.7</v>
       </c>
       <c r="G5" t="n">
-        <v>72.59999999999999</v>
+        <v>72.2</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -690,7 +690,7 @@
         <v>66.7</v>
       </c>
       <c r="G6" t="n">
-        <v>51.4</v>
+        <v>52.5</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -698,7 +698,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>18.38</v>
+        <v>18.39</v>
       </c>
       <c r="J6" t="n">
         <v>-22.39</v>
@@ -780,7 +780,7 @@
         <v>75</v>
       </c>
       <c r="G8" t="n">
-        <v>83.40000000000001</v>
+        <v>83.7</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>14.02</v>
+        <v>14.01</v>
       </c>
       <c r="J8" t="n">
         <v>-17.8</v>
@@ -827,7 +827,7 @@
         <v>75</v>
       </c>
       <c r="G9" t="n">
-        <v>74.5</v>
+        <v>74.2</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>12.87</v>
+        <v>12.88</v>
       </c>
       <c r="J9" t="n">
         <v>-20.6</v>
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>22.15</v>
+        <v>22.16</v>
       </c>
       <c r="J10" t="n">
         <v>-29.37</v>
@@ -921,15 +921,15 @@
         <v>33.3</v>
       </c>
       <c r="G11" t="n">
-        <v>64.7</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Hold / Monitor</t>
+          <t>Accumulate Carefully</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>36.23</v>
+        <v>36.26</v>
       </c>
       <c r="J11" t="n">
         <v>-35.74</v>
@@ -968,7 +968,7 @@
         <v>33.3</v>
       </c>
       <c r="G12" t="n">
-        <v>53.1</v>
+        <v>53.4</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>66.04000000000001</v>
+        <v>66.34999999999999</v>
       </c>
     </row>
     <row r="6">

--- a/ETF_Allocation_Model.xlsx
+++ b/ETF_Allocation_Model.xlsx
@@ -549,7 +549,7 @@
         <v>183.3</v>
       </c>
       <c r="G3" t="n">
-        <v>75.8</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -596,7 +596,7 @@
         <v>183.3</v>
       </c>
       <c r="G4" t="n">
-        <v>75.5</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -643,7 +643,7 @@
         <v>66.7</v>
       </c>
       <c r="G5" t="n">
-        <v>72.2</v>
+        <v>71.5</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>9.58</v>
+        <v>9.59</v>
       </c>
       <c r="J5" t="n">
         <v>-12.85</v>
@@ -690,7 +690,7 @@
         <v>66.7</v>
       </c>
       <c r="G6" t="n">
-        <v>52.5</v>
+        <v>51.7</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -698,7 +698,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>18.39</v>
+        <v>18.4</v>
       </c>
       <c r="J6" t="n">
         <v>-22.39</v>
@@ -780,7 +780,7 @@
         <v>75</v>
       </c>
       <c r="G8" t="n">
-        <v>83.7</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>14.01</v>
+        <v>14.04</v>
       </c>
       <c r="J8" t="n">
         <v>-17.8</v>
@@ -827,7 +827,7 @@
         <v>75</v>
       </c>
       <c r="G9" t="n">
-        <v>74.2</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -874,15 +874,15 @@
         <v>33.3</v>
       </c>
       <c r="G10" t="n">
-        <v>71.8</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Accumulate Carefully</t>
+          <t>Hold / Monitor</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>22.16</v>
+        <v>22.18</v>
       </c>
       <c r="J10" t="n">
         <v>-29.37</v>
@@ -921,11 +921,11 @@
         <v>33.3</v>
       </c>
       <c r="G11" t="n">
-        <v>68.59999999999999</v>
+        <v>64.7</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Accumulate Carefully</t>
+          <t>Hold / Monitor</t>
         </is>
       </c>
       <c r="I11" t="n">
@@ -968,7 +968,7 @@
         <v>33.3</v>
       </c>
       <c r="G12" t="n">
-        <v>53.4</v>
+        <v>53.7</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -976,7 +976,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>34.48</v>
+        <v>34.47</v>
       </c>
       <c r="J12" t="n">
         <v>-48.6</v>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>66.34999999999999</v>
+        <v>65.67</v>
       </c>
     </row>
     <row r="6">

--- a/ETF_Allocation_Model.xlsx
+++ b/ETF_Allocation_Model.xlsx
@@ -502,7 +502,7 @@
         <v>183.3</v>
       </c>
       <c r="G2" t="n">
-        <v>76.40000000000001</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -510,7 +510,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>12.95</v>
+        <v>12.94</v>
       </c>
       <c r="J2" t="n">
         <v>-21.07</v>
@@ -549,7 +549,7 @@
         <v>183.3</v>
       </c>
       <c r="G3" t="n">
-        <v>75.90000000000001</v>
+        <v>75.2</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>13.19</v>
+        <v>13.18</v>
       </c>
       <c r="J3" t="n">
         <v>-21.63</v>
@@ -596,7 +596,7 @@
         <v>183.3</v>
       </c>
       <c r="G4" t="n">
-        <v>75.59999999999999</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>14.18</v>
+        <v>14.17</v>
       </c>
       <c r="J4" t="n">
         <v>-23.32</v>
@@ -643,7 +643,7 @@
         <v>66.7</v>
       </c>
       <c r="G5" t="n">
-        <v>71.5</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -690,7 +690,7 @@
         <v>66.7</v>
       </c>
       <c r="G6" t="n">
-        <v>51.7</v>
+        <v>50.6</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -698,10 +698,10 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>18.4</v>
+        <v>18.39</v>
       </c>
       <c r="J6" t="n">
-        <v>-22.39</v>
+        <v>-22.63</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>75</v>
       </c>
       <c r="G8" t="n">
-        <v>83.40000000000001</v>
+        <v>79.8</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -827,7 +827,7 @@
         <v>75</v>
       </c>
       <c r="G9" t="n">
-        <v>74.40000000000001</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>12.88</v>
+        <v>12.87</v>
       </c>
       <c r="J9" t="n">
         <v>-20.6</v>
@@ -874,7 +874,7 @@
         <v>33.3</v>
       </c>
       <c r="G10" t="n">
-        <v>67.09999999999999</v>
+        <v>64.7</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>22.18</v>
+        <v>22.17</v>
       </c>
       <c r="J10" t="n">
         <v>-29.37</v>
@@ -921,7 +921,7 @@
         <v>33.3</v>
       </c>
       <c r="G11" t="n">
-        <v>64.7</v>
+        <v>63.3</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>36.26</v>
+        <v>36.33</v>
       </c>
       <c r="J11" t="n">
         <v>-35.74</v>
@@ -968,7 +968,7 @@
         <v>33.3</v>
       </c>
       <c r="G12" t="n">
-        <v>53.7</v>
+        <v>53.9</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -976,7 +976,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>34.47</v>
+        <v>34.45</v>
       </c>
       <c r="J12" t="n">
         <v>-48.6</v>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>65.67</v>
+        <v>64.56</v>
       </c>
     </row>
     <row r="6">

--- a/ETF_Allocation_Model.xlsx
+++ b/ETF_Allocation_Model.xlsx
@@ -502,7 +502,7 @@
         <v>183.3</v>
       </c>
       <c r="G2" t="n">
-        <v>75.40000000000001</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -510,7 +510,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>12.94</v>
+        <v>12.96</v>
       </c>
       <c r="J2" t="n">
         <v>-21.07</v>
@@ -549,7 +549,7 @@
         <v>183.3</v>
       </c>
       <c r="G3" t="n">
-        <v>75.2</v>
+        <v>74.5</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>13.18</v>
+        <v>13.19</v>
       </c>
       <c r="J3" t="n">
         <v>-21.63</v>
@@ -596,7 +596,7 @@
         <v>183.3</v>
       </c>
       <c r="G4" t="n">
-        <v>74.90000000000001</v>
+        <v>74.2</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>14.17</v>
+        <v>14.18</v>
       </c>
       <c r="J4" t="n">
         <v>-23.32</v>
@@ -643,7 +643,7 @@
         <v>66.7</v>
       </c>
       <c r="G5" t="n">
-        <v>71.59999999999999</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -690,7 +690,7 @@
         <v>66.7</v>
       </c>
       <c r="G6" t="n">
-        <v>50.6</v>
+        <v>50.9</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -698,10 +698,10 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>18.39</v>
+        <v>18.38</v>
       </c>
       <c r="J6" t="n">
-        <v>-22.63</v>
+        <v>-22.72</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>75</v>
       </c>
       <c r="G8" t="n">
-        <v>79.8</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -827,7 +827,7 @@
         <v>75</v>
       </c>
       <c r="G9" t="n">
-        <v>74.09999999999999</v>
+        <v>73.2</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>12.87</v>
+        <v>12.88</v>
       </c>
       <c r="J9" t="n">
         <v>-20.6</v>
@@ -849,12 +849,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>RBOT.MI</t>
+          <t>SMH</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>iShares Automation &amp; Robotics UCITS ETF USD (Acc)</t>
+          <t>VanEck Semiconductor ETF</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -864,7 +864,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Robotica e automazione</t>
+          <t>Semiconduttori</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -874,7 +874,7 @@
         <v>33.3</v>
       </c>
       <c r="G10" t="n">
-        <v>64.7</v>
+        <v>63</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -882,26 +882,26 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>22.17</v>
+        <v>36.3</v>
       </c>
       <c r="J10" t="n">
-        <v>-29.37</v>
+        <v>-35.74</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
+          <t>Rischio elevato: usare solo come quota satellite e con size ridotta.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SMH</t>
+          <t>RBOT.MI</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>VanEck Semiconductor ETF</t>
+          <t>iShares Automation &amp; Robotics UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -911,7 +911,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Semiconduttori</t>
+          <t>Robotica e automazione</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -921,7 +921,7 @@
         <v>33.3</v>
       </c>
       <c r="G11" t="n">
-        <v>63.3</v>
+        <v>62.3</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -929,14 +929,14 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>36.33</v>
+        <v>22.22</v>
       </c>
       <c r="J11" t="n">
-        <v>-35.74</v>
+        <v>-29.37</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Rischio elevato: usare solo come quota satellite e con size ridotta.</t>
+          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
         <v>33.3</v>
       </c>
       <c r="G12" t="n">
-        <v>53.9</v>
+        <v>54.2</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -976,7 +976,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>34.45</v>
+        <v>34.43</v>
       </c>
       <c r="J12" t="n">
         <v>-48.6</v>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>64.56</v>
+        <v>63.98</v>
       </c>
     </row>
     <row r="6">

--- a/ETF_Allocation_Model.xlsx
+++ b/ETF_Allocation_Model.xlsx
@@ -502,7 +502,7 @@
         <v>183.3</v>
       </c>
       <c r="G2" t="n">
-        <v>74.90000000000001</v>
+        <v>75.2</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -510,7 +510,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>12.96</v>
+        <v>12.97</v>
       </c>
       <c r="J2" t="n">
         <v>-21.07</v>
@@ -549,7 +549,7 @@
         <v>183.3</v>
       </c>
       <c r="G3" t="n">
-        <v>74.5</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -596,7 +596,7 @@
         <v>183.3</v>
       </c>
       <c r="G4" t="n">
-        <v>74.2</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>14.18</v>
+        <v>14.19</v>
       </c>
       <c r="J4" t="n">
         <v>-23.32</v>
@@ -643,7 +643,7 @@
         <v>66.7</v>
       </c>
       <c r="G5" t="n">
-        <v>72.09999999999999</v>
+        <v>71.8</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>9.59</v>
+        <v>9.58</v>
       </c>
       <c r="J5" t="n">
         <v>-12.85</v>
@@ -690,7 +690,7 @@
         <v>66.7</v>
       </c>
       <c r="G6" t="n">
-        <v>50.9</v>
+        <v>51.2</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -698,7 +698,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>18.38</v>
+        <v>18.39</v>
       </c>
       <c r="J6" t="n">
         <v>-22.72</v>
@@ -780,7 +780,7 @@
         <v>75</v>
       </c>
       <c r="G8" t="n">
-        <v>79.59999999999999</v>
+        <v>79.5</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -827,7 +827,7 @@
         <v>75</v>
       </c>
       <c r="G9" t="n">
-        <v>73.2</v>
+        <v>73.5</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>12.88</v>
+        <v>12.89</v>
       </c>
       <c r="J9" t="n">
         <v>-20.6</v>
@@ -849,12 +849,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SMH</t>
+          <t>RBOT.MI</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>VanEck Semiconductor ETF</t>
+          <t>iShares Automation &amp; Robotics UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -864,7 +864,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Semiconduttori</t>
+          <t>Robotica e automazione</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -874,7 +874,7 @@
         <v>33.3</v>
       </c>
       <c r="G10" t="n">
-        <v>63</v>
+        <v>63.9</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -882,26 +882,26 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>36.3</v>
+        <v>22.24</v>
       </c>
       <c r="J10" t="n">
-        <v>-35.74</v>
+        <v>-29.37</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Rischio elevato: usare solo come quota satellite e con size ridotta.</t>
+          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>RBOT.MI</t>
+          <t>SMH</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>iShares Automation &amp; Robotics UCITS ETF USD (Acc)</t>
+          <t>VanEck Semiconductor ETF</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -911,7 +911,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Robotica e automazione</t>
+          <t>Semiconduttori</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -921,7 +921,7 @@
         <v>33.3</v>
       </c>
       <c r="G11" t="n">
-        <v>62.3</v>
+        <v>63.2</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -929,14 +929,14 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>22.22</v>
+        <v>36.31</v>
       </c>
       <c r="J11" t="n">
-        <v>-29.37</v>
+        <v>-35.74</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
+          <t>Rischio elevato: usare solo come quota satellite e con size ridotta.</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
         <v>33.3</v>
       </c>
       <c r="G12" t="n">
-        <v>54.2</v>
+        <v>53.3</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -976,7 +976,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>34.43</v>
+        <v>34.38</v>
       </c>
       <c r="J12" t="n">
         <v>-48.6</v>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>63.98</v>
+        <v>64.20999999999999</v>
       </c>
     </row>
     <row r="6">

--- a/ETF_Allocation_Model.xlsx
+++ b/ETF_Allocation_Model.xlsx
@@ -502,7 +502,7 @@
         <v>183.3</v>
       </c>
       <c r="G2" t="n">
-        <v>75.2</v>
+        <v>75.5</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -549,7 +549,7 @@
         <v>183.3</v>
       </c>
       <c r="G3" t="n">
-        <v>74.90000000000001</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -571,12 +571,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SXR8.DE</t>
+          <t>EXSA.DE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>iShares Core S&amp;P 500 UCITS ETF USD (Acc)</t>
+          <t>iShares STOXX Europe 600 UCITS ETF (DE) EUR (Dist)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -586,7 +586,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>USA large cap</t>
+          <t>Europa</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -596,7 +596,7 @@
         <v>183.3</v>
       </c>
       <c r="G4" t="n">
-        <v>74.40000000000001</v>
+        <v>74.5</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -604,10 +604,10 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>14.19</v>
+        <v>12.83</v>
       </c>
       <c r="J4" t="n">
-        <v>-23.32</v>
+        <v>-16.33</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -643,7 +643,7 @@
         <v>66.7</v>
       </c>
       <c r="G5" t="n">
-        <v>71.8</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>9.58</v>
+        <v>9.57</v>
       </c>
       <c r="J5" t="n">
         <v>-12.85</v>
@@ -690,7 +690,7 @@
         <v>66.7</v>
       </c>
       <c r="G6" t="n">
-        <v>51.2</v>
+        <v>52.5</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -698,7 +698,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>18.39</v>
+        <v>18.41</v>
       </c>
       <c r="J6" t="n">
         <v>-22.72</v>
@@ -780,7 +780,7 @@
         <v>75</v>
       </c>
       <c r="G8" t="n">
-        <v>79.5</v>
+        <v>83.3</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>14.04</v>
+        <v>14.07</v>
       </c>
       <c r="J8" t="n">
         <v>-17.8</v>
@@ -874,7 +874,7 @@
         <v>33.3</v>
       </c>
       <c r="G10" t="n">
-        <v>63.9</v>
+        <v>65.2</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>22.24</v>
+        <v>22.26</v>
       </c>
       <c r="J10" t="n">
         <v>-29.37</v>
@@ -921,7 +921,7 @@
         <v>33.3</v>
       </c>
       <c r="G11" t="n">
-        <v>63.2</v>
+        <v>64.5</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>36.31</v>
+        <v>36.38</v>
       </c>
       <c r="J11" t="n">
         <v>-35.74</v>
@@ -968,7 +968,7 @@
         <v>33.3</v>
       </c>
       <c r="G12" t="n">
-        <v>53.3</v>
+        <v>54.2</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -976,7 +976,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>34.38</v>
+        <v>34.42</v>
       </c>
       <c r="J12" t="n">
         <v>-48.6</v>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>64.20999999999999</v>
+        <v>65.06</v>
       </c>
     </row>
     <row r="6">

--- a/ETF_Allocation_Model.xlsx
+++ b/ETF_Allocation_Model.xlsx
@@ -502,7 +502,7 @@
         <v>183.3</v>
       </c>
       <c r="G2" t="n">
-        <v>75.5</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -549,7 +549,7 @@
         <v>183.3</v>
       </c>
       <c r="G3" t="n">
-        <v>75.09999999999999</v>
+        <v>75</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -596,7 +596,7 @@
         <v>183.3</v>
       </c>
       <c r="G4" t="n">
-        <v>74.5</v>
+        <v>74.7</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -690,7 +690,7 @@
         <v>66.7</v>
       </c>
       <c r="G6" t="n">
-        <v>52.5</v>
+        <v>53.7</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -698,7 +698,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>18.41</v>
+        <v>18.44</v>
       </c>
       <c r="J6" t="n">
         <v>-22.72</v>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>14.07</v>
+        <v>14.08</v>
       </c>
       <c r="J8" t="n">
         <v>-17.8</v>
@@ -827,7 +827,7 @@
         <v>75</v>
       </c>
       <c r="G9" t="n">
-        <v>73.5</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -874,7 +874,7 @@
         <v>33.3</v>
       </c>
       <c r="G10" t="n">
-        <v>65.2</v>
+        <v>64.8</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -921,7 +921,7 @@
         <v>33.3</v>
       </c>
       <c r="G11" t="n">
-        <v>64.5</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>36.38</v>
+        <v>36.37</v>
       </c>
       <c r="J11" t="n">
         <v>-35.74</v>
@@ -968,15 +968,15 @@
         <v>33.3</v>
       </c>
       <c r="G12" t="n">
-        <v>54.2</v>
+        <v>55.5</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>High Risk</t>
+          <t>Hold / Monitor</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>34.42</v>
+        <v>34.52</v>
       </c>
       <c r="J12" t="n">
         <v>-48.6</v>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>65.06</v>
+        <v>65.19</v>
       </c>
     </row>
     <row r="6">

--- a/ETF_Allocation_Model.xlsx
+++ b/ETF_Allocation_Model.xlsx
@@ -477,12 +477,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>VWCE.DE</t>
+          <t>SWDA.MI</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Vanguard FTSE All-World UCITS ETF USD Accumulation</t>
+          <t>iShares Core MSCI World UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -492,7 +492,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Azionario globale</t>
+          <t>Azionario globale sviluppato</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -502,7 +502,7 @@
         <v>183.3</v>
       </c>
       <c r="G2" t="n">
-        <v>75.40000000000001</v>
+        <v>74</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -510,10 +510,10 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>12.97</v>
+        <v>13.21</v>
       </c>
       <c r="J2" t="n">
-        <v>-21.07</v>
+        <v>-21.63</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -524,12 +524,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SWDA.MI</t>
+          <t>EXSA.DE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>iShares Core MSCI World UCITS ETF USD (Acc)</t>
+          <t>iShares STOXX Europe 600 UCITS ETF (DE) EUR (Dist)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -539,7 +539,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Azionario globale sviluppato</t>
+          <t>Europa</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -549,7 +549,7 @@
         <v>183.3</v>
       </c>
       <c r="G3" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -557,10 +557,10 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>13.19</v>
+        <v>12.84</v>
       </c>
       <c r="J3" t="n">
-        <v>-21.63</v>
+        <v>-16.33</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -571,12 +571,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>SXR8.DE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>iShares STOXX Europe 600 UCITS ETF (DE) EUR (Dist)</t>
+          <t>iShares Core S&amp;P 500 UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -586,7 +586,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Europa</t>
+          <t>USA large cap</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -596,7 +596,7 @@
         <v>183.3</v>
       </c>
       <c r="G4" t="n">
-        <v>74.7</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -604,10 +604,10 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>12.83</v>
+        <v>14.2</v>
       </c>
       <c r="J4" t="n">
-        <v>-16.33</v>
+        <v>-23.32</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -643,7 +643,7 @@
         <v>66.7</v>
       </c>
       <c r="G5" t="n">
-        <v>71.59999999999999</v>
+        <v>71.8</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -690,7 +690,7 @@
         <v>66.7</v>
       </c>
       <c r="G6" t="n">
-        <v>53.7</v>
+        <v>51.7</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -698,7 +698,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>18.44</v>
+        <v>18.48</v>
       </c>
       <c r="J6" t="n">
         <v>-22.72</v>
@@ -780,7 +780,7 @@
         <v>75</v>
       </c>
       <c r="G8" t="n">
-        <v>83.3</v>
+        <v>83.2</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -827,7 +827,7 @@
         <v>75</v>
       </c>
       <c r="G9" t="n">
-        <v>73.40000000000001</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>12.89</v>
+        <v>12.9</v>
       </c>
       <c r="J9" t="n">
         <v>-20.6</v>
@@ -849,12 +849,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>RBOT.MI</t>
+          <t>SMH</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>iShares Automation &amp; Robotics UCITS ETF USD (Acc)</t>
+          <t>VanEck Semiconductor ETF</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -864,7 +864,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Robotica e automazione</t>
+          <t>Semiconduttori</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -874,7 +874,7 @@
         <v>33.3</v>
       </c>
       <c r="G10" t="n">
-        <v>64.8</v>
+        <v>64</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -882,26 +882,26 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>22.26</v>
+        <v>36.37</v>
       </c>
       <c r="J10" t="n">
-        <v>-29.37</v>
+        <v>-35.74</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
+          <t>Rischio elevato: usare solo come quota satellite e con size ridotta.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SMH</t>
+          <t>RBOT.MI</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>VanEck Semiconductor ETF</t>
+          <t>iShares Automation &amp; Robotics UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -911,7 +911,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Semiconduttori</t>
+          <t>Robotica e automazione</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -921,7 +921,7 @@
         <v>33.3</v>
       </c>
       <c r="G11" t="n">
-        <v>64.59999999999999</v>
+        <v>62.1</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -929,14 +929,14 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>36.37</v>
+        <v>22.26</v>
       </c>
       <c r="J11" t="n">
-        <v>-35.74</v>
+        <v>-29.37</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Rischio elevato: usare solo come quota satellite e con size ridotta.</t>
+          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
         </is>
       </c>
     </row>
@@ -968,15 +968,15 @@
         <v>33.3</v>
       </c>
       <c r="G12" t="n">
-        <v>55.5</v>
+        <v>49.9</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Hold / Monitor</t>
+          <t>High Risk</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>34.52</v>
+        <v>34.53</v>
       </c>
       <c r="J12" t="n">
         <v>-48.6</v>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>65.19</v>
+        <v>63.66</v>
       </c>
     </row>
     <row r="6">

--- a/ETF_Allocation_Model.xlsx
+++ b/ETF_Allocation_Model.xlsx
@@ -477,12 +477,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SWDA.MI</t>
+          <t>VWCE.DE</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>iShares Core MSCI World UCITS ETF USD (Acc)</t>
+          <t>Vanguard FTSE All-World UCITS ETF USD Accumulation</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -492,7 +492,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Azionario globale sviluppato</t>
+          <t>Azionario globale</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -502,7 +502,7 @@
         <v>183.3</v>
       </c>
       <c r="G2" t="n">
-        <v>74</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -510,10 +510,10 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>13.21</v>
+        <v>12.97</v>
       </c>
       <c r="J2" t="n">
-        <v>-21.63</v>
+        <v>-21.07</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -524,12 +524,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>SWDA.MI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>iShares STOXX Europe 600 UCITS ETF (DE) EUR (Dist)</t>
+          <t>iShares Core MSCI World UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -539,7 +539,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Europa</t>
+          <t>Azionario globale sviluppato</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -549,7 +549,7 @@
         <v>183.3</v>
       </c>
       <c r="G3" t="n">
-        <v>74</v>
+        <v>74.7</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -557,10 +557,10 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>12.84</v>
+        <v>13.2</v>
       </c>
       <c r="J3" t="n">
-        <v>-16.33</v>
+        <v>-21.63</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -571,12 +571,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SXR8.DE</t>
+          <t>EXSA.DE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>iShares Core S&amp;P 500 UCITS ETF USD (Acc)</t>
+          <t>iShares STOXX Europe 600 UCITS ETF (DE) EUR (Dist)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -586,7 +586,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>USA large cap</t>
+          <t>Europa</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -596,7 +596,7 @@
         <v>183.3</v>
       </c>
       <c r="G4" t="n">
-        <v>73.40000000000001</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -604,10 +604,10 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>14.2</v>
+        <v>12.84</v>
       </c>
       <c r="J4" t="n">
-        <v>-23.32</v>
+        <v>-16.33</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -643,7 +643,7 @@
         <v>66.7</v>
       </c>
       <c r="G5" t="n">
-        <v>71.8</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -690,7 +690,7 @@
         <v>66.7</v>
       </c>
       <c r="G6" t="n">
-        <v>51.7</v>
+        <v>52.3</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -698,7 +698,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>18.48</v>
+        <v>18.47</v>
       </c>
       <c r="J6" t="n">
         <v>-22.72</v>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>14.08</v>
+        <v>14.07</v>
       </c>
       <c r="J8" t="n">
         <v>-17.8</v>
@@ -827,7 +827,7 @@
         <v>75</v>
       </c>
       <c r="G9" t="n">
-        <v>72.59999999999999</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>12.9</v>
+        <v>12.89</v>
       </c>
       <c r="J9" t="n">
         <v>-20.6</v>
@@ -874,7 +874,7 @@
         <v>33.3</v>
       </c>
       <c r="G10" t="n">
-        <v>64</v>
+        <v>63.1</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>36.37</v>
+        <v>36.41</v>
       </c>
       <c r="J10" t="n">
         <v>-35.74</v>
@@ -921,7 +921,7 @@
         <v>33.3</v>
       </c>
       <c r="G11" t="n">
-        <v>62.1</v>
+        <v>62.4</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>22.26</v>
+        <v>22.25</v>
       </c>
       <c r="J11" t="n">
         <v>-29.37</v>
@@ -968,7 +968,7 @@
         <v>33.3</v>
       </c>
       <c r="G12" t="n">
-        <v>49.9</v>
+        <v>53.9</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -976,7 +976,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>34.53</v>
+        <v>34.55</v>
       </c>
       <c r="J12" t="n">
         <v>-48.6</v>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>63.66</v>
+        <v>63.95</v>
       </c>
     </row>
     <row r="6">

--- a/ETF_Allocation_Model.xlsx
+++ b/ETF_Allocation_Model.xlsx
@@ -477,12 +477,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>VWCE.DE</t>
+          <t>EXSA.DE</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Vanguard FTSE All-World UCITS ETF USD Accumulation</t>
+          <t>iShares STOXX Europe 600 UCITS ETF (DE) EUR (Dist)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -492,7 +492,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Azionario globale</t>
+          <t>Europa</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -502,7 +502,7 @@
         <v>183.3</v>
       </c>
       <c r="G2" t="n">
-        <v>74.90000000000001</v>
+        <v>74.5</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -510,10 +510,10 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>12.97</v>
+        <v>12.83</v>
       </c>
       <c r="J2" t="n">
-        <v>-21.07</v>
+        <v>-16.33</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -549,7 +549,7 @@
         <v>183.3</v>
       </c>
       <c r="G3" t="n">
-        <v>74.7</v>
+        <v>74.3</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>13.2</v>
+        <v>13.19</v>
       </c>
       <c r="J3" t="n">
         <v>-21.63</v>
@@ -571,12 +571,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>VWCE.DE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>iShares STOXX Europe 600 UCITS ETF (DE) EUR (Dist)</t>
+          <t>Vanguard FTSE All-World UCITS ETF USD Accumulation</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -586,7 +586,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Europa</t>
+          <t>Azionario globale</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -596,7 +596,7 @@
         <v>183.3</v>
       </c>
       <c r="G4" t="n">
-        <v>74.59999999999999</v>
+        <v>71</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -604,10 +604,10 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>12.84</v>
+        <v>12.97</v>
       </c>
       <c r="J4" t="n">
-        <v>-16.33</v>
+        <v>-21.07</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -643,7 +643,7 @@
         <v>66.7</v>
       </c>
       <c r="G5" t="n">
-        <v>72.59999999999999</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>9.57</v>
+        <v>9.59</v>
       </c>
       <c r="J5" t="n">
         <v>-12.85</v>
@@ -690,7 +690,7 @@
         <v>66.7</v>
       </c>
       <c r="G6" t="n">
-        <v>52.3</v>
+        <v>53</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -698,7 +698,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>18.47</v>
+        <v>18.48</v>
       </c>
       <c r="J6" t="n">
         <v>-22.72</v>
@@ -780,7 +780,7 @@
         <v>75</v>
       </c>
       <c r="G8" t="n">
-        <v>83.2</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -827,7 +827,7 @@
         <v>75</v>
       </c>
       <c r="G9" t="n">
-        <v>73.40000000000001</v>
+        <v>73</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>12.89</v>
+        <v>12.87</v>
       </c>
       <c r="J9" t="n">
         <v>-20.6</v>
@@ -874,7 +874,7 @@
         <v>33.3</v>
       </c>
       <c r="G10" t="n">
-        <v>63.1</v>
+        <v>62.4</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>36.41</v>
+        <v>36.53</v>
       </c>
       <c r="J10" t="n">
         <v>-35.74</v>
@@ -921,7 +921,7 @@
         <v>33.3</v>
       </c>
       <c r="G11" t="n">
-        <v>62.4</v>
+        <v>61.9</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>22.25</v>
+        <v>22.24</v>
       </c>
       <c r="J11" t="n">
         <v>-29.37</v>
@@ -968,15 +968,15 @@
         <v>33.3</v>
       </c>
       <c r="G12" t="n">
-        <v>53.9</v>
+        <v>55.3</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>High Risk</t>
+          <t>Hold / Monitor</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>34.55</v>
+        <v>34.66</v>
       </c>
       <c r="J12" t="n">
         <v>-48.6</v>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>63.95</v>
+        <v>63.27</v>
       </c>
     </row>
     <row r="6">

--- a/ETF_Allocation_Model.xlsx
+++ b/ETF_Allocation_Model.xlsx
@@ -502,7 +502,7 @@
         <v>183.3</v>
       </c>
       <c r="G2" t="n">
-        <v>74.5</v>
+        <v>75.2</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -549,7 +549,7 @@
         <v>183.3</v>
       </c>
       <c r="G3" t="n">
-        <v>74.3</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -571,12 +571,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>VWCE.DE</t>
+          <t>SXR8.DE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Vanguard FTSE All-World UCITS ETF USD Accumulation</t>
+          <t>iShares Core S&amp;P 500 UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -586,7 +586,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Azionario globale</t>
+          <t>USA large cap</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -596,7 +596,7 @@
         <v>183.3</v>
       </c>
       <c r="G4" t="n">
-        <v>71</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -604,10 +604,10 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>12.97</v>
+        <v>14.19</v>
       </c>
       <c r="J4" t="n">
-        <v>-21.07</v>
+        <v>-23.32</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -643,7 +643,7 @@
         <v>66.7</v>
       </c>
       <c r="G5" t="n">
-        <v>73.09999999999999</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>9.59</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="J5" t="n">
         <v>-12.85</v>
@@ -690,7 +690,7 @@
         <v>66.7</v>
       </c>
       <c r="G6" t="n">
-        <v>53</v>
+        <v>52.4</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -698,7 +698,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>18.48</v>
+        <v>18.5</v>
       </c>
       <c r="J6" t="n">
         <v>-22.72</v>
@@ -780,7 +780,7 @@
         <v>75</v>
       </c>
       <c r="G8" t="n">
-        <v>82.90000000000001</v>
+        <v>79.5</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -827,7 +827,7 @@
         <v>75</v>
       </c>
       <c r="G9" t="n">
-        <v>73</v>
+        <v>73.5</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -849,12 +849,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SMH</t>
+          <t>RBOT.MI</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>VanEck Semiconductor ETF</t>
+          <t>iShares Automation &amp; Robotics UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -864,7 +864,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Semiconduttori</t>
+          <t>Robotica e automazione</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -874,7 +874,7 @@
         <v>33.3</v>
       </c>
       <c r="G10" t="n">
-        <v>62.4</v>
+        <v>62.2</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -882,26 +882,26 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>36.53</v>
+        <v>22.24</v>
       </c>
       <c r="J10" t="n">
-        <v>-35.74</v>
+        <v>-29.37</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Rischio elevato: usare solo come quota satellite e con size ridotta.</t>
+          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>RBOT.MI</t>
+          <t>SMH</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>iShares Automation &amp; Robotics UCITS ETF USD (Acc)</t>
+          <t>VanEck Semiconductor ETF</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -911,7 +911,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Robotica e automazione</t>
+          <t>Semiconduttori</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -921,7 +921,7 @@
         <v>33.3</v>
       </c>
       <c r="G11" t="n">
-        <v>61.9</v>
+        <v>60.9</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -929,14 +929,14 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>22.24</v>
+        <v>36.48</v>
       </c>
       <c r="J11" t="n">
-        <v>-29.37</v>
+        <v>-35.74</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
+          <t>Rischio elevato: usare solo come quota satellite e con size ridotta.</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
         <v>33.3</v>
       </c>
       <c r="G12" t="n">
-        <v>55.3</v>
+        <v>55.4</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -976,7 +976,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>34.66</v>
+        <v>34.69</v>
       </c>
       <c r="J12" t="n">
         <v>-48.6</v>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>63.27</v>
+        <v>63.12</v>
       </c>
     </row>
     <row r="6">

--- a/ETF_Allocation_Model.xlsx
+++ b/ETF_Allocation_Model.xlsx
@@ -502,7 +502,7 @@
         <v>183.3</v>
       </c>
       <c r="G2" t="n">
-        <v>75.2</v>
+        <v>74.5</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -549,7 +549,7 @@
         <v>183.3</v>
       </c>
       <c r="G3" t="n">
-        <v>74.59999999999999</v>
+        <v>73.8</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>13.19</v>
+        <v>13.2</v>
       </c>
       <c r="J3" t="n">
         <v>-21.63</v>
@@ -571,12 +571,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SXR8.DE</t>
+          <t>VWCE.DE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>iShares Core S&amp;P 500 UCITS ETF USD (Acc)</t>
+          <t>Vanguard FTSE All-World UCITS ETF USD Accumulation</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -586,7 +586,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>USA large cap</t>
+          <t>Azionario globale</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -596,7 +596,7 @@
         <v>183.3</v>
       </c>
       <c r="G4" t="n">
-        <v>73.59999999999999</v>
+        <v>70</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -604,10 +604,10 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>14.19</v>
+        <v>12.98</v>
       </c>
       <c r="J4" t="n">
-        <v>-23.32</v>
+        <v>-21.07</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -643,7 +643,7 @@
         <v>66.7</v>
       </c>
       <c r="G5" t="n">
-        <v>74.09999999999999</v>
+        <v>74</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -690,7 +690,7 @@
         <v>66.7</v>
       </c>
       <c r="G6" t="n">
-        <v>52.4</v>
+        <v>51.1</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>75</v>
       </c>
       <c r="G8" t="n">
-        <v>79.5</v>
+        <v>79.2</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -827,7 +827,7 @@
         <v>75</v>
       </c>
       <c r="G9" t="n">
-        <v>73.5</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>12.87</v>
+        <v>12.88</v>
       </c>
       <c r="J9" t="n">
         <v>-20.6</v>
@@ -874,7 +874,7 @@
         <v>33.3</v>
       </c>
       <c r="G10" t="n">
-        <v>62.2</v>
+        <v>60.7</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -921,7 +921,7 @@
         <v>33.3</v>
       </c>
       <c r="G11" t="n">
-        <v>60.9</v>
+        <v>57.7</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>36.48</v>
+        <v>36.56</v>
       </c>
       <c r="J11" t="n">
         <v>-35.74</v>
@@ -968,15 +968,15 @@
         <v>33.3</v>
       </c>
       <c r="G12" t="n">
-        <v>55.4</v>
+        <v>54.9</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Hold / Monitor</t>
+          <t>High Risk</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>34.69</v>
+        <v>34.64</v>
       </c>
       <c r="J12" t="n">
         <v>-48.6</v>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>63.12</v>
+        <v>61.79</v>
       </c>
     </row>
     <row r="6">

--- a/ETF_Allocation_Model.xlsx
+++ b/ETF_Allocation_Model.xlsx
@@ -502,7 +502,7 @@
         <v>183.3</v>
       </c>
       <c r="G2" t="n">
-        <v>74.5</v>
+        <v>75.3</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -524,12 +524,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SWDA.MI</t>
+          <t>VWCE.DE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>iShares Core MSCI World UCITS ETF USD (Acc)</t>
+          <t>Vanguard FTSE All-World UCITS ETF USD Accumulation</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -539,7 +539,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Azionario globale sviluppato</t>
+          <t>Azionario globale</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -549,7 +549,7 @@
         <v>183.3</v>
       </c>
       <c r="G3" t="n">
-        <v>73.8</v>
+        <v>69.8</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -557,10 +557,10 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>13.2</v>
+        <v>12.97</v>
       </c>
       <c r="J3" t="n">
-        <v>-21.63</v>
+        <v>-21.07</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -571,12 +571,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>VWCE.DE</t>
+          <t>SWDA.MI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Vanguard FTSE All-World UCITS ETF USD Accumulation</t>
+          <t>iShares Core MSCI World UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -586,7 +586,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Azionario globale</t>
+          <t>Azionario globale sviluppato</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -596,7 +596,7 @@
         <v>183.3</v>
       </c>
       <c r="G4" t="n">
-        <v>70</v>
+        <v>69.7</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -604,10 +604,10 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>12.98</v>
+        <v>13.19</v>
       </c>
       <c r="J4" t="n">
-        <v>-21.07</v>
+        <v>-21.63</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -643,7 +643,7 @@
         <v>66.7</v>
       </c>
       <c r="G5" t="n">
-        <v>74</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>9.619999999999999</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="J5" t="n">
         <v>-12.85</v>
@@ -690,7 +690,7 @@
         <v>66.7</v>
       </c>
       <c r="G6" t="n">
-        <v>51.1</v>
+        <v>52.5</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -698,7 +698,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>18.5</v>
+        <v>18.49</v>
       </c>
       <c r="J6" t="n">
         <v>-22.72</v>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>14.07</v>
+        <v>14.06</v>
       </c>
       <c r="J8" t="n">
         <v>-17.8</v>
@@ -827,7 +827,7 @@
         <v>75</v>
       </c>
       <c r="G9" t="n">
-        <v>72.90000000000001</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -874,7 +874,7 @@
         <v>33.3</v>
       </c>
       <c r="G10" t="n">
-        <v>60.7</v>
+        <v>62.5</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -921,7 +921,7 @@
         <v>33.3</v>
       </c>
       <c r="G11" t="n">
-        <v>57.7</v>
+        <v>61.8</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>36.56</v>
+        <v>36.78</v>
       </c>
       <c r="J11" t="n">
         <v>-35.74</v>
@@ -968,7 +968,7 @@
         <v>33.3</v>
       </c>
       <c r="G12" t="n">
-        <v>54.9</v>
+        <v>53.7</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -976,7 +976,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>34.64</v>
+        <v>34.67</v>
       </c>
       <c r="J12" t="n">
         <v>-48.6</v>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>61.79</v>
+        <v>61.99</v>
       </c>
     </row>
     <row r="6">

--- a/ETF_Allocation_Model.xlsx
+++ b/ETF_Allocation_Model.xlsx
@@ -502,7 +502,7 @@
         <v>183.3</v>
       </c>
       <c r="G2" t="n">
-        <v>75.3</v>
+        <v>74.7</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -510,7 +510,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>12.83</v>
+        <v>12.82</v>
       </c>
       <c r="J2" t="n">
         <v>-16.33</v>
@@ -596,7 +596,7 @@
         <v>183.3</v>
       </c>
       <c r="G4" t="n">
-        <v>69.7</v>
+        <v>69.8</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -643,7 +643,7 @@
         <v>66.7</v>
       </c>
       <c r="G5" t="n">
-        <v>72.40000000000001</v>
+        <v>72.5</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>9.720000000000001</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="J5" t="n">
         <v>-12.85</v>
@@ -690,7 +690,7 @@
         <v>66.7</v>
       </c>
       <c r="G6" t="n">
-        <v>52.5</v>
+        <v>51.6</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -698,7 +698,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>18.49</v>
+        <v>18.5</v>
       </c>
       <c r="J6" t="n">
         <v>-22.72</v>
@@ -780,11 +780,11 @@
         <v>75</v>
       </c>
       <c r="G8" t="n">
-        <v>79.2</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Buy Watchlist</t>
+          <t>Accumulate Carefully</t>
         </is>
       </c>
       <c r="I8" t="n">
@@ -795,7 +795,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>ETF forte e in trend favorevole; valutare solo con coerenza di portafoglio.</t>
+          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
         <v>75</v>
       </c>
       <c r="G9" t="n">
-        <v>72.40000000000001</v>
+        <v>72.2</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>12.88</v>
+        <v>12.87</v>
       </c>
       <c r="J9" t="n">
         <v>-20.6</v>
@@ -874,7 +874,7 @@
         <v>33.3</v>
       </c>
       <c r="G10" t="n">
-        <v>62.5</v>
+        <v>62.4</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -921,7 +921,7 @@
         <v>33.3</v>
       </c>
       <c r="G11" t="n">
-        <v>61.8</v>
+        <v>61.4</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>36.78</v>
+        <v>36.75</v>
       </c>
       <c r="J11" t="n">
         <v>-35.74</v>
@@ -968,7 +968,7 @@
         <v>33.3</v>
       </c>
       <c r="G12" t="n">
-        <v>53.7</v>
+        <v>53.6</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -976,7 +976,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>34.67</v>
+        <v>34.66</v>
       </c>
       <c r="J12" t="n">
         <v>-48.6</v>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>61.99</v>
+        <v>61.74</v>
       </c>
     </row>
     <row r="6">

--- a/ETF_Allocation_Model.xlsx
+++ b/ETF_Allocation_Model.xlsx
@@ -502,7 +502,7 @@
         <v>183.3</v>
       </c>
       <c r="G2" t="n">
-        <v>74.7</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -510,7 +510,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>12.82</v>
+        <v>12.8</v>
       </c>
       <c r="J2" t="n">
         <v>-16.33</v>
@@ -549,7 +549,7 @@
         <v>183.3</v>
       </c>
       <c r="G3" t="n">
-        <v>69.8</v>
+        <v>74</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>12.97</v>
+        <v>12.98</v>
       </c>
       <c r="J3" t="n">
         <v>-21.07</v>
@@ -596,7 +596,7 @@
         <v>183.3</v>
       </c>
       <c r="G4" t="n">
-        <v>69.8</v>
+        <v>74</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>13.19</v>
+        <v>13.21</v>
       </c>
       <c r="J4" t="n">
         <v>-21.63</v>
@@ -643,7 +643,7 @@
         <v>66.7</v>
       </c>
       <c r="G5" t="n">
-        <v>72.5</v>
+        <v>72.8</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -690,7 +690,7 @@
         <v>66.7</v>
       </c>
       <c r="G6" t="n">
-        <v>51.6</v>
+        <v>51.8</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -698,7 +698,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>18.5</v>
+        <v>18.52</v>
       </c>
       <c r="J6" t="n">
         <v>-22.72</v>
@@ -780,7 +780,7 @@
         <v>75</v>
       </c>
       <c r="G8" t="n">
-        <v>77.90000000000001</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>14.06</v>
+        <v>14.05</v>
       </c>
       <c r="J8" t="n">
         <v>-17.8</v>
@@ -827,7 +827,7 @@
         <v>75</v>
       </c>
       <c r="G9" t="n">
-        <v>72.2</v>
+        <v>72.8</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>12.87</v>
+        <v>12.89</v>
       </c>
       <c r="J9" t="n">
         <v>-20.6</v>
@@ -874,7 +874,7 @@
         <v>33.3</v>
       </c>
       <c r="G10" t="n">
-        <v>62.4</v>
+        <v>63.5</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>22.24</v>
+        <v>22.25</v>
       </c>
       <c r="J10" t="n">
         <v>-29.37</v>
@@ -921,7 +921,7 @@
         <v>33.3</v>
       </c>
       <c r="G11" t="n">
-        <v>61.4</v>
+        <v>62.4</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>36.75</v>
+        <v>36.76</v>
       </c>
       <c r="J11" t="n">
         <v>-35.74</v>
@@ -968,7 +968,7 @@
         <v>33.3</v>
       </c>
       <c r="G12" t="n">
-        <v>53.6</v>
+        <v>54.3</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -976,7 +976,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>34.66</v>
+        <v>34.71</v>
       </c>
       <c r="J12" t="n">
         <v>-48.6</v>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>61.74</v>
+        <v>63.16</v>
       </c>
     </row>
     <row r="6">

--- a/ETF_Allocation_Model.xlsx
+++ b/ETF_Allocation_Model.xlsx
@@ -502,7 +502,7 @@
         <v>183.3</v>
       </c>
       <c r="G2" t="n">
-        <v>74.90000000000001</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -510,7 +510,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>12.8</v>
+        <v>12.83</v>
       </c>
       <c r="J2" t="n">
         <v>-16.33</v>
@@ -549,7 +549,7 @@
         <v>183.3</v>
       </c>
       <c r="G3" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>12.98</v>
+        <v>13.06</v>
       </c>
       <c r="J3" t="n">
         <v>-21.07</v>
@@ -596,7 +596,7 @@
         <v>183.3</v>
       </c>
       <c r="G4" t="n">
-        <v>74</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>13.21</v>
+        <v>13.29</v>
       </c>
       <c r="J4" t="n">
         <v>-21.63</v>
@@ -643,7 +643,7 @@
         <v>66.7</v>
       </c>
       <c r="G5" t="n">
-        <v>72.8</v>
+        <v>73</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>9.710000000000001</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="J5" t="n">
         <v>-12.85</v>
@@ -690,7 +690,7 @@
         <v>66.7</v>
       </c>
       <c r="G6" t="n">
-        <v>51.8</v>
+        <v>52.8</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -698,7 +698,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>18.52</v>
+        <v>18.53</v>
       </c>
       <c r="J6" t="n">
         <v>-22.72</v>
@@ -780,22 +780,22 @@
         <v>75</v>
       </c>
       <c r="G8" t="n">
-        <v>77.59999999999999</v>
+        <v>82.7</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Accumulate Carefully</t>
+          <t>Buy Watchlist</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>14.05</v>
+        <v>14.12</v>
       </c>
       <c r="J8" t="n">
         <v>-17.8</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
+          <t>ETF forte e in trend favorevole; valutare solo con coerenza di portafoglio.</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
         <v>75</v>
       </c>
       <c r="G9" t="n">
-        <v>72.8</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>12.89</v>
+        <v>12.95</v>
       </c>
       <c r="J9" t="n">
         <v>-20.6</v>
@@ -874,15 +874,15 @@
         <v>33.3</v>
       </c>
       <c r="G10" t="n">
-        <v>63.5</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Hold / Monitor</t>
+          <t>Accumulate Carefully</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>22.25</v>
+        <v>22.46</v>
       </c>
       <c r="J10" t="n">
         <v>-29.37</v>
@@ -921,7 +921,7 @@
         <v>33.3</v>
       </c>
       <c r="G11" t="n">
-        <v>62.4</v>
+        <v>63.7</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>36.76</v>
+        <v>36.89</v>
       </c>
       <c r="J11" t="n">
         <v>-35.74</v>
@@ -968,7 +968,7 @@
         <v>33.3</v>
       </c>
       <c r="G12" t="n">
-        <v>54.3</v>
+        <v>52.9</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -976,7 +976,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>34.71</v>
+        <v>34.86</v>
       </c>
       <c r="J12" t="n">
         <v>-48.6</v>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>63.16</v>
+        <v>64.64</v>
       </c>
     </row>
     <row r="6">

--- a/ETF_Allocation_Model.xlsx
+++ b/ETF_Allocation_Model.xlsx
@@ -502,7 +502,7 @@
         <v>183.3</v>
       </c>
       <c r="G2" t="n">
-        <v>75.40000000000001</v>
+        <v>75.7</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -510,7 +510,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>12.83</v>
+        <v>12.82</v>
       </c>
       <c r="J2" t="n">
         <v>-16.33</v>
@@ -549,7 +549,7 @@
         <v>183.3</v>
       </c>
       <c r="G3" t="n">
-        <v>75</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>13.06</v>
+        <v>13.02</v>
       </c>
       <c r="J3" t="n">
         <v>-21.07</v>
@@ -596,7 +596,7 @@
         <v>183.3</v>
       </c>
       <c r="G4" t="n">
-        <v>74.90000000000001</v>
+        <v>75.3</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>13.29</v>
+        <v>13.25</v>
       </c>
       <c r="J4" t="n">
         <v>-21.63</v>
@@ -643,7 +643,7 @@
         <v>66.7</v>
       </c>
       <c r="G5" t="n">
-        <v>73</v>
+        <v>73.2</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -690,15 +690,15 @@
         <v>66.7</v>
       </c>
       <c r="G6" t="n">
-        <v>52.8</v>
+        <v>58</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Avoid for Now</t>
+          <t>Hold / Monitor</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>18.53</v>
+        <v>18.75</v>
       </c>
       <c r="J6" t="n">
         <v>-22.72</v>
@@ -780,7 +780,7 @@
         <v>75</v>
       </c>
       <c r="G8" t="n">
-        <v>82.7</v>
+        <v>82.8</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>14.12</v>
+        <v>14.11</v>
       </c>
       <c r="J8" t="n">
         <v>-17.8</v>
@@ -827,7 +827,7 @@
         <v>75</v>
       </c>
       <c r="G9" t="n">
-        <v>73.59999999999999</v>
+        <v>74</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>12.95</v>
+        <v>12.92</v>
       </c>
       <c r="J9" t="n">
         <v>-20.6</v>
@@ -874,7 +874,7 @@
         <v>33.3</v>
       </c>
       <c r="G10" t="n">
-        <v>69.40000000000001</v>
+        <v>70</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>22.46</v>
+        <v>22.38</v>
       </c>
       <c r="J10" t="n">
         <v>-29.37</v>
@@ -921,7 +921,7 @@
         <v>33.3</v>
       </c>
       <c r="G11" t="n">
-        <v>63.7</v>
+        <v>63.5</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>36.89</v>
+        <v>36.87</v>
       </c>
       <c r="J11" t="n">
         <v>-35.74</v>
@@ -968,7 +968,7 @@
         <v>33.3</v>
       </c>
       <c r="G12" t="n">
-        <v>52.9</v>
+        <v>52.3</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -976,7 +976,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>34.86</v>
+        <v>34.77</v>
       </c>
       <c r="J12" t="n">
         <v>-48.6</v>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>64.64</v>
+        <v>65.11</v>
       </c>
     </row>
     <row r="6">

--- a/ETF_Allocation_Model.xlsx
+++ b/ETF_Allocation_Model.xlsx
@@ -502,7 +502,7 @@
         <v>183.3</v>
       </c>
       <c r="G2" t="n">
-        <v>75.7</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -510,7 +510,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>12.82</v>
+        <v>12.81</v>
       </c>
       <c r="J2" t="n">
         <v>-16.33</v>
@@ -524,12 +524,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>VWCE.DE</t>
+          <t>SWDA.MI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Vanguard FTSE All-World UCITS ETF USD Accumulation</t>
+          <t>iShares Core MSCI World UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -539,7 +539,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Azionario globale</t>
+          <t>Azionario globale sviluppato</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -557,10 +557,10 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>13.02</v>
+        <v>13.23</v>
       </c>
       <c r="J3" t="n">
-        <v>-21.07</v>
+        <v>-21.63</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -571,12 +571,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SWDA.MI</t>
+          <t>VWCE.DE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>iShares Core MSCI World UCITS ETF USD (Acc)</t>
+          <t>Vanguard FTSE All-World UCITS ETF USD Accumulation</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -586,7 +586,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Azionario globale sviluppato</t>
+          <t>Azionario globale</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -596,7 +596,7 @@
         <v>183.3</v>
       </c>
       <c r="G4" t="n">
-        <v>75.3</v>
+        <v>75.5</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -604,10 +604,10 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>13.25</v>
+        <v>13</v>
       </c>
       <c r="J4" t="n">
-        <v>-21.63</v>
+        <v>-21.07</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>9.720000000000001</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="J5" t="n">
         <v>-12.85</v>
@@ -690,7 +690,7 @@
         <v>66.7</v>
       </c>
       <c r="G6" t="n">
-        <v>58</v>
+        <v>58.3</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -698,7 +698,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>18.75</v>
+        <v>18.66</v>
       </c>
       <c r="J6" t="n">
         <v>-22.72</v>
@@ -780,7 +780,7 @@
         <v>75</v>
       </c>
       <c r="G8" t="n">
-        <v>82.8</v>
+        <v>82.5</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>14.11</v>
+        <v>14.09</v>
       </c>
       <c r="J8" t="n">
         <v>-17.8</v>
@@ -827,7 +827,7 @@
         <v>75</v>
       </c>
       <c r="G9" t="n">
-        <v>74</v>
+        <v>74.3</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>12.92</v>
+        <v>12.9</v>
       </c>
       <c r="J9" t="n">
         <v>-20.6</v>
@@ -874,7 +874,7 @@
         <v>33.3</v>
       </c>
       <c r="G10" t="n">
-        <v>70</v>
+        <v>70.3</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>22.38</v>
+        <v>22.34</v>
       </c>
       <c r="J10" t="n">
         <v>-29.37</v>
@@ -921,7 +921,7 @@
         <v>33.3</v>
       </c>
       <c r="G11" t="n">
-        <v>63.5</v>
+        <v>63.6</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>36.87</v>
+        <v>36.84</v>
       </c>
       <c r="J11" t="n">
         <v>-35.74</v>
@@ -968,7 +968,7 @@
         <v>33.3</v>
       </c>
       <c r="G12" t="n">
-        <v>52.3</v>
+        <v>52.6</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -976,7 +976,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>34.77</v>
+        <v>34.71</v>
       </c>
       <c r="J12" t="n">
         <v>-48.6</v>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>65.11</v>
+        <v>65.23999999999999</v>
       </c>
     </row>
     <row r="6">

--- a/ETF_Allocation_Model.xlsx
+++ b/ETF_Allocation_Model.xlsx
@@ -502,7 +502,7 @@
         <v>183.3</v>
       </c>
       <c r="G2" t="n">
-        <v>76.09999999999999</v>
+        <v>76.5</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -510,7 +510,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>12.81</v>
+        <v>12.79</v>
       </c>
       <c r="J2" t="n">
         <v>-16.33</v>
@@ -524,12 +524,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SWDA.MI</t>
+          <t>VWCE.DE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>iShares Core MSCI World UCITS ETF USD (Acc)</t>
+          <t>Vanguard FTSE All-World UCITS ETF USD Accumulation</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -539,7 +539,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Azionario globale sviluppato</t>
+          <t>Azionario globale</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -549,7 +549,7 @@
         <v>183.3</v>
       </c>
       <c r="G3" t="n">
-        <v>75.59999999999999</v>
+        <v>76</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -557,10 +557,10 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>13.23</v>
+        <v>12.99</v>
       </c>
       <c r="J3" t="n">
-        <v>-21.63</v>
+        <v>-21.07</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -571,12 +571,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>VWCE.DE</t>
+          <t>SWDA.MI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Vanguard FTSE All-World UCITS ETF USD Accumulation</t>
+          <t>iShares Core MSCI World UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -586,7 +586,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Azionario globale</t>
+          <t>Azionario globale sviluppato</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -596,7 +596,7 @@
         <v>183.3</v>
       </c>
       <c r="G4" t="n">
-        <v>75.5</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -604,10 +604,10 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>13</v>
+        <v>13.21</v>
       </c>
       <c r="J4" t="n">
-        <v>-21.07</v>
+        <v>-21.63</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -643,7 +643,7 @@
         <v>66.7</v>
       </c>
       <c r="G5" t="n">
-        <v>73.2</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -690,7 +690,7 @@
         <v>66.7</v>
       </c>
       <c r="G6" t="n">
-        <v>58.3</v>
+        <v>59.8</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -698,7 +698,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>18.66</v>
+        <v>18.67</v>
       </c>
       <c r="J6" t="n">
         <v>-22.72</v>
@@ -780,7 +780,7 @@
         <v>75</v>
       </c>
       <c r="G8" t="n">
-        <v>82.5</v>
+        <v>82.2</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>14.09</v>
+        <v>14.07</v>
       </c>
       <c r="J8" t="n">
         <v>-17.8</v>
@@ -827,7 +827,7 @@
         <v>75</v>
       </c>
       <c r="G9" t="n">
-        <v>74.3</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>12.9</v>
+        <v>12.88</v>
       </c>
       <c r="J9" t="n">
         <v>-20.6</v>
@@ -874,7 +874,7 @@
         <v>33.3</v>
       </c>
       <c r="G10" t="n">
-        <v>70.3</v>
+        <v>71.2</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>22.34</v>
+        <v>22.32</v>
       </c>
       <c r="J10" t="n">
         <v>-29.37</v>
@@ -921,7 +921,7 @@
         <v>33.3</v>
       </c>
       <c r="G11" t="n">
-        <v>63.6</v>
+        <v>64</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>36.84</v>
+        <v>36.83</v>
       </c>
       <c r="J11" t="n">
         <v>-35.74</v>
@@ -968,7 +968,7 @@
         <v>33.3</v>
       </c>
       <c r="G12" t="n">
-        <v>52.6</v>
+        <v>52.2</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -976,7 +976,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>34.71</v>
+        <v>34.74</v>
       </c>
       <c r="J12" t="n">
         <v>-48.6</v>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>65.23999999999999</v>
+        <v>65.59</v>
       </c>
     </row>
     <row r="6">

--- a/ETF_Allocation_Model.xlsx
+++ b/ETF_Allocation_Model.xlsx
@@ -502,7 +502,7 @@
         <v>183.3</v>
       </c>
       <c r="G2" t="n">
-        <v>76.5</v>
+        <v>76</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -510,7 +510,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>12.79</v>
+        <v>12.8</v>
       </c>
       <c r="J2" t="n">
         <v>-16.33</v>
@@ -549,7 +549,7 @@
         <v>183.3</v>
       </c>
       <c r="G3" t="n">
-        <v>76</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>12.99</v>
+        <v>13</v>
       </c>
       <c r="J3" t="n">
         <v>-21.07</v>
@@ -596,7 +596,7 @@
         <v>183.3</v>
       </c>
       <c r="G4" t="n">
-        <v>75.90000000000001</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>13.21</v>
+        <v>13.23</v>
       </c>
       <c r="J4" t="n">
         <v>-21.63</v>
@@ -643,7 +643,7 @@
         <v>66.7</v>
       </c>
       <c r="G5" t="n">
-        <v>73.90000000000001</v>
+        <v>74</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>9.710000000000001</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="J5" t="n">
         <v>-12.85</v>
@@ -690,7 +690,7 @@
         <v>66.7</v>
       </c>
       <c r="G6" t="n">
-        <v>59.8</v>
+        <v>59.4</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -698,7 +698,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>18.67</v>
+        <v>18.69</v>
       </c>
       <c r="J6" t="n">
         <v>-22.72</v>
@@ -780,7 +780,7 @@
         <v>75</v>
       </c>
       <c r="G8" t="n">
-        <v>82.2</v>
+        <v>81.3</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>14.07</v>
+        <v>14.08</v>
       </c>
       <c r="J8" t="n">
         <v>-17.8</v>
@@ -827,7 +827,7 @@
         <v>75</v>
       </c>
       <c r="G9" t="n">
-        <v>74.40000000000001</v>
+        <v>74.2</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>12.88</v>
+        <v>12.9</v>
       </c>
       <c r="J9" t="n">
         <v>-20.6</v>
@@ -874,7 +874,7 @@
         <v>33.3</v>
       </c>
       <c r="G10" t="n">
-        <v>71.2</v>
+        <v>70.5</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>22.32</v>
+        <v>22.33</v>
       </c>
       <c r="J10" t="n">
         <v>-29.37</v>
@@ -921,7 +921,7 @@
         <v>33.3</v>
       </c>
       <c r="G11" t="n">
-        <v>64</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>36.83</v>
+        <v>36.85</v>
       </c>
       <c r="J11" t="n">
         <v>-35.74</v>
@@ -968,7 +968,7 @@
         <v>33.3</v>
       </c>
       <c r="G12" t="n">
-        <v>52.2</v>
+        <v>50.7</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -976,7 +976,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>34.74</v>
+        <v>34.79</v>
       </c>
       <c r="J12" t="n">
         <v>-48.6</v>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>65.59</v>
+        <v>64.95</v>
       </c>
     </row>
     <row r="6">

--- a/ETF_Allocation_Model.xlsx
+++ b/ETF_Allocation_Model.xlsx
@@ -502,7 +502,7 @@
         <v>183.3</v>
       </c>
       <c r="G2" t="n">
-        <v>76</v>
+        <v>75.8</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -510,7 +510,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>12.8</v>
+        <v>12.78</v>
       </c>
       <c r="J2" t="n">
         <v>-16.33</v>
@@ -549,7 +549,7 @@
         <v>183.3</v>
       </c>
       <c r="G3" t="n">
-        <v>75.40000000000001</v>
+        <v>75</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>13</v>
+        <v>12.99</v>
       </c>
       <c r="J3" t="n">
         <v>-21.07</v>
@@ -596,7 +596,7 @@
         <v>183.3</v>
       </c>
       <c r="G4" t="n">
-        <v>75.40000000000001</v>
+        <v>75</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>13.23</v>
+        <v>13.22</v>
       </c>
       <c r="J4" t="n">
         <v>-21.63</v>
@@ -643,7 +643,7 @@
         <v>66.7</v>
       </c>
       <c r="G5" t="n">
-        <v>74</v>
+        <v>73.5</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -690,7 +690,7 @@
         <v>66.7</v>
       </c>
       <c r="G6" t="n">
-        <v>59.4</v>
+        <v>59.5</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>75</v>
       </c>
       <c r="G8" t="n">
-        <v>81.3</v>
+        <v>80.7</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -827,7 +827,7 @@
         <v>75</v>
       </c>
       <c r="G9" t="n">
-        <v>74.2</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>12.9</v>
+        <v>12.89</v>
       </c>
       <c r="J9" t="n">
         <v>-20.6</v>
@@ -874,7 +874,7 @@
         <v>33.3</v>
       </c>
       <c r="G10" t="n">
-        <v>70.5</v>
+        <v>70.2</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>22.33</v>
+        <v>22.32</v>
       </c>
       <c r="J10" t="n">
         <v>-29.37</v>
@@ -921,7 +921,7 @@
         <v>33.3</v>
       </c>
       <c r="G11" t="n">
-        <v>64.09999999999999</v>
+        <v>63.5</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>36.85</v>
+        <v>36.84</v>
       </c>
       <c r="J11" t="n">
         <v>-35.74</v>
@@ -968,7 +968,7 @@
         <v>33.3</v>
       </c>
       <c r="G12" t="n">
-        <v>50.7</v>
+        <v>50.3</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>64.95</v>
+        <v>64.76000000000001</v>
       </c>
     </row>
     <row r="6">

--- a/ETF_Allocation_Model.xlsx
+++ b/ETF_Allocation_Model.xlsx
@@ -510,7 +510,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>12.78</v>
+        <v>12.79</v>
       </c>
       <c r="J2" t="n">
         <v>-16.33</v>
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>12.99</v>
+        <v>13</v>
       </c>
       <c r="J3" t="n">
         <v>-21.07</v>
@@ -596,7 +596,7 @@
         <v>183.3</v>
       </c>
       <c r="G4" t="n">
-        <v>75</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>13.22</v>
+        <v>13.23</v>
       </c>
       <c r="J4" t="n">
         <v>-21.63</v>
@@ -643,7 +643,7 @@
         <v>66.7</v>
       </c>
       <c r="G5" t="n">
-        <v>73.5</v>
+        <v>73.3</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -698,7 +698,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>18.69</v>
+        <v>18.72</v>
       </c>
       <c r="J6" t="n">
         <v>-22.72</v>
@@ -780,7 +780,7 @@
         <v>75</v>
       </c>
       <c r="G8" t="n">
-        <v>80.7</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>14.08</v>
+        <v>14.1</v>
       </c>
       <c r="J8" t="n">
         <v>-17.8</v>
@@ -827,7 +827,7 @@
         <v>75</v>
       </c>
       <c r="G9" t="n">
-        <v>73.90000000000001</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -874,7 +874,7 @@
         <v>33.3</v>
       </c>
       <c r="G10" t="n">
-        <v>70.2</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>22.32</v>
+        <v>22.35</v>
       </c>
       <c r="J10" t="n">
         <v>-29.37</v>
@@ -921,7 +921,7 @@
         <v>33.3</v>
       </c>
       <c r="G11" t="n">
-        <v>63.5</v>
+        <v>64.5</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>36.84</v>
+        <v>36.82</v>
       </c>
       <c r="J11" t="n">
         <v>-35.74</v>
@@ -968,7 +968,7 @@
         <v>33.3</v>
       </c>
       <c r="G12" t="n">
-        <v>50.3</v>
+        <v>51.3</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -976,7 +976,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>34.79</v>
+        <v>34.81</v>
       </c>
       <c r="J12" t="n">
         <v>-48.6</v>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>64.76000000000001</v>
+        <v>65.33</v>
       </c>
     </row>
     <row r="6">

--- a/ETF_Allocation_Model.xlsx
+++ b/ETF_Allocation_Model.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Suggested_Allocation" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Suggested_Allocation" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -502,7 +502,7 @@
         <v>183.3</v>
       </c>
       <c r="G2" t="n">
-        <v>75.8</v>
+        <v>76.5</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -510,7 +510,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>12.79</v>
+        <v>12.78</v>
       </c>
       <c r="J2" t="n">
         <v>-16.33</v>
@@ -549,7 +549,7 @@
         <v>183.3</v>
       </c>
       <c r="G3" t="n">
-        <v>75</v>
+        <v>75.7</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -596,7 +596,7 @@
         <v>183.3</v>
       </c>
       <c r="G4" t="n">
-        <v>74.90000000000001</v>
+        <v>75.5</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>13.23</v>
+        <v>13.22</v>
       </c>
       <c r="J4" t="n">
         <v>-21.63</v>
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>9.720000000000001</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="J5" t="n">
         <v>-12.85</v>
@@ -690,7 +690,7 @@
         <v>66.7</v>
       </c>
       <c r="G6" t="n">
-        <v>59.5</v>
+        <v>60.2</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -698,7 +698,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>18.72</v>
+        <v>18.69</v>
       </c>
       <c r="J6" t="n">
         <v>-22.72</v>
@@ -780,7 +780,7 @@
         <v>75</v>
       </c>
       <c r="G8" t="n">
-        <v>81.59999999999999</v>
+        <v>82.8</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>14.1</v>
+        <v>14.12</v>
       </c>
       <c r="J8" t="n">
         <v>-17.8</v>
@@ -827,7 +827,7 @@
         <v>75</v>
       </c>
       <c r="G9" t="n">
-        <v>73.59999999999999</v>
+        <v>74</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>12.89</v>
+        <v>12.88</v>
       </c>
       <c r="J9" t="n">
         <v>-20.6</v>
@@ -874,7 +874,7 @@
         <v>33.3</v>
       </c>
       <c r="G10" t="n">
-        <v>70.40000000000001</v>
+        <v>71.5</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -921,7 +921,7 @@
         <v>33.3</v>
       </c>
       <c r="G11" t="n">
-        <v>64.5</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>36.82</v>
+        <v>36.8</v>
       </c>
       <c r="J11" t="n">
         <v>-35.74</v>
@@ -968,7 +968,7 @@
         <v>33.3</v>
       </c>
       <c r="G12" t="n">
-        <v>51.3</v>
+        <v>51.2</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -976,7 +976,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>34.81</v>
+        <v>34.79</v>
       </c>
       <c r="J12" t="n">
         <v>-48.6</v>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>65.33</v>
+        <v>65.86</v>
       </c>
     </row>
     <row r="6">

--- a/ETF_Allocation_Model.xlsx
+++ b/ETF_Allocation_Model.xlsx
@@ -502,7 +502,7 @@
         <v>183.3</v>
       </c>
       <c r="G2" t="n">
-        <v>76.5</v>
+        <v>76</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -510,7 +510,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>12.78</v>
+        <v>12.77</v>
       </c>
       <c r="J2" t="n">
         <v>-16.33</v>
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>13</v>
+        <v>12.98</v>
       </c>
       <c r="J3" t="n">
         <v>-21.07</v>
@@ -596,7 +596,7 @@
         <v>183.3</v>
       </c>
       <c r="G4" t="n">
-        <v>75.5</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>13.22</v>
+        <v>13.21</v>
       </c>
       <c r="J4" t="n">
         <v>-21.63</v>
@@ -643,7 +643,7 @@
         <v>66.7</v>
       </c>
       <c r="G5" t="n">
-        <v>73.3</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -690,7 +690,7 @@
         <v>66.7</v>
       </c>
       <c r="G6" t="n">
-        <v>60.2</v>
+        <v>60.6</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>75</v>
       </c>
       <c r="G8" t="n">
-        <v>82.8</v>
+        <v>83</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>14.12</v>
+        <v>14.09</v>
       </c>
       <c r="J8" t="n">
         <v>-17.8</v>
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>12.88</v>
+        <v>12.87</v>
       </c>
       <c r="J9" t="n">
         <v>-20.6</v>
@@ -874,7 +874,7 @@
         <v>33.3</v>
       </c>
       <c r="G10" t="n">
-        <v>71.5</v>
+        <v>72</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>22.35</v>
+        <v>22.31</v>
       </c>
       <c r="J10" t="n">
         <v>-29.37</v>
@@ -921,7 +921,7 @@
         <v>33.3</v>
       </c>
       <c r="G11" t="n">
-        <v>64.90000000000001</v>
+        <v>64.7</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>36.8</v>
+        <v>36.77</v>
       </c>
       <c r="J11" t="n">
         <v>-35.74</v>
@@ -968,7 +968,7 @@
         <v>33.3</v>
       </c>
       <c r="G12" t="n">
-        <v>51.2</v>
+        <v>49.9</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -976,7 +976,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>34.79</v>
+        <v>34.82</v>
       </c>
       <c r="J12" t="n">
         <v>-48.6</v>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>65.86</v>
+        <v>65.79000000000001</v>
       </c>
     </row>
     <row r="6">

--- a/ETF_Allocation_Model.xlsx
+++ b/ETF_Allocation_Model.xlsx
@@ -477,12 +477,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>VWCE.DE</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>iShares STOXX Europe 600 UCITS ETF (DE) EUR (Dist)</t>
+          <t>Vanguard FTSE All-World UCITS ETF USD Accumulation</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -492,7 +492,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Europa</t>
+          <t>Azionario globale</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -502,7 +502,7 @@
         <v>183.3</v>
       </c>
       <c r="G2" t="n">
-        <v>76</v>
+        <v>75.7</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -510,10 +510,10 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>12.77</v>
+        <v>12.98</v>
       </c>
       <c r="J2" t="n">
-        <v>-16.33</v>
+        <v>-21.07</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -524,12 +524,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>VWCE.DE</t>
+          <t>SWDA.MI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Vanguard FTSE All-World UCITS ETF USD Accumulation</t>
+          <t>iShares Core MSCI World UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -539,7 +539,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Azionario globale</t>
+          <t>Azionario globale sviluppato</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -549,7 +549,7 @@
         <v>183.3</v>
       </c>
       <c r="G3" t="n">
-        <v>75.7</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -557,10 +557,10 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>12.98</v>
+        <v>13.2</v>
       </c>
       <c r="J3" t="n">
-        <v>-21.07</v>
+        <v>-21.63</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -571,12 +571,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SWDA.MI</t>
+          <t>EXSA.DE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>iShares Core MSCI World UCITS ETF USD (Acc)</t>
+          <t>iShares STOXX Europe 600 UCITS ETF (DE) EUR (Dist)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -586,7 +586,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Azionario globale sviluppato</t>
+          <t>Europa</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -596,7 +596,7 @@
         <v>183.3</v>
       </c>
       <c r="G4" t="n">
-        <v>75.59999999999999</v>
+        <v>75.3</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -604,10 +604,10 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>13.21</v>
+        <v>12.75</v>
       </c>
       <c r="J4" t="n">
-        <v>-21.63</v>
+        <v>-16.33</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -643,7 +643,7 @@
         <v>66.7</v>
       </c>
       <c r="G5" t="n">
-        <v>72.90000000000001</v>
+        <v>72.3</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -690,7 +690,7 @@
         <v>66.7</v>
       </c>
       <c r="G6" t="n">
-        <v>60.6</v>
+        <v>60.7</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -698,7 +698,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>18.69</v>
+        <v>18.7</v>
       </c>
       <c r="J6" t="n">
         <v>-22.72</v>
@@ -780,7 +780,7 @@
         <v>75</v>
       </c>
       <c r="G8" t="n">
-        <v>83</v>
+        <v>83.3</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>14.09</v>
+        <v>14.07</v>
       </c>
       <c r="J8" t="n">
         <v>-17.8</v>
@@ -827,7 +827,7 @@
         <v>75</v>
       </c>
       <c r="G9" t="n">
-        <v>74</v>
+        <v>73.5</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -874,7 +874,7 @@
         <v>33.3</v>
       </c>
       <c r="G10" t="n">
-        <v>72</v>
+        <v>71.7</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -921,15 +921,15 @@
         <v>33.3</v>
       </c>
       <c r="G11" t="n">
-        <v>64.7</v>
+        <v>68.7</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Hold / Monitor</t>
+          <t>Accumulate Carefully</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>36.77</v>
+        <v>36.8</v>
       </c>
       <c r="J11" t="n">
         <v>-35.74</v>
@@ -968,7 +968,7 @@
         <v>33.3</v>
       </c>
       <c r="G12" t="n">
-        <v>49.9</v>
+        <v>52.1</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -976,7 +976,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>34.82</v>
+        <v>34.8</v>
       </c>
       <c r="J12" t="n">
         <v>-48.6</v>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>65.79000000000001</v>
+        <v>66.16</v>
       </c>
     </row>
     <row r="6">

--- a/ETF_Allocation_Model.xlsx
+++ b/ETF_Allocation_Model.xlsx
@@ -502,7 +502,7 @@
         <v>183.3</v>
       </c>
       <c r="G2" t="n">
-        <v>75.7</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -510,7 +510,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>12.98</v>
+        <v>13</v>
       </c>
       <c r="J2" t="n">
         <v>-21.07</v>
@@ -524,12 +524,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SWDA.MI</t>
+          <t>EXSA.DE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>iShares Core MSCI World UCITS ETF USD (Acc)</t>
+          <t>iShares STOXX Europe 600 UCITS ETF (DE) EUR (Dist)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -539,7 +539,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Azionario globale sviluppato</t>
+          <t>Europa</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -549,7 +549,7 @@
         <v>183.3</v>
       </c>
       <c r="G3" t="n">
-        <v>75.40000000000001</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -557,10 +557,10 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>13.2</v>
+        <v>12.77</v>
       </c>
       <c r="J3" t="n">
-        <v>-21.63</v>
+        <v>-16.33</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -571,12 +571,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>SWDA.MI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>iShares STOXX Europe 600 UCITS ETF (DE) EUR (Dist)</t>
+          <t>iShares Core MSCI World UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -586,7 +586,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Europa</t>
+          <t>Azionario globale sviluppato</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -596,7 +596,7 @@
         <v>183.3</v>
       </c>
       <c r="G4" t="n">
-        <v>75.3</v>
+        <v>74.7</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -604,10 +604,10 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>12.75</v>
+        <v>13.21</v>
       </c>
       <c r="J4" t="n">
-        <v>-16.33</v>
+        <v>-21.63</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -643,7 +643,7 @@
         <v>66.7</v>
       </c>
       <c r="G5" t="n">
-        <v>72.3</v>
+        <v>72.5</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>9.710000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J5" t="n">
         <v>-12.85</v>
@@ -690,7 +690,7 @@
         <v>66.7</v>
       </c>
       <c r="G6" t="n">
-        <v>60.7</v>
+        <v>60.6</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -698,7 +698,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>18.7</v>
+        <v>18.71</v>
       </c>
       <c r="J6" t="n">
         <v>-22.72</v>
@@ -780,7 +780,7 @@
         <v>75</v>
       </c>
       <c r="G8" t="n">
-        <v>83.3</v>
+        <v>81.7</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>14.07</v>
+        <v>14.09</v>
       </c>
       <c r="J8" t="n">
         <v>-17.8</v>
@@ -827,7 +827,7 @@
         <v>75</v>
       </c>
       <c r="G9" t="n">
-        <v>73.5</v>
+        <v>73.2</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>12.87</v>
+        <v>12.88</v>
       </c>
       <c r="J9" t="n">
         <v>-20.6</v>
@@ -874,7 +874,7 @@
         <v>33.3</v>
       </c>
       <c r="G10" t="n">
-        <v>71.7</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>22.31</v>
+        <v>22.38</v>
       </c>
       <c r="J10" t="n">
         <v>-29.37</v>
@@ -921,15 +921,15 @@
         <v>33.3</v>
       </c>
       <c r="G11" t="n">
-        <v>68.7</v>
+        <v>63.9</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Accumulate Carefully</t>
+          <t>Hold / Monitor</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>36.8</v>
+        <v>36.9</v>
       </c>
       <c r="J11" t="n">
         <v>-35.74</v>
@@ -968,7 +968,7 @@
         <v>33.3</v>
       </c>
       <c r="G12" t="n">
-        <v>52.1</v>
+        <v>51.7</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -976,7 +976,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>34.8</v>
+        <v>34.81</v>
       </c>
       <c r="J12" t="n">
         <v>-48.6</v>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>66.16</v>
+        <v>64.79000000000001</v>
       </c>
     </row>
     <row r="6">

--- a/ETF_Allocation_Model.xlsx
+++ b/ETF_Allocation_Model.xlsx
@@ -502,7 +502,7 @@
         <v>183.3</v>
       </c>
       <c r="G2" t="n">
-        <v>74.90000000000001</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -510,7 +510,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>13</v>
+        <v>13.01</v>
       </c>
       <c r="J2" t="n">
         <v>-21.07</v>
@@ -549,7 +549,7 @@
         <v>183.3</v>
       </c>
       <c r="G3" t="n">
-        <v>74.90000000000001</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -596,7 +596,7 @@
         <v>183.3</v>
       </c>
       <c r="G4" t="n">
-        <v>74.7</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>13.21</v>
+        <v>13.22</v>
       </c>
       <c r="J4" t="n">
         <v>-21.63</v>
@@ -643,7 +643,7 @@
         <v>66.7</v>
       </c>
       <c r="G5" t="n">
-        <v>72.5</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -690,7 +690,7 @@
         <v>66.7</v>
       </c>
       <c r="G6" t="n">
-        <v>60.6</v>
+        <v>61.2</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>75</v>
       </c>
       <c r="G8" t="n">
-        <v>81.7</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>14.09</v>
+        <v>14.15</v>
       </c>
       <c r="J8" t="n">
         <v>-17.8</v>
@@ -827,7 +827,7 @@
         <v>75</v>
       </c>
       <c r="G9" t="n">
-        <v>73.2</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>12.88</v>
+        <v>12.87</v>
       </c>
       <c r="J9" t="n">
         <v>-20.6</v>
@@ -874,7 +874,7 @@
         <v>33.3</v>
       </c>
       <c r="G10" t="n">
-        <v>70.09999999999999</v>
+        <v>70</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>22.38</v>
+        <v>22.45</v>
       </c>
       <c r="J10" t="n">
         <v>-29.37</v>
@@ -921,7 +921,7 @@
         <v>33.3</v>
       </c>
       <c r="G11" t="n">
-        <v>63.9</v>
+        <v>63.2</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>36.9</v>
+        <v>36.85</v>
       </c>
       <c r="J11" t="n">
         <v>-35.74</v>
@@ -968,7 +968,7 @@
         <v>33.3</v>
       </c>
       <c r="G12" t="n">
-        <v>51.7</v>
+        <v>51.9</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -976,7 +976,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>34.81</v>
+        <v>34.83</v>
       </c>
       <c r="J12" t="n">
         <v>-48.6</v>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>64.79000000000001</v>
+        <v>64.58</v>
       </c>
     </row>
     <row r="6">

--- a/ETF_Allocation_Model.xlsx
+++ b/ETF_Allocation_Model.xlsx
@@ -477,12 +477,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>VWCE.DE</t>
+          <t>EXSA.DE</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Vanguard FTSE All-World UCITS ETF USD Accumulation</t>
+          <t>iShares STOXX Europe 600 UCITS ETF (DE) EUR (Dist)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -492,7 +492,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Azionario globale</t>
+          <t>Europa</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -502,7 +502,7 @@
         <v>183.3</v>
       </c>
       <c r="G2" t="n">
-        <v>74.59999999999999</v>
+        <v>74.2</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -510,10 +510,10 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>13.01</v>
+        <v>12.76</v>
       </c>
       <c r="J2" t="n">
-        <v>-21.07</v>
+        <v>-16.33</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -524,12 +524,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>VWCE.DE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>iShares STOXX Europe 600 UCITS ETF (DE) EUR (Dist)</t>
+          <t>Vanguard FTSE All-World UCITS ETF USD Accumulation</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -539,7 +539,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Europa</t>
+          <t>Azionario globale</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -549,7 +549,7 @@
         <v>183.3</v>
       </c>
       <c r="G3" t="n">
-        <v>74.59999999999999</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -557,10 +557,10 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>12.77</v>
+        <v>13.01</v>
       </c>
       <c r="J3" t="n">
-        <v>-16.33</v>
+        <v>-21.07</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -596,7 +596,7 @@
         <v>183.3</v>
       </c>
       <c r="G4" t="n">
-        <v>74.40000000000001</v>
+        <v>73.3</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -643,7 +643,7 @@
         <v>66.7</v>
       </c>
       <c r="G5" t="n">
-        <v>72.59999999999999</v>
+        <v>72.2</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -690,7 +690,7 @@
         <v>66.7</v>
       </c>
       <c r="G6" t="n">
-        <v>61.2</v>
+        <v>66</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -698,7 +698,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>18.71</v>
+        <v>18.79</v>
       </c>
       <c r="J6" t="n">
         <v>-22.72</v>
@@ -780,7 +780,7 @@
         <v>75</v>
       </c>
       <c r="G8" t="n">
-        <v>81.09999999999999</v>
+        <v>80</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>14.15</v>
+        <v>14.12</v>
       </c>
       <c r="J8" t="n">
         <v>-17.8</v>
@@ -827,7 +827,7 @@
         <v>75</v>
       </c>
       <c r="G9" t="n">
-        <v>72.90000000000001</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -874,7 +874,7 @@
         <v>33.3</v>
       </c>
       <c r="G10" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>22.45</v>
+        <v>22.44</v>
       </c>
       <c r="J10" t="n">
         <v>-29.37</v>
@@ -921,7 +921,7 @@
         <v>33.3</v>
       </c>
       <c r="G11" t="n">
-        <v>63.2</v>
+        <v>62.2</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>36.85</v>
+        <v>36.83</v>
       </c>
       <c r="J11" t="n">
         <v>-35.74</v>
@@ -968,7 +968,7 @@
         <v>33.3</v>
       </c>
       <c r="G12" t="n">
-        <v>51.9</v>
+        <v>53.1</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -976,7 +976,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>34.83</v>
+        <v>34.81</v>
       </c>
       <c r="J12" t="n">
         <v>-48.6</v>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>64.58</v>
+        <v>64.16</v>
       </c>
     </row>
     <row r="6">

--- a/ETF_Allocation_Model.xlsx
+++ b/ETF_Allocation_Model.xlsx
@@ -502,7 +502,7 @@
         <v>183.3</v>
       </c>
       <c r="G2" t="n">
-        <v>74.2</v>
+        <v>74</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -510,7 +510,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>12.76</v>
+        <v>12.75</v>
       </c>
       <c r="J2" t="n">
         <v>-16.33</v>
@@ -549,7 +549,7 @@
         <v>183.3</v>
       </c>
       <c r="G3" t="n">
-        <v>73.59999999999999</v>
+        <v>73.7</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>13.01</v>
+        <v>12.99</v>
       </c>
       <c r="J3" t="n">
         <v>-21.07</v>
@@ -596,7 +596,7 @@
         <v>183.3</v>
       </c>
       <c r="G4" t="n">
-        <v>73.3</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>13.22</v>
+        <v>13.2</v>
       </c>
       <c r="J4" t="n">
         <v>-21.63</v>
@@ -643,7 +643,7 @@
         <v>66.7</v>
       </c>
       <c r="G5" t="n">
-        <v>72.2</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>9.699999999999999</v>
+        <v>9.69</v>
       </c>
       <c r="J5" t="n">
         <v>-12.85</v>
@@ -690,7 +690,7 @@
         <v>66.7</v>
       </c>
       <c r="G6" t="n">
-        <v>66</v>
+        <v>65.8</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>75</v>
       </c>
       <c r="G8" t="n">
-        <v>80</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>12.87</v>
+        <v>12.86</v>
       </c>
       <c r="J9" t="n">
         <v>-20.6</v>
@@ -874,15 +874,15 @@
         <v>33.3</v>
       </c>
       <c r="G10" t="n">
-        <v>68</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Accumulate Carefully</t>
+          <t>Hold / Monitor</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>22.44</v>
+        <v>22.42</v>
       </c>
       <c r="J10" t="n">
         <v>-29.37</v>
@@ -921,7 +921,7 @@
         <v>33.3</v>
       </c>
       <c r="G11" t="n">
-        <v>62.2</v>
+        <v>61.8</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>36.83</v>
+        <v>36.8</v>
       </c>
       <c r="J11" t="n">
         <v>-35.74</v>
@@ -968,7 +968,7 @@
         <v>33.3</v>
       </c>
       <c r="G12" t="n">
-        <v>53.1</v>
+        <v>53</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -976,7 +976,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>34.81</v>
+        <v>34.78</v>
       </c>
       <c r="J12" t="n">
         <v>-48.6</v>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>64.16</v>
+        <v>64.15000000000001</v>
       </c>
     </row>
     <row r="6">

--- a/ETF_Allocation_Model.xlsx
+++ b/ETF_Allocation_Model.xlsx
@@ -502,7 +502,7 @@
         <v>183.3</v>
       </c>
       <c r="G2" t="n">
-        <v>74</v>
+        <v>74.3</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -510,7 +510,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>12.75</v>
+        <v>12.76</v>
       </c>
       <c r="J2" t="n">
         <v>-16.33</v>
@@ -549,7 +549,7 @@
         <v>183.3</v>
       </c>
       <c r="G3" t="n">
-        <v>73.7</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -596,7 +596,7 @@
         <v>183.3</v>
       </c>
       <c r="G4" t="n">
-        <v>73.40000000000001</v>
+        <v>73.3</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>13.2</v>
+        <v>13.19</v>
       </c>
       <c r="J4" t="n">
         <v>-21.63</v>
@@ -643,7 +643,7 @@
         <v>66.7</v>
       </c>
       <c r="G5" t="n">
-        <v>72.09999999999999</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -690,7 +690,7 @@
         <v>66.7</v>
       </c>
       <c r="G6" t="n">
-        <v>65.8</v>
+        <v>66.3</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>75</v>
       </c>
       <c r="G8" t="n">
-        <v>80.09999999999999</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>14.12</v>
+        <v>14.13</v>
       </c>
       <c r="J8" t="n">
         <v>-17.8</v>
@@ -827,7 +827,7 @@
         <v>75</v>
       </c>
       <c r="G9" t="n">
-        <v>71.90000000000001</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>12.86</v>
+        <v>12.85</v>
       </c>
       <c r="J9" t="n">
         <v>-20.6</v>
@@ -874,7 +874,7 @@
         <v>33.3</v>
       </c>
       <c r="G10" t="n">
-        <v>67.90000000000001</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -921,7 +921,7 @@
         <v>33.3</v>
       </c>
       <c r="G11" t="n">
-        <v>61.8</v>
+        <v>59.5</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>36.8</v>
+        <v>36.82</v>
       </c>
       <c r="J11" t="n">
         <v>-35.74</v>
@@ -968,7 +968,7 @@
         <v>33.3</v>
       </c>
       <c r="G12" t="n">
-        <v>53</v>
+        <v>53.8</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -976,7 +976,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>34.78</v>
+        <v>34.77</v>
       </c>
       <c r="J12" t="n">
         <v>-48.6</v>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>64.15000000000001</v>
+        <v>63.28</v>
       </c>
     </row>
     <row r="6">

--- a/ETF_Allocation_Model.xlsx
+++ b/ETF_Allocation_Model.xlsx
@@ -502,7 +502,7 @@
         <v>183.3</v>
       </c>
       <c r="G2" t="n">
-        <v>74.3</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -510,7 +510,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>12.76</v>
+        <v>12.77</v>
       </c>
       <c r="J2" t="n">
         <v>-16.33</v>
@@ -549,7 +549,7 @@
         <v>183.3</v>
       </c>
       <c r="G3" t="n">
-        <v>73.40000000000001</v>
+        <v>73.7</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>12.99</v>
+        <v>13</v>
       </c>
       <c r="J3" t="n">
         <v>-21.07</v>
@@ -596,7 +596,7 @@
         <v>183.3</v>
       </c>
       <c r="G4" t="n">
-        <v>73.3</v>
+        <v>73.5</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>13.19</v>
+        <v>13.2</v>
       </c>
       <c r="J4" t="n">
         <v>-21.63</v>
@@ -643,7 +643,7 @@
         <v>66.7</v>
       </c>
       <c r="G5" t="n">
-        <v>72.40000000000001</v>
+        <v>72.5</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>9.69</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J5" t="n">
         <v>-12.85</v>
@@ -780,7 +780,7 @@
         <v>75</v>
       </c>
       <c r="G8" t="n">
-        <v>78.90000000000001</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>14.13</v>
+        <v>14.12</v>
       </c>
       <c r="J8" t="n">
         <v>-17.8</v>
@@ -827,7 +827,7 @@
         <v>75</v>
       </c>
       <c r="G9" t="n">
-        <v>72.09999999999999</v>
+        <v>72.3</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>12.85</v>
+        <v>12.86</v>
       </c>
       <c r="J9" t="n">
         <v>-20.6</v>
@@ -874,11 +874,11 @@
         <v>33.3</v>
       </c>
       <c r="G10" t="n">
-        <v>64.09999999999999</v>
+        <v>68.3</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Hold / Monitor</t>
+          <t>Accumulate Carefully</t>
         </is>
       </c>
       <c r="I10" t="n">
@@ -921,7 +921,7 @@
         <v>33.3</v>
       </c>
       <c r="G11" t="n">
-        <v>59.5</v>
+        <v>58.6</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>36.82</v>
+        <v>36.83</v>
       </c>
       <c r="J11" t="n">
         <v>-35.74</v>
@@ -968,7 +968,7 @@
         <v>33.3</v>
       </c>
       <c r="G12" t="n">
-        <v>53.8</v>
+        <v>54.2</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -976,7 +976,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>34.77</v>
+        <v>34.8</v>
       </c>
       <c r="J12" t="n">
         <v>-48.6</v>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>63.28</v>
+        <v>63.79</v>
       </c>
     </row>
     <row r="6">

--- a/ETF_Allocation_Model.xlsx
+++ b/ETF_Allocation_Model.xlsx
@@ -502,7 +502,7 @@
         <v>183.3</v>
       </c>
       <c r="G2" t="n">
-        <v>74.59999999999999</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -510,7 +510,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>12.77</v>
+        <v>12.75</v>
       </c>
       <c r="J2" t="n">
         <v>-16.33</v>
@@ -549,7 +549,7 @@
         <v>183.3</v>
       </c>
       <c r="G3" t="n">
-        <v>73.7</v>
+        <v>73.5</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -596,7 +596,7 @@
         <v>183.3</v>
       </c>
       <c r="G4" t="n">
-        <v>73.5</v>
+        <v>73.3</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -643,7 +643,7 @@
         <v>66.7</v>
       </c>
       <c r="G5" t="n">
-        <v>72.5</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -690,7 +690,7 @@
         <v>66.7</v>
       </c>
       <c r="G6" t="n">
-        <v>66.3</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -698,7 +698,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>18.79</v>
+        <v>18.82</v>
       </c>
       <c r="J6" t="n">
         <v>-22.72</v>
@@ -780,7 +780,7 @@
         <v>75</v>
       </c>
       <c r="G8" t="n">
-        <v>79.40000000000001</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>14.12</v>
+        <v>14.14</v>
       </c>
       <c r="J8" t="n">
         <v>-17.8</v>
@@ -827,7 +827,7 @@
         <v>75</v>
       </c>
       <c r="G9" t="n">
-        <v>72.3</v>
+        <v>72.2</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>12.86</v>
+        <v>12.85</v>
       </c>
       <c r="J9" t="n">
         <v>-20.6</v>
@@ -874,11 +874,11 @@
         <v>33.3</v>
       </c>
       <c r="G10" t="n">
-        <v>68.3</v>
+        <v>67.2</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Accumulate Carefully</t>
+          <t>Hold / Monitor</t>
         </is>
       </c>
       <c r="I10" t="n">
@@ -921,7 +921,7 @@
         <v>33.3</v>
       </c>
       <c r="G11" t="n">
-        <v>58.6</v>
+        <v>58.7</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -968,7 +968,7 @@
         <v>33.3</v>
       </c>
       <c r="G12" t="n">
-        <v>54.2</v>
+        <v>55</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>63.79</v>
+        <v>64.13</v>
       </c>
     </row>
     <row r="6">

--- a/ETF_Allocation_Model.xlsx
+++ b/ETF_Allocation_Model.xlsx
@@ -502,7 +502,7 @@
         <v>183.3</v>
       </c>
       <c r="G2" t="n">
-        <v>74.40000000000001</v>
+        <v>74.5</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -510,7 +510,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>12.75</v>
+        <v>12.74</v>
       </c>
       <c r="J2" t="n">
         <v>-16.33</v>
@@ -549,7 +549,7 @@
         <v>183.3</v>
       </c>
       <c r="G3" t="n">
-        <v>73.5</v>
+        <v>73.2</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>13</v>
+        <v>12.99</v>
       </c>
       <c r="J3" t="n">
         <v>-21.07</v>
@@ -596,7 +596,7 @@
         <v>183.3</v>
       </c>
       <c r="G4" t="n">
-        <v>73.3</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>13.2</v>
+        <v>13.19</v>
       </c>
       <c r="J4" t="n">
         <v>-21.63</v>
@@ -643,7 +643,7 @@
         <v>66.7</v>
       </c>
       <c r="G5" t="n">
-        <v>72.59999999999999</v>
+        <v>72.7</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>9.699999999999999</v>
+        <v>9.69</v>
       </c>
       <c r="J5" t="n">
         <v>-12.85</v>
@@ -690,7 +690,7 @@
         <v>66.7</v>
       </c>
       <c r="G6" t="n">
-        <v>66.09999999999999</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -698,7 +698,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>18.82</v>
+        <v>18.79</v>
       </c>
       <c r="J6" t="n">
         <v>-22.72</v>
@@ -780,7 +780,7 @@
         <v>75</v>
       </c>
       <c r="G8" t="n">
-        <v>79.09999999999999</v>
+        <v>78.8</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>14.14</v>
+        <v>14.12</v>
       </c>
       <c r="J8" t="n">
         <v>-17.8</v>
@@ -827,7 +827,7 @@
         <v>75</v>
       </c>
       <c r="G9" t="n">
-        <v>72.2</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -874,7 +874,7 @@
         <v>33.3</v>
       </c>
       <c r="G10" t="n">
-        <v>67.2</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>22.42</v>
+        <v>22.4</v>
       </c>
       <c r="J10" t="n">
         <v>-29.37</v>
@@ -921,7 +921,7 @@
         <v>33.3</v>
       </c>
       <c r="G11" t="n">
-        <v>58.7</v>
+        <v>61.9</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>36.83</v>
+        <v>36.84</v>
       </c>
       <c r="J11" t="n">
         <v>-35.74</v>
@@ -968,15 +968,15 @@
         <v>33.3</v>
       </c>
       <c r="G12" t="n">
-        <v>55</v>
+        <v>55.3</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>High Risk</t>
+          <t>Hold / Monitor</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>34.8</v>
+        <v>34.77</v>
       </c>
       <c r="J12" t="n">
         <v>-48.6</v>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>64.13</v>
+        <v>64.23999999999999</v>
       </c>
     </row>
     <row r="6">

--- a/ETF_Allocation_Model.xlsx
+++ b/ETF_Allocation_Model.xlsx
@@ -921,7 +921,7 @@
         <v>33.3</v>
       </c>
       <c r="G11" t="n">
-        <v>61.9</v>
+        <v>58.8</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>36.84</v>
+        <v>36.88</v>
       </c>
       <c r="J11" t="n">
         <v>-35.74</v>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>64.23999999999999</v>
+        <v>64.02</v>
       </c>
     </row>
     <row r="6">

--- a/ETF_Allocation_Model.xlsx
+++ b/ETF_Allocation_Model.xlsx
@@ -510,7 +510,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>12.74</v>
+        <v>12.75</v>
       </c>
       <c r="J2" t="n">
         <v>-16.33</v>
@@ -549,7 +549,7 @@
         <v>183.3</v>
       </c>
       <c r="G3" t="n">
-        <v>73.2</v>
+        <v>73.3</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>12.99</v>
+        <v>12.98</v>
       </c>
       <c r="J3" t="n">
         <v>-21.07</v>
@@ -596,7 +596,7 @@
         <v>183.3</v>
       </c>
       <c r="G4" t="n">
-        <v>73.09999999999999</v>
+        <v>73.2</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>13.19</v>
+        <v>13.18</v>
       </c>
       <c r="J4" t="n">
         <v>-21.63</v>
@@ -690,7 +690,7 @@
         <v>66.7</v>
       </c>
       <c r="G6" t="n">
-        <v>65.40000000000001</v>
+        <v>60.4</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -698,7 +698,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>18.79</v>
+        <v>18.89</v>
       </c>
       <c r="J6" t="n">
         <v>-22.72</v>
@@ -780,7 +780,7 @@
         <v>75</v>
       </c>
       <c r="G8" t="n">
-        <v>78.8</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>14.12</v>
+        <v>14.13</v>
       </c>
       <c r="J8" t="n">
         <v>-17.8</v>
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>12.85</v>
+        <v>12.84</v>
       </c>
       <c r="J9" t="n">
         <v>-20.6</v>
@@ -874,15 +874,15 @@
         <v>33.3</v>
       </c>
       <c r="G10" t="n">
-        <v>67.09999999999999</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Hold / Monitor</t>
+          <t>Accumulate Carefully</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>22.4</v>
+        <v>22.44</v>
       </c>
       <c r="J10" t="n">
         <v>-29.37</v>
@@ -968,15 +968,15 @@
         <v>33.3</v>
       </c>
       <c r="G12" t="n">
-        <v>55.3</v>
+        <v>51.3</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Hold / Monitor</t>
+          <t>High Risk</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>34.77</v>
+        <v>35.03</v>
       </c>
       <c r="J12" t="n">
         <v>-48.6</v>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>64.02</v>
+        <v>63.51</v>
       </c>
     </row>
     <row r="6">

--- a/ETF_Allocation_Model.xlsx
+++ b/ETF_Allocation_Model.xlsx
@@ -502,7 +502,7 @@
         <v>183.3</v>
       </c>
       <c r="G2" t="n">
-        <v>74.5</v>
+        <v>75.3</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -549,7 +549,7 @@
         <v>183.3</v>
       </c>
       <c r="G3" t="n">
-        <v>73.3</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>12.98</v>
+        <v>12.99</v>
       </c>
       <c r="J3" t="n">
         <v>-21.07</v>
@@ -596,7 +596,7 @@
         <v>183.3</v>
       </c>
       <c r="G4" t="n">
-        <v>73.2</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>13.18</v>
+        <v>13.19</v>
       </c>
       <c r="J4" t="n">
         <v>-21.63</v>
@@ -643,7 +643,7 @@
         <v>66.7</v>
       </c>
       <c r="G5" t="n">
-        <v>72.7</v>
+        <v>72.5</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -690,7 +690,7 @@
         <v>66.7</v>
       </c>
       <c r="G6" t="n">
-        <v>60.4</v>
+        <v>60.7</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -698,7 +698,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>18.89</v>
+        <v>18.85</v>
       </c>
       <c r="J6" t="n">
         <v>-22.72</v>
@@ -780,7 +780,7 @@
         <v>75</v>
       </c>
       <c r="G8" t="n">
-        <v>78.40000000000001</v>
+        <v>78.5</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -827,7 +827,7 @@
         <v>75</v>
       </c>
       <c r="G9" t="n">
-        <v>72.09999999999999</v>
+        <v>72</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -874,11 +874,11 @@
         <v>33.3</v>
       </c>
       <c r="G10" t="n">
-        <v>68.09999999999999</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Accumulate Carefully</t>
+          <t>Hold / Monitor</t>
         </is>
       </c>
       <c r="I10" t="n">
@@ -968,7 +968,7 @@
         <v>33.3</v>
       </c>
       <c r="G12" t="n">
-        <v>51.3</v>
+        <v>51.8</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -976,7 +976,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>35.03</v>
+        <v>35.05</v>
       </c>
       <c r="J12" t="n">
         <v>-48.6</v>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>63.51</v>
+        <v>63.61</v>
       </c>
     </row>
     <row r="6">

--- a/ETF_Allocation_Model.xlsx
+++ b/ETF_Allocation_Model.xlsx
@@ -502,7 +502,7 @@
         <v>183.3</v>
       </c>
       <c r="G2" t="n">
-        <v>75.3</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -549,7 +549,7 @@
         <v>183.3</v>
       </c>
       <c r="G3" t="n">
-        <v>73.40000000000001</v>
+        <v>73.7</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -596,7 +596,7 @@
         <v>183.3</v>
       </c>
       <c r="G4" t="n">
-        <v>73.09999999999999</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -643,7 +643,7 @@
         <v>66.7</v>
       </c>
       <c r="G5" t="n">
-        <v>72.5</v>
+        <v>72.8</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -690,7 +690,7 @@
         <v>66.7</v>
       </c>
       <c r="G6" t="n">
-        <v>60.7</v>
+        <v>65.8</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -698,7 +698,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>18.85</v>
+        <v>18.81</v>
       </c>
       <c r="J6" t="n">
         <v>-22.72</v>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>14.13</v>
+        <v>14.14</v>
       </c>
       <c r="J8" t="n">
         <v>-17.8</v>
@@ -827,7 +827,7 @@
         <v>75</v>
       </c>
       <c r="G9" t="n">
-        <v>72</v>
+        <v>72.5</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>12.84</v>
+        <v>12.85</v>
       </c>
       <c r="J9" t="n">
         <v>-20.6</v>
@@ -874,11 +874,11 @@
         <v>33.3</v>
       </c>
       <c r="G10" t="n">
-        <v>67.40000000000001</v>
+        <v>68.7</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Hold / Monitor</t>
+          <t>Accumulate Carefully</t>
         </is>
       </c>
       <c r="I10" t="n">
@@ -921,7 +921,7 @@
         <v>33.3</v>
       </c>
       <c r="G11" t="n">
-        <v>58.8</v>
+        <v>58.9</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>36.88</v>
+        <v>36.93</v>
       </c>
       <c r="J11" t="n">
         <v>-35.74</v>
@@ -968,7 +968,7 @@
         <v>33.3</v>
       </c>
       <c r="G12" t="n">
-        <v>51.8</v>
+        <v>50</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>63.61</v>
+        <v>64.05</v>
       </c>
     </row>
     <row r="6">

--- a/ETF_Allocation_Model.xlsx
+++ b/ETF_Allocation_Model.xlsx
@@ -502,7 +502,7 @@
         <v>183.3</v>
       </c>
       <c r="G2" t="n">
-        <v>74.59999999999999</v>
+        <v>74.5</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -510,7 +510,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>12.75</v>
+        <v>12.77</v>
       </c>
       <c r="J2" t="n">
         <v>-16.33</v>
@@ -549,7 +549,7 @@
         <v>183.3</v>
       </c>
       <c r="G3" t="n">
-        <v>73.7</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>12.99</v>
+        <v>13.01</v>
       </c>
       <c r="J3" t="n">
         <v>-21.07</v>
@@ -596,7 +596,7 @@
         <v>183.3</v>
       </c>
       <c r="G4" t="n">
-        <v>73.59999999999999</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>13.19</v>
+        <v>13.21</v>
       </c>
       <c r="J4" t="n">
         <v>-21.63</v>
@@ -643,7 +643,7 @@
         <v>66.7</v>
       </c>
       <c r="G5" t="n">
-        <v>72.8</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -690,7 +690,7 @@
         <v>66.7</v>
       </c>
       <c r="G6" t="n">
-        <v>65.8</v>
+        <v>59.6</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -698,7 +698,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>18.81</v>
+        <v>18.97</v>
       </c>
       <c r="J6" t="n">
         <v>-22.72</v>
@@ -780,7 +780,7 @@
         <v>75</v>
       </c>
       <c r="G8" t="n">
-        <v>78.5</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>14.14</v>
+        <v>14.13</v>
       </c>
       <c r="J8" t="n">
         <v>-17.8</v>
@@ -827,15 +827,15 @@
         <v>75</v>
       </c>
       <c r="G9" t="n">
-        <v>72.5</v>
+        <v>67.8</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Accumulate Carefully</t>
+          <t>Hold / Monitor</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>12.85</v>
+        <v>12.88</v>
       </c>
       <c r="J9" t="n">
         <v>-20.6</v>
@@ -874,15 +874,15 @@
         <v>33.3</v>
       </c>
       <c r="G10" t="n">
-        <v>68.7</v>
+        <v>62.3</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Accumulate Carefully</t>
+          <t>Hold / Monitor</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>22.44</v>
+        <v>22.52</v>
       </c>
       <c r="J10" t="n">
         <v>-29.37</v>
@@ -921,7 +921,7 @@
         <v>33.3</v>
       </c>
       <c r="G11" t="n">
-        <v>58.9</v>
+        <v>57</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>36.93</v>
+        <v>36.95</v>
       </c>
       <c r="J11" t="n">
         <v>-35.74</v>
@@ -968,7 +968,7 @@
         <v>33.3</v>
       </c>
       <c r="G12" t="n">
-        <v>50</v>
+        <v>52.4</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -976,7 +976,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>35.05</v>
+        <v>35.07</v>
       </c>
       <c r="J12" t="n">
         <v>-48.6</v>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>64.05</v>
+        <v>62.56</v>
       </c>
     </row>
     <row r="6">

--- a/ETF_Allocation_Model.xlsx
+++ b/ETF_Allocation_Model.xlsx
@@ -477,12 +477,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>VWCE.DE</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>iShares STOXX Europe 600 UCITS ETF (DE) EUR (Dist)</t>
+          <t>Vanguard FTSE All-World UCITS ETF USD Accumulation</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -492,7 +492,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Europa</t>
+          <t>Azionario globale</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -502,7 +502,7 @@
         <v>183.3</v>
       </c>
       <c r="G2" t="n">
-        <v>74.5</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -510,10 +510,10 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>12.77</v>
+        <v>13.01</v>
       </c>
       <c r="J2" t="n">
-        <v>-16.33</v>
+        <v>-21.07</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -524,12 +524,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>VWCE.DE</t>
+          <t>SWDA.MI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Vanguard FTSE All-World UCITS ETF USD Accumulation</t>
+          <t>iShares Core MSCI World UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -539,7 +539,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Azionario globale</t>
+          <t>Azionario globale sviluppato</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -549,7 +549,7 @@
         <v>183.3</v>
       </c>
       <c r="G3" t="n">
-        <v>72.90000000000001</v>
+        <v>72.7</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -557,10 +557,10 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>13.01</v>
+        <v>13.21</v>
       </c>
       <c r="J3" t="n">
-        <v>-21.07</v>
+        <v>-21.63</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -571,12 +571,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SWDA.MI</t>
+          <t>SXR8.DE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>iShares Core MSCI World UCITS ETF USD (Acc)</t>
+          <t>iShares Core S&amp;P 500 UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -586,7 +586,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Azionario globale sviluppato</t>
+          <t>USA large cap</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -596,7 +596,7 @@
         <v>183.3</v>
       </c>
       <c r="G4" t="n">
-        <v>72.59999999999999</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -604,10 +604,10 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>13.21</v>
+        <v>14.26</v>
       </c>
       <c r="J4" t="n">
-        <v>-21.63</v>
+        <v>-23.32</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -643,7 +643,7 @@
         <v>66.7</v>
       </c>
       <c r="G5" t="n">
-        <v>72.40000000000001</v>
+        <v>72.5</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -690,7 +690,7 @@
         <v>66.7</v>
       </c>
       <c r="G6" t="n">
-        <v>59.6</v>
+        <v>59.5</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -698,7 +698,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>18.97</v>
+        <v>18.91</v>
       </c>
       <c r="J6" t="n">
         <v>-22.72</v>
@@ -780,7 +780,7 @@
         <v>75</v>
       </c>
       <c r="G8" t="n">
-        <v>78.59999999999999</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -827,7 +827,7 @@
         <v>75</v>
       </c>
       <c r="G9" t="n">
-        <v>67.8</v>
+        <v>67.5</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>12.88</v>
+        <v>12.87</v>
       </c>
       <c r="J9" t="n">
         <v>-20.6</v>
@@ -874,7 +874,7 @@
         <v>33.3</v>
       </c>
       <c r="G10" t="n">
-        <v>62.3</v>
+        <v>61.7</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>22.52</v>
+        <v>22.53</v>
       </c>
       <c r="J10" t="n">
         <v>-29.37</v>
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>36.95</v>
+        <v>36.93</v>
       </c>
       <c r="J11" t="n">
         <v>-35.74</v>
@@ -968,7 +968,7 @@
         <v>33.3</v>
       </c>
       <c r="G12" t="n">
-        <v>52.4</v>
+        <v>53.7</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>62.56</v>
+        <v>62.45</v>
       </c>
     </row>
     <row r="6">

--- a/ETF_Allocation_Model.xlsx
+++ b/ETF_Allocation_Model.xlsx
@@ -643,7 +643,7 @@
         <v>66.7</v>
       </c>
       <c r="G5" t="n">
-        <v>72.5</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -690,7 +690,7 @@
         <v>66.7</v>
       </c>
       <c r="G6" t="n">
-        <v>59.5</v>
+        <v>60.1</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -698,7 +698,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>18.91</v>
+        <v>18.89</v>
       </c>
       <c r="J6" t="n">
         <v>-22.72</v>
@@ -827,7 +827,7 @@
         <v>75</v>
       </c>
       <c r="G9" t="n">
-        <v>67.5</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -874,7 +874,7 @@
         <v>33.3</v>
       </c>
       <c r="G10" t="n">
-        <v>61.7</v>
+        <v>61.4</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>22.53</v>
+        <v>22.55</v>
       </c>
       <c r="J10" t="n">
         <v>-29.37</v>
@@ -921,7 +921,7 @@
         <v>33.3</v>
       </c>
       <c r="G11" t="n">
-        <v>57</v>
+        <v>56.9</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -968,7 +968,7 @@
         <v>33.3</v>
       </c>
       <c r="G12" t="n">
-        <v>53.7</v>
+        <v>54.5</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -976,7 +976,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>35.07</v>
+        <v>35.11</v>
       </c>
       <c r="J12" t="n">
         <v>-48.6</v>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>62.45</v>
+        <v>62.53</v>
       </c>
     </row>
     <row r="6">

--- a/ETF_Allocation_Model.xlsx
+++ b/ETF_Allocation_Model.xlsx
@@ -502,7 +502,7 @@
         <v>183.3</v>
       </c>
       <c r="G2" t="n">
-        <v>73.09999999999999</v>
+        <v>73.3</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -549,7 +549,7 @@
         <v>183.3</v>
       </c>
       <c r="G3" t="n">
-        <v>72.7</v>
+        <v>73</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -596,7 +596,7 @@
         <v>183.3</v>
       </c>
       <c r="G4" t="n">
-        <v>71.59999999999999</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -643,7 +643,7 @@
         <v>66.7</v>
       </c>
       <c r="G5" t="n">
-        <v>72.40000000000001</v>
+        <v>72.5</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -690,7 +690,7 @@
         <v>66.7</v>
       </c>
       <c r="G6" t="n">
-        <v>60.1</v>
+        <v>59.8</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -698,7 +698,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>18.89</v>
+        <v>18.9</v>
       </c>
       <c r="J6" t="n">
         <v>-22.72</v>
@@ -780,7 +780,7 @@
         <v>75</v>
       </c>
       <c r="G8" t="n">
-        <v>79.09999999999999</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -827,7 +827,7 @@
         <v>75</v>
       </c>
       <c r="G9" t="n">
-        <v>67.40000000000001</v>
+        <v>67.8</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -874,7 +874,7 @@
         <v>33.3</v>
       </c>
       <c r="G10" t="n">
-        <v>61.4</v>
+        <v>61.9</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>22.55</v>
+        <v>22.52</v>
       </c>
       <c r="J10" t="n">
         <v>-29.37</v>
@@ -921,7 +921,7 @@
         <v>33.3</v>
       </c>
       <c r="G11" t="n">
-        <v>56.9</v>
+        <v>57.8</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -968,7 +968,7 @@
         <v>33.3</v>
       </c>
       <c r="G12" t="n">
-        <v>54.5</v>
+        <v>54.8</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -976,7 +976,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>35.11</v>
+        <v>35.13</v>
       </c>
       <c r="J12" t="n">
         <v>-48.6</v>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>62.53</v>
+        <v>62.75</v>
       </c>
     </row>
     <row r="6">

--- a/ETF_Allocation_Model.xlsx
+++ b/ETF_Allocation_Model.xlsx
@@ -477,12 +477,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>VWCE.DE</t>
+          <t>EXSA.DE</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Vanguard FTSE All-World UCITS ETF USD Accumulation</t>
+          <t>iShares STOXX Europe 600 UCITS ETF (DE) EUR (Dist)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -492,7 +492,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Azionario globale</t>
+          <t>Europa</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -502,7 +502,7 @@
         <v>183.3</v>
       </c>
       <c r="G2" t="n">
-        <v>73.3</v>
+        <v>74.8</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -510,10 +510,10 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>13.01</v>
+        <v>12.76</v>
       </c>
       <c r="J2" t="n">
-        <v>-21.07</v>
+        <v>-16.33</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -524,12 +524,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SWDA.MI</t>
+          <t>VWCE.DE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>iShares Core MSCI World UCITS ETF USD (Acc)</t>
+          <t>Vanguard FTSE All-World UCITS ETF USD Accumulation</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -539,7 +539,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Azionario globale sviluppato</t>
+          <t>Azionario globale</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -549,7 +549,7 @@
         <v>183.3</v>
       </c>
       <c r="G3" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -557,10 +557,10 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>13.21</v>
+        <v>13.01</v>
       </c>
       <c r="J3" t="n">
-        <v>-21.63</v>
+        <v>-21.07</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -571,12 +571,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SXR8.DE</t>
+          <t>SWDA.MI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>iShares Core S&amp;P 500 UCITS ETF USD (Acc)</t>
+          <t>iShares Core MSCI World UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -586,7 +586,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>USA large cap</t>
+          <t>Azionario globale sviluppato</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -596,7 +596,7 @@
         <v>183.3</v>
       </c>
       <c r="G4" t="n">
-        <v>71.90000000000001</v>
+        <v>73.5</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -604,10 +604,10 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>14.26</v>
+        <v>13.21</v>
       </c>
       <c r="J4" t="n">
-        <v>-23.32</v>
+        <v>-21.63</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -643,7 +643,7 @@
         <v>66.7</v>
       </c>
       <c r="G5" t="n">
-        <v>72.5</v>
+        <v>72.3</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -690,7 +690,7 @@
         <v>66.7</v>
       </c>
       <c r="G6" t="n">
-        <v>59.8</v>
+        <v>61.4</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -698,7 +698,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>18.9</v>
+        <v>18.96</v>
       </c>
       <c r="J6" t="n">
         <v>-22.72</v>
@@ -780,7 +780,7 @@
         <v>75</v>
       </c>
       <c r="G8" t="n">
-        <v>79.40000000000001</v>
+        <v>80.5</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -827,15 +827,15 @@
         <v>75</v>
       </c>
       <c r="G9" t="n">
-        <v>67.8</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Hold / Monitor</t>
+          <t>Accumulate Carefully</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>12.87</v>
+        <v>12.86</v>
       </c>
       <c r="J9" t="n">
         <v>-20.6</v>
@@ -874,7 +874,7 @@
         <v>33.3</v>
       </c>
       <c r="G10" t="n">
-        <v>61.9</v>
+        <v>67.8</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>22.52</v>
+        <v>22.47</v>
       </c>
       <c r="J10" t="n">
         <v>-29.37</v>
@@ -921,7 +921,7 @@
         <v>33.3</v>
       </c>
       <c r="G11" t="n">
-        <v>57.8</v>
+        <v>58.4</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>36.93</v>
+        <v>36.9</v>
       </c>
       <c r="J11" t="n">
         <v>-35.74</v>
@@ -968,7 +968,7 @@
         <v>33.3</v>
       </c>
       <c r="G12" t="n">
-        <v>54.8</v>
+        <v>54</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -976,7 +976,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>35.13</v>
+        <v>35.02</v>
       </c>
       <c r="J12" t="n">
         <v>-48.6</v>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>62.75</v>
+        <v>64.29000000000001</v>
       </c>
     </row>
     <row r="6">

--- a/ETF_Allocation_Model.xlsx
+++ b/ETF_Allocation_Model.xlsx
@@ -502,7 +502,7 @@
         <v>183.3</v>
       </c>
       <c r="G2" t="n">
-        <v>74.8</v>
+        <v>75</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -549,7 +549,7 @@
         <v>183.3</v>
       </c>
       <c r="G3" t="n">
-        <v>74</v>
+        <v>74.3</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>13.01</v>
+        <v>12.99</v>
       </c>
       <c r="J3" t="n">
         <v>-21.07</v>
@@ -571,12 +571,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SWDA.MI</t>
+          <t>EIMI.MI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>iShares Core MSCI World UCITS ETF USD (Acc)</t>
+          <t>iShares Core MSCI EM IMI UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -586,7 +586,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Azionario globale sviluppato</t>
+          <t>Mercati emergenti</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -596,7 +596,7 @@
         <v>183.3</v>
       </c>
       <c r="G4" t="n">
-        <v>73.5</v>
+        <v>74</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -604,10 +604,10 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>13.21</v>
+        <v>17.06</v>
       </c>
       <c r="J4" t="n">
-        <v>-21.63</v>
+        <v>-19.17</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -643,7 +643,7 @@
         <v>66.7</v>
       </c>
       <c r="G5" t="n">
-        <v>72.3</v>
+        <v>72.2</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>9.69</v>
+        <v>9.68</v>
       </c>
       <c r="J5" t="n">
         <v>-12.85</v>
@@ -690,7 +690,7 @@
         <v>66.7</v>
       </c>
       <c r="G6" t="n">
-        <v>61.4</v>
+        <v>61.5</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -698,7 +698,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>18.96</v>
+        <v>18.89</v>
       </c>
       <c r="J6" t="n">
         <v>-22.72</v>
@@ -780,7 +780,7 @@
         <v>75</v>
       </c>
       <c r="G8" t="n">
-        <v>80.5</v>
+        <v>81.2</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>14.13</v>
+        <v>14.15</v>
       </c>
       <c r="J8" t="n">
         <v>-17.8</v>
@@ -827,7 +827,7 @@
         <v>75</v>
       </c>
       <c r="G9" t="n">
-        <v>71.59999999999999</v>
+        <v>71.7</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>12.86</v>
+        <v>12.85</v>
       </c>
       <c r="J9" t="n">
         <v>-20.6</v>
@@ -874,15 +874,15 @@
         <v>33.3</v>
       </c>
       <c r="G10" t="n">
-        <v>67.8</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Hold / Monitor</t>
+          <t>Accumulate Carefully</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>22.47</v>
+        <v>22.49</v>
       </c>
       <c r="J10" t="n">
         <v>-29.37</v>
@@ -921,7 +921,7 @@
         <v>33.3</v>
       </c>
       <c r="G11" t="n">
-        <v>58.4</v>
+        <v>64</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>36.9</v>
+        <v>36.91</v>
       </c>
       <c r="J11" t="n">
         <v>-35.74</v>
@@ -968,15 +968,15 @@
         <v>33.3</v>
       </c>
       <c r="G12" t="n">
-        <v>54</v>
+        <v>55.8</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>High Risk</t>
+          <t>Hold / Monitor</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>35.02</v>
+        <v>35.04</v>
       </c>
       <c r="J12" t="n">
         <v>-48.6</v>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>64.29000000000001</v>
+        <v>65.16</v>
       </c>
     </row>
     <row r="6">

--- a/ETF_Allocation_Model.xlsx
+++ b/ETF_Allocation_Model.xlsx
@@ -549,7 +549,7 @@
         <v>183.3</v>
       </c>
       <c r="G3" t="n">
-        <v>74.3</v>
+        <v>74.8</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -596,7 +596,7 @@
         <v>183.3</v>
       </c>
       <c r="G4" t="n">
-        <v>74</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -643,7 +643,7 @@
         <v>66.7</v>
       </c>
       <c r="G5" t="n">
-        <v>72.2</v>
+        <v>71.7</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>9.68</v>
+        <v>9.69</v>
       </c>
       <c r="J5" t="n">
         <v>-12.85</v>
@@ -690,7 +690,7 @@
         <v>66.7</v>
       </c>
       <c r="G6" t="n">
-        <v>61.5</v>
+        <v>62.1</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -698,7 +698,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>18.89</v>
+        <v>18.98</v>
       </c>
       <c r="J6" t="n">
         <v>-22.72</v>
@@ -780,7 +780,7 @@
         <v>75</v>
       </c>
       <c r="G8" t="n">
-        <v>81.2</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>14.15</v>
+        <v>14.14</v>
       </c>
       <c r="J8" t="n">
         <v>-17.8</v>
@@ -827,7 +827,7 @@
         <v>75</v>
       </c>
       <c r="G9" t="n">
-        <v>71.7</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -874,7 +874,7 @@
         <v>33.3</v>
       </c>
       <c r="G10" t="n">
-        <v>68.09999999999999</v>
+        <v>69.2</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -968,7 +968,7 @@
         <v>33.3</v>
       </c>
       <c r="G12" t="n">
-        <v>55.8</v>
+        <v>57.1</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -976,7 +976,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>35.04</v>
+        <v>35.1</v>
       </c>
       <c r="J12" t="n">
         <v>-48.6</v>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>65.16</v>
+        <v>65.54000000000001</v>
       </c>
     </row>
     <row r="6">

--- a/ETF_Allocation_Model.xlsx
+++ b/ETF_Allocation_Model.xlsx
@@ -596,7 +596,7 @@
         <v>183.3</v>
       </c>
       <c r="G4" t="n">
-        <v>74.40000000000001</v>
+        <v>74.5</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -643,7 +643,7 @@
         <v>66.7</v>
       </c>
       <c r="G5" t="n">
-        <v>71.7</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -690,7 +690,7 @@
         <v>66.7</v>
       </c>
       <c r="G6" t="n">
-        <v>62.1</v>
+        <v>62.4</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -698,7 +698,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>18.98</v>
+        <v>18.97</v>
       </c>
       <c r="J6" t="n">
         <v>-22.72</v>
@@ -968,7 +968,7 @@
         <v>33.3</v>
       </c>
       <c r="G12" t="n">
-        <v>57.1</v>
+        <v>57.4</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -976,7 +976,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>35.1</v>
+        <v>35.11</v>
       </c>
       <c r="J12" t="n">
         <v>-48.6</v>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>65.54000000000001</v>
+        <v>65.56999999999999</v>
       </c>
     </row>
     <row r="6">

--- a/ETF_Allocation_Model.xlsx
+++ b/ETF_Allocation_Model.xlsx
@@ -510,7 +510,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>12.76</v>
+        <v>12.77</v>
       </c>
       <c r="J2" t="n">
         <v>-16.33</v>
@@ -549,7 +549,7 @@
         <v>183.3</v>
       </c>
       <c r="G3" t="n">
-        <v>74.8</v>
+        <v>74.7</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>12.99</v>
+        <v>13</v>
       </c>
       <c r="J3" t="n">
         <v>-21.07</v>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>17.06</v>
+        <v>17.07</v>
       </c>
       <c r="J4" t="n">
         <v>-19.17</v>
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>9.69</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J5" t="n">
         <v>-12.85</v>
@@ -698,7 +698,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>18.97</v>
+        <v>18.99</v>
       </c>
       <c r="J6" t="n">
         <v>-22.72</v>
@@ -780,7 +780,7 @@
         <v>75</v>
       </c>
       <c r="G8" t="n">
-        <v>82.40000000000001</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -827,7 +827,7 @@
         <v>75</v>
       </c>
       <c r="G9" t="n">
-        <v>68.40000000000001</v>
+        <v>68.3</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>12.85</v>
+        <v>12.86</v>
       </c>
       <c r="J9" t="n">
         <v>-20.6</v>
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>22.49</v>
+        <v>22.5</v>
       </c>
       <c r="J10" t="n">
         <v>-29.37</v>
@@ -976,7 +976,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>35.11</v>
+        <v>35.13</v>
       </c>
       <c r="J12" t="n">
         <v>-48.6</v>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>65.56999999999999</v>
+        <v>65.55</v>
       </c>
     </row>
     <row r="6">

--- a/ETF_Allocation_Model.xlsx
+++ b/ETF_Allocation_Model.xlsx
@@ -524,12 +524,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>VWCE.DE</t>
+          <t>EIMI.MI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Vanguard FTSE All-World UCITS ETF USD Accumulation</t>
+          <t>iShares Core MSCI EM IMI UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -539,7 +539,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Azionario globale</t>
+          <t>Mercati emergenti</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -557,10 +557,10 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>13</v>
+        <v>17.07</v>
       </c>
       <c r="J3" t="n">
-        <v>-21.07</v>
+        <v>-19.17</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -571,12 +571,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>EIMI.MI</t>
+          <t>VWCE.DE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>iShares Core MSCI EM IMI UCITS ETF USD (Acc)</t>
+          <t>Vanguard FTSE All-World UCITS ETF USD Accumulation</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -586,7 +586,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Mercati emergenti</t>
+          <t>Azionario globale</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -596,7 +596,7 @@
         <v>183.3</v>
       </c>
       <c r="G4" t="n">
-        <v>74.5</v>
+        <v>74.7</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -604,10 +604,10 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>17.07</v>
+        <v>13</v>
       </c>
       <c r="J4" t="n">
-        <v>-19.17</v>
+        <v>-21.07</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -643,7 +643,7 @@
         <v>66.7</v>
       </c>
       <c r="G5" t="n">
-        <v>71.59999999999999</v>
+        <v>71.3</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>9.699999999999999</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="J5" t="n">
         <v>-12.85</v>
@@ -690,7 +690,7 @@
         <v>66.7</v>
       </c>
       <c r="G6" t="n">
-        <v>62.4</v>
+        <v>62.2</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>75</v>
       </c>
       <c r="G8" t="n">
-        <v>82.09999999999999</v>
+        <v>82</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -827,11 +827,11 @@
         <v>75</v>
       </c>
       <c r="G9" t="n">
-        <v>68.3</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Accumulate Carefully</t>
+          <t>Hold / Monitor</t>
         </is>
       </c>
       <c r="I9" t="n">
@@ -921,7 +921,7 @@
         <v>33.3</v>
       </c>
       <c r="G11" t="n">
-        <v>64</v>
+        <v>67.3</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>36.91</v>
+        <v>36.92</v>
       </c>
       <c r="J11" t="n">
         <v>-35.74</v>
@@ -968,7 +968,7 @@
         <v>33.3</v>
       </c>
       <c r="G12" t="n">
-        <v>57.4</v>
+        <v>58.4</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -976,7 +976,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>35.13</v>
+        <v>35.17</v>
       </c>
       <c r="J12" t="n">
         <v>-48.6</v>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>65.55</v>
+        <v>65.89</v>
       </c>
     </row>
     <row r="6">

--- a/ETF_Allocation_Model.xlsx
+++ b/ETF_Allocation_Model.xlsx
@@ -921,7 +921,7 @@
         <v>33.3</v>
       </c>
       <c r="G11" t="n">
-        <v>67.3</v>
+        <v>67</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>36.92</v>
+        <v>36.95</v>
       </c>
       <c r="J11" t="n">
         <v>-35.74</v>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>65.89</v>
+        <v>65.87</v>
       </c>
     </row>
     <row r="6">

--- a/ETF_Allocation_Model.xlsx
+++ b/ETF_Allocation_Model.xlsx
@@ -477,12 +477,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>VWCE.DE</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>iShares STOXX Europe 600 UCITS ETF (DE) EUR (Dist)</t>
+          <t>Vanguard FTSE All-World UCITS ETF USD Accumulation</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -492,7 +492,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Europa</t>
+          <t>Azionario globale</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -502,7 +502,7 @@
         <v>183.3</v>
       </c>
       <c r="G2" t="n">
-        <v>75</v>
+        <v>74.2</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -510,10 +510,10 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>12.77</v>
+        <v>13.01</v>
       </c>
       <c r="J2" t="n">
-        <v>-16.33</v>
+        <v>-21.07</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -549,7 +549,7 @@
         <v>183.3</v>
       </c>
       <c r="G3" t="n">
-        <v>74.7</v>
+        <v>73.8</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -571,12 +571,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>VWCE.DE</t>
+          <t>SWDA.MI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Vanguard FTSE All-World UCITS ETF USD Accumulation</t>
+          <t>iShares Core MSCI World UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -586,7 +586,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Azionario globale</t>
+          <t>Azionario globale sviluppato</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -596,7 +596,7 @@
         <v>183.3</v>
       </c>
       <c r="G4" t="n">
-        <v>74.7</v>
+        <v>70.2</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -604,10 +604,10 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>13</v>
+        <v>13.21</v>
       </c>
       <c r="J4" t="n">
-        <v>-21.07</v>
+        <v>-21.63</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -643,15 +643,15 @@
         <v>66.7</v>
       </c>
       <c r="G5" t="n">
-        <v>71.3</v>
+        <v>67.8</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Accumulate Carefully</t>
+          <t>Hold / Monitor</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>9.710000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J5" t="n">
         <v>-12.85</v>
@@ -690,7 +690,7 @@
         <v>66.7</v>
       </c>
       <c r="G6" t="n">
-        <v>62.2</v>
+        <v>62.5</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>75</v>
       </c>
       <c r="G8" t="n">
-        <v>82</v>
+        <v>81.2</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>14.14</v>
+        <v>14.16</v>
       </c>
       <c r="J8" t="n">
         <v>-17.8</v>
@@ -827,7 +827,7 @@
         <v>75</v>
       </c>
       <c r="G9" t="n">
-        <v>67.90000000000001</v>
+        <v>67.5</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>12.86</v>
+        <v>12.87</v>
       </c>
       <c r="J9" t="n">
         <v>-20.6</v>
@@ -849,12 +849,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>RBOT.MI</t>
+          <t>SMH</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>iShares Automation &amp; Robotics UCITS ETF USD (Acc)</t>
+          <t>VanEck Semiconductor ETF</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -864,7 +864,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Robotica e automazione</t>
+          <t>Semiconduttori</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -874,34 +874,34 @@
         <v>33.3</v>
       </c>
       <c r="G10" t="n">
-        <v>69.2</v>
+        <v>67</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Accumulate Carefully</t>
+          <t>Hold / Monitor</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>22.5</v>
+        <v>36.95</v>
       </c>
       <c r="J10" t="n">
-        <v>-29.37</v>
+        <v>-35.74</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
+          <t>Rischio elevato: usare solo come quota satellite e con size ridotta.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SMH</t>
+          <t>RBOT.MI</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>VanEck Semiconductor ETF</t>
+          <t>iShares Automation &amp; Robotics UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -911,7 +911,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Semiconduttori</t>
+          <t>Robotica e automazione</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -921,7 +921,7 @@
         <v>33.3</v>
       </c>
       <c r="G11" t="n">
-        <v>67</v>
+        <v>64.5</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -929,14 +929,14 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>36.95</v>
+        <v>22.51</v>
       </c>
       <c r="J11" t="n">
-        <v>-35.74</v>
+        <v>-29.37</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Rischio elevato: usare solo come quota satellite e con size ridotta.</t>
+          <t>Da monitorare: non è un segnale automatico di acquisto.</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
         <v>33.3</v>
       </c>
       <c r="G12" t="n">
-        <v>58.4</v>
+        <v>58.9</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -976,7 +976,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>35.17</v>
+        <v>35.15</v>
       </c>
       <c r="J12" t="n">
         <v>-48.6</v>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>65.87</v>
+        <v>64.20999999999999</v>
       </c>
     </row>
     <row r="6">

--- a/ETF_Allocation_Model.xlsx
+++ b/ETF_Allocation_Model.xlsx
@@ -502,7 +502,7 @@
         <v>183.3</v>
       </c>
       <c r="G2" t="n">
-        <v>74.2</v>
+        <v>74</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -549,7 +549,7 @@
         <v>183.3</v>
       </c>
       <c r="G3" t="n">
-        <v>73.8</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -571,12 +571,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SWDA.MI</t>
+          <t>EXSA.DE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>iShares Core MSCI World UCITS ETF USD (Acc)</t>
+          <t>iShares STOXX Europe 600 UCITS ETF (DE) EUR (Dist)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -586,7 +586,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Azionario globale sviluppato</t>
+          <t>Europa</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -596,7 +596,7 @@
         <v>183.3</v>
       </c>
       <c r="G4" t="n">
-        <v>70.2</v>
+        <v>70</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -604,10 +604,10 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>13.21</v>
+        <v>12.8</v>
       </c>
       <c r="J4" t="n">
-        <v>-21.63</v>
+        <v>-16.33</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -643,7 +643,7 @@
         <v>66.7</v>
       </c>
       <c r="G5" t="n">
-        <v>67.8</v>
+        <v>67.3</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>9.699999999999999</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="J5" t="n">
         <v>-12.85</v>
@@ -690,7 +690,7 @@
         <v>66.7</v>
       </c>
       <c r="G6" t="n">
-        <v>62.5</v>
+        <v>62.6</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>75</v>
       </c>
       <c r="G8" t="n">
-        <v>81.2</v>
+        <v>81.3</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -827,7 +827,7 @@
         <v>75</v>
       </c>
       <c r="G9" t="n">
-        <v>67.5</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>12.87</v>
+        <v>12.88</v>
       </c>
       <c r="J9" t="n">
         <v>-20.6</v>
@@ -874,7 +874,7 @@
         <v>33.3</v>
       </c>
       <c r="G10" t="n">
-        <v>67</v>
+        <v>67.3</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>36.95</v>
+        <v>36.92</v>
       </c>
       <c r="J10" t="n">
         <v>-35.74</v>
@@ -968,7 +968,7 @@
         <v>33.3</v>
       </c>
       <c r="G12" t="n">
-        <v>58.9</v>
+        <v>59.2</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -976,7 +976,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>35.15</v>
+        <v>35.17</v>
       </c>
       <c r="J12" t="n">
         <v>-48.6</v>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>64.20999999999999</v>
+        <v>64.03</v>
       </c>
     </row>
     <row r="6">

--- a/ETF_Allocation_Model.xlsx
+++ b/ETF_Allocation_Model.xlsx
@@ -874,7 +874,7 @@
         <v>33.3</v>
       </c>
       <c r="G10" t="n">
-        <v>67.3</v>
+        <v>67.2</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>64.03</v>
+        <v>64.02</v>
       </c>
     </row>
     <row r="6">

--- a/ETF_Allocation_Model.xlsx
+++ b/ETF_Allocation_Model.xlsx
@@ -477,12 +477,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>VWCE.DE</t>
+          <t>EIMI.MI</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Vanguard FTSE All-World UCITS ETF USD Accumulation</t>
+          <t>iShares Core MSCI EM IMI UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -492,7 +492,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Azionario globale</t>
+          <t>Mercati emergenti</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -502,7 +502,7 @@
         <v>183.3</v>
       </c>
       <c r="G2" t="n">
-        <v>74</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -510,10 +510,10 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>13.01</v>
+        <v>17.08</v>
       </c>
       <c r="J2" t="n">
-        <v>-21.07</v>
+        <v>-19.17</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -524,12 +524,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>EIMI.MI</t>
+          <t>VWCE.DE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>iShares Core MSCI EM IMI UCITS ETF USD (Acc)</t>
+          <t>Vanguard FTSE All-World UCITS ETF USD Accumulation</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -539,7 +539,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Mercati emergenti</t>
+          <t>Azionario globale</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -549,7 +549,7 @@
         <v>183.3</v>
       </c>
       <c r="G3" t="n">
-        <v>73.90000000000001</v>
+        <v>69.8</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -557,10 +557,10 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>17.07</v>
+        <v>13.01</v>
       </c>
       <c r="J3" t="n">
-        <v>-19.17</v>
+        <v>-21.07</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -571,12 +571,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>SWDA.MI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>iShares STOXX Europe 600 UCITS ETF (DE) EUR (Dist)</t>
+          <t>iShares Core MSCI World UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -586,7 +586,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Europa</t>
+          <t>Azionario globale sviluppato</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -596,7 +596,7 @@
         <v>183.3</v>
       </c>
       <c r="G4" t="n">
-        <v>70</v>
+        <v>69.3</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -604,10 +604,10 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>12.8</v>
+        <v>13.21</v>
       </c>
       <c r="J4" t="n">
-        <v>-16.33</v>
+        <v>-21.63</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -643,7 +643,7 @@
         <v>66.7</v>
       </c>
       <c r="G5" t="n">
-        <v>67.3</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>9.720000000000001</v>
+        <v>9.69</v>
       </c>
       <c r="J5" t="n">
         <v>-12.85</v>
@@ -690,7 +690,7 @@
         <v>66.7</v>
       </c>
       <c r="G6" t="n">
-        <v>62.6</v>
+        <v>61.2</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -698,7 +698,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>18.99</v>
+        <v>18.98</v>
       </c>
       <c r="J6" t="n">
         <v>-22.72</v>
@@ -780,7 +780,7 @@
         <v>75</v>
       </c>
       <c r="G8" t="n">
-        <v>81.3</v>
+        <v>80.2</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>14.16</v>
+        <v>14.15</v>
       </c>
       <c r="J8" t="n">
         <v>-17.8</v>
@@ -827,7 +827,7 @@
         <v>75</v>
       </c>
       <c r="G9" t="n">
-        <v>67.09999999999999</v>
+        <v>66.8</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>12.88</v>
+        <v>12.86</v>
       </c>
       <c r="J9" t="n">
         <v>-20.6</v>
@@ -921,7 +921,7 @@
         <v>33.3</v>
       </c>
       <c r="G11" t="n">
-        <v>64.5</v>
+        <v>62.5</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -976,7 +976,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>35.17</v>
+        <v>35.13</v>
       </c>
       <c r="J12" t="n">
         <v>-48.6</v>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>64.02</v>
+        <v>63.04</v>
       </c>
     </row>
     <row r="6">

--- a/ETF_Allocation_Model.xlsx
+++ b/ETF_Allocation_Model.xlsx
@@ -502,7 +502,7 @@
         <v>183.3</v>
       </c>
       <c r="G2" t="n">
-        <v>72.40000000000001</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -510,7 +510,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>17.08</v>
+        <v>17.12</v>
       </c>
       <c r="J2" t="n">
         <v>-19.17</v>
@@ -549,7 +549,7 @@
         <v>183.3</v>
       </c>
       <c r="G3" t="n">
-        <v>69.8</v>
+        <v>69.3</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>13.01</v>
+        <v>13.03</v>
       </c>
       <c r="J3" t="n">
         <v>-21.07</v>
@@ -596,7 +596,7 @@
         <v>183.3</v>
       </c>
       <c r="G4" t="n">
-        <v>69.3</v>
+        <v>68.8</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>13.21</v>
+        <v>13.23</v>
       </c>
       <c r="J4" t="n">
         <v>-21.63</v>
@@ -643,7 +643,7 @@
         <v>66.7</v>
       </c>
       <c r="G5" t="n">
-        <v>67.59999999999999</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>9.69</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J5" t="n">
         <v>-12.85</v>
@@ -690,7 +690,7 @@
         <v>66.7</v>
       </c>
       <c r="G6" t="n">
-        <v>61.2</v>
+        <v>61</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>75</v>
       </c>
       <c r="G8" t="n">
-        <v>80.2</v>
+        <v>79.8</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>14.15</v>
+        <v>14.16</v>
       </c>
       <c r="J8" t="n">
         <v>-17.8</v>
@@ -827,7 +827,7 @@
         <v>75</v>
       </c>
       <c r="G9" t="n">
-        <v>66.8</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>12.86</v>
+        <v>12.88</v>
       </c>
       <c r="J9" t="n">
         <v>-20.6</v>
@@ -874,7 +874,7 @@
         <v>33.3</v>
       </c>
       <c r="G10" t="n">
-        <v>67.2</v>
+        <v>62.8</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -921,7 +921,7 @@
         <v>33.3</v>
       </c>
       <c r="G11" t="n">
-        <v>62.5</v>
+        <v>61.9</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>22.51</v>
+        <v>22.54</v>
       </c>
       <c r="J11" t="n">
         <v>-29.37</v>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>63.04</v>
+        <v>62.32</v>
       </c>
     </row>
     <row r="6">

--- a/ETF_Allocation_Model.xlsx
+++ b/ETF_Allocation_Model.xlsx
@@ -502,7 +502,7 @@
         <v>183.3</v>
       </c>
       <c r="G2" t="n">
-        <v>71.59999999999999</v>
+        <v>71.8</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -510,7 +510,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>17.12</v>
+        <v>17.1</v>
       </c>
       <c r="J2" t="n">
         <v>-19.17</v>
@@ -549,7 +549,7 @@
         <v>183.3</v>
       </c>
       <c r="G3" t="n">
-        <v>69.3</v>
+        <v>69.5</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>13.03</v>
+        <v>13.02</v>
       </c>
       <c r="J3" t="n">
         <v>-21.07</v>
@@ -596,7 +596,7 @@
         <v>183.3</v>
       </c>
       <c r="G4" t="n">
-        <v>68.8</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>13.23</v>
+        <v>13.22</v>
       </c>
       <c r="J4" t="n">
         <v>-21.63</v>
@@ -643,7 +643,7 @@
         <v>66.7</v>
       </c>
       <c r="G5" t="n">
-        <v>67.40000000000001</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>75</v>
       </c>
       <c r="G8" t="n">
-        <v>79.8</v>
+        <v>79.7</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>14.16</v>
+        <v>14.17</v>
       </c>
       <c r="J8" t="n">
         <v>-17.8</v>
@@ -827,7 +827,7 @@
         <v>75</v>
       </c>
       <c r="G9" t="n">
-        <v>66.09999999999999</v>
+        <v>66.3</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>12.88</v>
+        <v>12.87</v>
       </c>
       <c r="J9" t="n">
         <v>-20.6</v>
@@ -874,7 +874,7 @@
         <v>33.3</v>
       </c>
       <c r="G10" t="n">
-        <v>62.8</v>
+        <v>63.1</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -921,7 +921,7 @@
         <v>33.3</v>
       </c>
       <c r="G11" t="n">
-        <v>61.9</v>
+        <v>62.1</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>22.54</v>
+        <v>22.53</v>
       </c>
       <c r="J11" t="n">
         <v>-29.37</v>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>62.32</v>
+        <v>62.44</v>
       </c>
     </row>
     <row r="6">

--- a/ETF_Allocation_Model.xlsx
+++ b/ETF_Allocation_Model.xlsx
@@ -874,7 +874,7 @@
         <v>33.3</v>
       </c>
       <c r="G10" t="n">
-        <v>63.1</v>
+        <v>62.7</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>62.44</v>
+        <v>62.41</v>
       </c>
     </row>
     <row r="6">

--- a/ETF_Allocation_Model.xlsx
+++ b/ETF_Allocation_Model.xlsx
@@ -874,7 +874,7 @@
         <v>33.3</v>
       </c>
       <c r="G10" t="n">
-        <v>62.7</v>
+        <v>62.5</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>36.92</v>
+        <v>36.93</v>
       </c>
       <c r="J10" t="n">
         <v>-35.74</v>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>62.41</v>
+        <v>62.39</v>
       </c>
     </row>
     <row r="6">

--- a/ETF_Allocation_Model.xlsx
+++ b/ETF_Allocation_Model.xlsx
@@ -477,12 +477,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>EIMI.MI</t>
+          <t>VWCE.DE</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>iShares Core MSCI EM IMI UCITS ETF USD (Acc)</t>
+          <t>Vanguard FTSE All-World UCITS ETF USD Accumulation</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -492,7 +492,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Mercati emergenti</t>
+          <t>Azionario globale</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -502,7 +502,7 @@
         <v>183.3</v>
       </c>
       <c r="G2" t="n">
-        <v>71.8</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -510,10 +510,10 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>17.1</v>
+        <v>12.99</v>
       </c>
       <c r="J2" t="n">
-        <v>-19.17</v>
+        <v>-21.07</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -524,12 +524,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>VWCE.DE</t>
+          <t>EIMI.MI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Vanguard FTSE All-World UCITS ETF USD Accumulation</t>
+          <t>iShares Core MSCI EM IMI UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -539,7 +539,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Azionario globale</t>
+          <t>Mercati emergenti</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -549,7 +549,7 @@
         <v>183.3</v>
       </c>
       <c r="G3" t="n">
-        <v>69.5</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -557,10 +557,10 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>13.02</v>
+        <v>17.06</v>
       </c>
       <c r="J3" t="n">
-        <v>-21.07</v>
+        <v>-19.17</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -596,7 +596,7 @@
         <v>183.3</v>
       </c>
       <c r="G4" t="n">
-        <v>68.90000000000001</v>
+        <v>69.2</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>13.22</v>
+        <v>13.2</v>
       </c>
       <c r="J4" t="n">
         <v>-21.63</v>
@@ -643,7 +643,7 @@
         <v>66.7</v>
       </c>
       <c r="G5" t="n">
-        <v>67.09999999999999</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -690,7 +690,7 @@
         <v>66.7</v>
       </c>
       <c r="G6" t="n">
-        <v>61</v>
+        <v>59.7</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>75</v>
       </c>
       <c r="G8" t="n">
-        <v>79.7</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>14.17</v>
+        <v>14.14</v>
       </c>
       <c r="J8" t="n">
         <v>-17.8</v>
@@ -827,7 +827,7 @@
         <v>75</v>
       </c>
       <c r="G9" t="n">
-        <v>66.3</v>
+        <v>66.7</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>12.87</v>
+        <v>12.85</v>
       </c>
       <c r="J9" t="n">
         <v>-20.6</v>
@@ -921,7 +921,7 @@
         <v>33.3</v>
       </c>
       <c r="G11" t="n">
-        <v>62.1</v>
+        <v>61.3</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>22.53</v>
+        <v>22.49</v>
       </c>
       <c r="J11" t="n">
         <v>-29.37</v>
@@ -976,7 +976,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>35.13</v>
+        <v>35.1</v>
       </c>
       <c r="J12" t="n">
         <v>-48.6</v>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>62.39</v>
+        <v>62.68</v>
       </c>
     </row>
     <row r="6">

--- a/ETF_Allocation_Model.xlsx
+++ b/ETF_Allocation_Model.xlsx
@@ -502,7 +502,7 @@
         <v>183.3</v>
       </c>
       <c r="G2" t="n">
-        <v>73.09999999999999</v>
+        <v>73.2</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -524,12 +524,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>EIMI.MI</t>
+          <t>SXR8.DE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>iShares Core MSCI EM IMI UCITS ETF USD (Acc)</t>
+          <t>iShares Core S&amp;P 500 UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -539,7 +539,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Mercati emergenti</t>
+          <t>USA large cap</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -549,7 +549,7 @@
         <v>183.3</v>
       </c>
       <c r="G3" t="n">
-        <v>71.40000000000001</v>
+        <v>71.8</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -557,10 +557,10 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>17.06</v>
+        <v>14.25</v>
       </c>
       <c r="J3" t="n">
-        <v>-19.17</v>
+        <v>-23.32</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -571,12 +571,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SWDA.MI</t>
+          <t>EIMI.MI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>iShares Core MSCI World UCITS ETF USD (Acc)</t>
+          <t>iShares Core MSCI EM IMI UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -586,7 +586,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Azionario globale sviluppato</t>
+          <t>Mercati emergenti</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -596,7 +596,7 @@
         <v>183.3</v>
       </c>
       <c r="G4" t="n">
-        <v>69.2</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -604,10 +604,10 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>13.2</v>
+        <v>17.06</v>
       </c>
       <c r="J4" t="n">
-        <v>-21.63</v>
+        <v>-19.17</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -643,7 +643,7 @@
         <v>66.7</v>
       </c>
       <c r="G5" t="n">
-        <v>67.59999999999999</v>
+        <v>67.7</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -690,7 +690,7 @@
         <v>66.7</v>
       </c>
       <c r="G6" t="n">
-        <v>59.7</v>
+        <v>60.4</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -698,7 +698,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>18.98</v>
+        <v>18.96</v>
       </c>
       <c r="J6" t="n">
         <v>-22.72</v>
@@ -780,7 +780,7 @@
         <v>75</v>
       </c>
       <c r="G8" t="n">
-        <v>79.59999999999999</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>14.14</v>
+        <v>14.13</v>
       </c>
       <c r="J8" t="n">
         <v>-17.8</v>
@@ -874,7 +874,7 @@
         <v>33.3</v>
       </c>
       <c r="G10" t="n">
-        <v>62.5</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>36.93</v>
+        <v>36.92</v>
       </c>
       <c r="J10" t="n">
         <v>-35.74</v>
@@ -921,7 +921,7 @@
         <v>33.3</v>
       </c>
       <c r="G11" t="n">
-        <v>61.3</v>
+        <v>61.8</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>22.49</v>
+        <v>22.48</v>
       </c>
       <c r="J11" t="n">
         <v>-29.37</v>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>62.68</v>
+        <v>63.34</v>
       </c>
     </row>
     <row r="6">

--- a/ETF_Allocation_Model.xlsx
+++ b/ETF_Allocation_Model.xlsx
@@ -502,7 +502,7 @@
         <v>183.3</v>
       </c>
       <c r="G2" t="n">
-        <v>73.2</v>
+        <v>73.3</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -510,7 +510,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>12.99</v>
+        <v>13</v>
       </c>
       <c r="J2" t="n">
         <v>-21.07</v>
@@ -524,12 +524,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SXR8.DE</t>
+          <t>SWDA.MI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>iShares Core S&amp;P 500 UCITS ETF USD (Acc)</t>
+          <t>iShares Core MSCI World UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -539,7 +539,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>USA large cap</t>
+          <t>Azionario globale sviluppato</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -549,7 +549,7 @@
         <v>183.3</v>
       </c>
       <c r="G3" t="n">
-        <v>71.8</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -557,10 +557,10 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>14.25</v>
+        <v>13.2</v>
       </c>
       <c r="J3" t="n">
-        <v>-23.32</v>
+        <v>-21.63</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -571,12 +571,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>EIMI.MI</t>
+          <t>SXR8.DE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>iShares Core MSCI EM IMI UCITS ETF USD (Acc)</t>
+          <t>iShares Core S&amp;P 500 UCITS ETF USD (Acc)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -586,7 +586,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Mercati emergenti</t>
+          <t>USA large cap</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -596,7 +596,7 @@
         <v>183.3</v>
       </c>
       <c r="G4" t="n">
-        <v>71.40000000000001</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -604,10 +604,10 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>17.06</v>
+        <v>14.25</v>
       </c>
       <c r="J4" t="n">
-        <v>-19.17</v>
+        <v>-23.32</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -643,7 +643,7 @@
         <v>66.7</v>
       </c>
       <c r="G5" t="n">
-        <v>67.7</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -690,7 +690,7 @@
         <v>66.7</v>
       </c>
       <c r="G6" t="n">
-        <v>60.4</v>
+        <v>60.2</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -698,7 +698,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>18.96</v>
+        <v>18.97</v>
       </c>
       <c r="J6" t="n">
         <v>-22.72</v>
@@ -780,7 +780,7 @@
         <v>75</v>
       </c>
       <c r="G8" t="n">
-        <v>79.90000000000001</v>
+        <v>80</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>14.13</v>
+        <v>14.14</v>
       </c>
       <c r="J8" t="n">
         <v>-17.8</v>
@@ -827,7 +827,7 @@
         <v>75</v>
       </c>
       <c r="G9" t="n">
-        <v>66.7</v>
+        <v>66.8</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -921,7 +921,7 @@
         <v>33.3</v>
       </c>
       <c r="G11" t="n">
-        <v>61.8</v>
+        <v>62.3</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -976,7 +976,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>35.1</v>
+        <v>35.11</v>
       </c>
       <c r="J12" t="n">
         <v>-48.6</v>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>63.34</v>
+        <v>63.67</v>
       </c>
     </row>
     <row r="6">

--- a/ETF_Allocation_Model.xlsx
+++ b/ETF_Allocation_Model.xlsx
@@ -874,7 +874,7 @@
         <v>33.3</v>
       </c>
       <c r="G10" t="n">
-        <v>66.09999999999999</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>36.92</v>
+        <v>36.91</v>
       </c>
       <c r="J10" t="n">
         <v>-35.74</v>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>63.67</v>
+        <v>63.66</v>
       </c>
     </row>
     <row r="6">

--- a/ETF_Allocation_Model.xlsx
+++ b/ETF_Allocation_Model.xlsx
@@ -874,7 +874,7 @@
         <v>33.3</v>
       </c>
       <c r="G10" t="n">
-        <v>65.90000000000001</v>
+        <v>62.4</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>36.91</v>
+        <v>36.93</v>
       </c>
       <c r="J10" t="n">
         <v>-35.74</v>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>63.66</v>
+        <v>63.41</v>
       </c>
     </row>
     <row r="6">
